--- a/files/Controller Design/ZNMethods_ITAE_Errors.xlsx
+++ b/files/Controller Design/ZNMethods_ITAE_Errors.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulisboa-my.sharepoint.com/personal/ist1100262_tecnico_ulisboa_pt/Documents/MEMec/Thesis/files/Controller Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{95F32091-D855-4402-ADD3-8991BE5FE270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57578E72-98F7-491C-B14A-8C7045C7D2C3}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{95F32091-D855-4402-ADD3-8991BE5FE270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD873D05-E60F-41DE-AA59-2D68210EC1D0}"/>
   <bookViews>
-    <workbookView xWindow="-3696" yWindow="-17388" windowWidth="30936" windowHeight="17496" xr2:uid="{6BCB78A0-0C46-4270-8084-079A19E30873}"/>
+    <workbookView xWindow="-3696" yWindow="-17388" windowWidth="30936" windowHeight="17496" activeTab="1" xr2:uid="{6BCB78A0-0C46-4270-8084-079A19E30873}"/>
   </bookViews>
   <sheets>
     <sheet name="CritGain" sheetId="1" r:id="rId1"/>
+    <sheet name="Folha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="19">
   <si>
     <t>ν/ζ</t>
   </si>
@@ -48,12 +49,6 @@
   </si>
   <si>
     <t>Ziegler-Nichols Methods</t>
-  </si>
-  <si>
-    <t>Critical Gain Method</t>
-  </si>
-  <si>
-    <t>S-Shape Method</t>
   </si>
   <si>
     <t>Mean</t>
@@ -84,6 +79,24 @@
   </si>
   <si>
     <t>Note: 'NaN' implies Not S-Shaped and 'Inf' implies that the system is unstable</t>
+  </si>
+  <si>
+    <t>Z-N Critical Gain</t>
+  </si>
+  <si>
+    <t>Z-N S-Shape</t>
+  </si>
+  <si>
+    <t>PSO</t>
+  </si>
+  <si>
+    <t>iters</t>
+  </si>
+  <si>
+    <t>particles</t>
+  </si>
+  <si>
+    <t>x\</t>
   </si>
 </sst>
 </file>
@@ -504,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -525,17 +538,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -546,36 +572,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -617,28 +622,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -979,7 +963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E4CF69-D65E-4E98-B411-A1D521930B25}">
-  <dimension ref="B1:N29"/>
+  <dimension ref="B1:P42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" customWidth="1"/>
@@ -989,31 +973,31 @@
   <sheetData>
     <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
     </row>
     <row r="3" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="21"/>
+      <c r="B3" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
     </row>
     <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="21"/>
+      <c r="B6" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
     </row>
     <row r="7" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="20" t="s">
         <v>0</v>
       </c>
       <c r="C7" s="17">
@@ -1046,18 +1030,18 @@
       <c r="L7" s="19">
         <v>5</v>
       </c>
-      <c r="M7" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" s="28" t="s">
-        <v>10</v>
+      <c r="M7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="N7" s="22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="13">
         <v>0.5</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="23" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -1087,8 +1071,8 @@
       <c r="L8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="M8" s="30" t="s">
-        <v>5</v>
+      <c r="M8" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="5">
         <f>AVERAGE(C8:L15)</f>
@@ -1129,8 +1113,8 @@
       <c r="L9" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M9" s="30" t="s">
-        <v>6</v>
+      <c r="M9" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="N9" s="5">
         <f>MEDIAN(C8:L15)</f>
@@ -1171,8 +1155,8 @@
       <c r="L10" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M10" s="30" t="s">
-        <v>7</v>
+      <c r="M10" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="N10" s="5">
         <f>MAX(C8:L15)</f>
@@ -1213,8 +1197,8 @@
       <c r="L11" s="5">
         <v>4.5002000000000004</v>
       </c>
-      <c r="M11" s="30" t="s">
-        <v>8</v>
+      <c r="M11" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="N11" s="5">
         <f>MIN(C8:L15)</f>
@@ -1300,7 +1284,7 @@
         <v>1.7</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1">
         <v>32.021099999999997</v>
@@ -1333,17 +1317,17 @@
       <c r="N14" s="5"/>
     </row>
     <row r="15" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="31">
+      <c r="B15" s="24">
         <v>1.9</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F15" s="7">
         <v>100.63500000000001</v>
@@ -1370,32 +1354,32 @@
       <c r="N15" s="8"/>
     </row>
     <row r="16" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="34"/>
+      <c r="B16" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="27"/>
     </row>
     <row r="18" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="21"/>
+      <c r="B19" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="29"/>
+      <c r="D19" s="30"/>
     </row>
     <row r="20" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="20" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="17">
@@ -1428,11 +1412,11 @@
       <c r="L20" s="19">
         <v>5</v>
       </c>
-      <c r="M20" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="N20" s="28" t="s">
-        <v>10</v>
+      <c r="M20" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="N20" s="22" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.3">
@@ -1469,8 +1453,8 @@
       <c r="L21" s="16">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="M21" s="30" t="s">
-        <v>5</v>
+      <c r="M21" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="N21" s="5">
         <f>AVERAGE(C21:L28)</f>
@@ -1511,8 +1495,8 @@
       <c r="L22" s="5">
         <v>1.11E-2</v>
       </c>
-      <c r="M22" s="30" t="s">
-        <v>6</v>
+      <c r="M22" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="5">
         <f>MEDIAN(C21:L28)</f>
@@ -1553,8 +1537,8 @@
       <c r="L23" s="5">
         <v>3.39E-2</v>
       </c>
-      <c r="M23" s="30" t="s">
-        <v>7</v>
+      <c r="M23" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="N23" s="5">
         <f>MAX(C21:L28)</f>
@@ -1595,8 +1579,8 @@
       <c r="L24" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M24" s="30" t="s">
-        <v>8</v>
+      <c r="M24" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="N24" s="5">
         <f>MIN(C21:L28)</f>
@@ -1682,7 +1666,7 @@
         <v>1.7</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>1</v>
@@ -1719,13 +1703,13 @@
         <v>1.9</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>1</v>
@@ -1752,67 +1736,429 @@
       <c r="N28" s="8"/>
     </row>
     <row r="29" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="34"/>
+      <c r="B29" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="27"/>
+    </row>
+    <row r="31" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="29"/>
+      <c r="D32" s="30"/>
+    </row>
+    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="D33" s="18">
+        <v>1</v>
+      </c>
+      <c r="E33" s="18">
+        <v>1.5</v>
+      </c>
+      <c r="F33" s="18">
+        <v>2</v>
+      </c>
+      <c r="G33" s="18">
+        <v>2.5</v>
+      </c>
+      <c r="H33" s="18">
+        <v>3</v>
+      </c>
+      <c r="I33" s="18">
+        <v>3.5</v>
+      </c>
+      <c r="J33" s="18">
+        <v>4</v>
+      </c>
+      <c r="K33" s="18">
+        <v>4.5</v>
+      </c>
+      <c r="L33" s="19">
+        <v>5</v>
+      </c>
+      <c r="M33" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="N33" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="O33" t="s">
+        <v>16</v>
+      </c>
+      <c r="P33">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B34" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="C34" s="14">
+        <v>2.29E-2</v>
+      </c>
+      <c r="D34" s="15">
+        <v>5.1900000000000002E-2</v>
+      </c>
+      <c r="E34" s="15">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="F34" s="15">
+        <v>0.1129</v>
+      </c>
+      <c r="G34" s="15">
+        <v>0.14410000000000001</v>
+      </c>
+      <c r="H34" s="15">
+        <v>0.1759</v>
+      </c>
+      <c r="I34" s="15">
+        <v>0.20710000000000001</v>
+      </c>
+      <c r="J34" s="15">
+        <v>0.23860000000000001</v>
+      </c>
+      <c r="K34" s="15">
+        <v>0.27060000000000001</v>
+      </c>
+      <c r="L34" s="16">
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N34" s="5">
+        <f>AVERAGE(C34:L41)</f>
+        <v>0.11138157894736841</v>
+      </c>
+      <c r="O34" t="s">
+        <v>17</v>
+      </c>
+      <c r="P34">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B35" s="11">
+        <v>0.7</v>
+      </c>
+      <c r="C35" s="9">
+        <v>1.3299999999999999E-2</v>
+      </c>
+      <c r="D35" s="1">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="E35" s="1">
+        <v>5.6399999999999999E-2</v>
+      </c>
+      <c r="F35" s="1">
+        <v>7.8200000000000006E-2</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0.12180000000000001</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0.14360000000000001</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0.16539999999999999</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0.18809999999999999</v>
+      </c>
+      <c r="L35" s="5">
+        <v>0.20910000000000001</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="N35" s="5">
+        <f>MEDIAN(C34:L41)</f>
+        <v>0.10395</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B36" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="C36" s="9">
+        <v>3.3E-3</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1.46E-2</v>
+      </c>
+      <c r="E36" s="1">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F36" s="1">
+        <v>4.6300000000000001E-2</v>
+      </c>
+      <c r="G36" s="1">
+        <v>6.08E-2</v>
+      </c>
+      <c r="H36" s="1">
+        <v>7.5399999999999995E-2</v>
+      </c>
+      <c r="I36" s="1">
+        <v>9.01E-2</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0.1048</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0.1196</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0.13450000000000001</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="N36" s="5">
+        <f>MAX(C34:L41)</f>
+        <v>0.30299999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B37" s="11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C37" s="9">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="D37" s="1">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2.23E-2</v>
+      </c>
+      <c r="F37" s="1">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="G37" s="1">
+        <v>5.1700000000000003E-2</v>
+      </c>
+      <c r="H37" s="1">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I37" s="1">
+        <v>7.7600000000000002E-2</v>
+      </c>
+      <c r="J37" s="1">
+        <v>9.0399999999999994E-2</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0.10349999999999999</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0.1168</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="N37" s="5">
+        <f>MIN(C34:L41)</f>
+        <v>2.3999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B38" s="11">
+        <v>1.3</v>
+      </c>
+      <c r="C38" s="9">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="E38" s="1">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="F38" s="1">
+        <v>6.0100000000000001E-2</v>
+      </c>
+      <c r="G38" s="1">
+        <v>7.4300000000000005E-2</v>
+      </c>
+      <c r="H38" s="1">
+        <v>8.9099999999999999E-2</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0.10440000000000001</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0.1198</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0.1368</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0.15590000000000001</v>
+      </c>
+      <c r="M38" s="4"/>
+      <c r="N38" s="5"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B39" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="C39" s="9">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2.12E-2</v>
+      </c>
+      <c r="E39" s="1">
+        <v>4.87E-2</v>
+      </c>
+      <c r="F39" s="1">
+        <v>7.1199999999999999E-2</v>
+      </c>
+      <c r="G39" s="1">
+        <v>9.69E-2</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0.1229</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0.14710000000000001</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0.17230000000000001</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0.19889999999999999</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0.22689999999999999</v>
+      </c>
+      <c r="M39" s="4"/>
+      <c r="N39" s="5"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B40" s="11">
+        <v>1.7</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="E40" s="1">
+        <v>7.1099999999999997E-2</v>
+      </c>
+      <c r="F40" s="1">
+        <v>8.8400000000000006E-2</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0.1091</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0.1318</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0.15620000000000001</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0.18210000000000001</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0.2089</v>
+      </c>
+      <c r="L40" s="5">
+        <v>0.2364</v>
+      </c>
+      <c r="M40" s="4"/>
+      <c r="N40" s="5"/>
+    </row>
+    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="12">
+        <v>1.9</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="7">
+        <v>0.14130000000000001</v>
+      </c>
+      <c r="G41" s="7">
+        <v>0.14530000000000001</v>
+      </c>
+      <c r="H41" s="7">
+        <v>0.1588</v>
+      </c>
+      <c r="I41" s="7">
+        <v>0.1757</v>
+      </c>
+      <c r="J41" s="7">
+        <v>0.19739999999999999</v>
+      </c>
+      <c r="K41" s="7">
+        <v>0.22239999999999999</v>
+      </c>
+      <c r="L41" s="8">
+        <v>0.24790000000000001</v>
+      </c>
+      <c r="M41" s="6"/>
+      <c r="N41" s="8"/>
+    </row>
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B32:D32"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:L15 M8:M11">
-    <cfRule type="containsText" dxfId="8" priority="7" operator="containsText" text="NaN">
+    <cfRule type="containsText" dxfId="7" priority="12" operator="containsText" text="NaN">
       <formula>NOT(ISERROR(SEARCH("NaN",C8)))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C21:L28">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="NaN">
-      <formula>NOT(ISERROR(SEARCH("NaN",C21)))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF92D050"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFFF0000"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="Inf">
-      <formula>NOT(ISERROR(SEARCH("Inf",C21)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M21:M24">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="NaN">
-      <formula>NOT(ISERROR(SEARCH("NaN",M21)))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1824,11 +2170,1746 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:L15">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Inf">
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="Inf">
       <formula>NOT(ISERROR(SEARCH("Inf",C8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:L28">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="Inf">
+      <formula>NOT(ISERROR(SEARCH("Inf",C21)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="10" operator="containsText" text="NaN">
+      <formula>NOT(ISERROR(SEARCH("NaN",C21)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C34:L41">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Inf">
+      <formula>NOT(ISERROR(SEARCH("Inf",C34)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="NaN">
+      <formula>NOT(ISERROR(SEARCH("NaN",C34)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M21:M24">
+    <cfRule type="containsText" dxfId="1" priority="8" operator="containsText" text="NaN">
+      <formula>NOT(ISERROR(SEARCH("NaN",M21)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M34:M37">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="NaN">
+      <formula>NOT(ISERROR(SEARCH("NaN",M34)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0560039F-0F7B-4DB4-BC89-56D20BBE7290}">
+  <dimension ref="B1:AB32"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="20" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C3">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="D3">
+        <v>1.83E-2</v>
+      </c>
+      <c r="E3">
+        <v>4.36E-2</v>
+      </c>
+      <c r="F3">
+        <v>6.9400000000000003E-2</v>
+      </c>
+      <c r="G3">
+        <v>9.5299999999999996E-2</v>
+      </c>
+      <c r="H3">
+        <v>0.1212</v>
+      </c>
+      <c r="I3">
+        <v>0.1482</v>
+      </c>
+      <c r="J3">
+        <v>0.17449999999999999</v>
+      </c>
+      <c r="K3">
+        <v>0.20180000000000001</v>
+      </c>
+      <c r="L3">
+        <v>0.2283</v>
+      </c>
+      <c r="M3">
+        <v>0.25530000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C4">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="D4">
+        <v>1.3299999999999999E-2</v>
+      </c>
+      <c r="E4">
+        <v>3.4700000000000002E-2</v>
+      </c>
+      <c r="F4">
+        <v>5.6399999999999999E-2</v>
+      </c>
+      <c r="G4">
+        <v>7.85E-2</v>
+      </c>
+      <c r="H4">
+        <v>0.1</v>
+      </c>
+      <c r="I4">
+        <v>0.12180000000000001</v>
+      </c>
+      <c r="J4">
+        <v>0.14360000000000001</v>
+      </c>
+      <c r="K4">
+        <v>0.16619999999999999</v>
+      </c>
+      <c r="L4">
+        <v>0.18809999999999999</v>
+      </c>
+      <c r="M4">
+        <v>0.20960000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C5">
+        <v>3.7000000000000002E-3</v>
+      </c>
+      <c r="D5">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="E5">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="F5">
+        <v>4.3700000000000003E-2</v>
+      </c>
+      <c r="G5">
+        <v>6.1600000000000002E-2</v>
+      </c>
+      <c r="H5">
+        <v>7.9500000000000001E-2</v>
+      </c>
+      <c r="I5">
+        <v>9.74E-2</v>
+      </c>
+      <c r="J5">
+        <v>0.11550000000000001</v>
+      </c>
+      <c r="K5">
+        <v>0.13539999999999999</v>
+      </c>
+      <c r="L5">
+        <v>0.15160000000000001</v>
+      </c>
+      <c r="M5">
+        <v>0.1696</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C6">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="D6">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="E6">
+        <v>1.8100000000000002E-2</v>
+      </c>
+      <c r="F6">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G6">
+        <v>4.6300000000000001E-2</v>
+      </c>
+      <c r="H6">
+        <v>6.08E-2</v>
+      </c>
+      <c r="I6">
+        <v>7.5399999999999995E-2</v>
+      </c>
+      <c r="J6">
+        <v>9.01E-2</v>
+      </c>
+      <c r="K6">
+        <v>0.1053</v>
+      </c>
+      <c r="L6">
+        <v>0.1196</v>
+      </c>
+      <c r="M6">
+        <v>0.13450000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C7">
+        <v>2.5499999999999998E-2</v>
+      </c>
+      <c r="D7">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="E7">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="F7">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="G7">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="H7">
+        <v>4.4600000000000001E-2</v>
+      </c>
+      <c r="I7">
+        <v>5.62E-2</v>
+      </c>
+      <c r="J7">
+        <v>6.8099999999999994E-2</v>
+      </c>
+      <c r="K7">
+        <v>8.0100000000000005E-2</v>
+      </c>
+      <c r="L7">
+        <v>9.2200000000000004E-2</v>
+      </c>
+      <c r="M7">
+        <v>0.1043</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E8">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="F8">
+        <v>2.41E-2</v>
+      </c>
+      <c r="G8">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="H8">
+        <v>5.2699999999999997E-2</v>
+      </c>
+      <c r="I8">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="J8">
+        <v>7.9399999999999998E-2</v>
+      </c>
+      <c r="K8">
+        <v>9.0800000000000006E-2</v>
+      </c>
+      <c r="L8">
+        <v>0.1036</v>
+      </c>
+      <c r="M8">
+        <v>0.1168</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>1.34E-2</v>
+      </c>
+      <c r="E9">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="F9">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="G9">
+        <v>4.99E-2</v>
+      </c>
+      <c r="H9">
+        <v>6.3E-2</v>
+      </c>
+      <c r="I9">
+        <v>7.9500000000000001E-2</v>
+      </c>
+      <c r="J9">
+        <v>9.0499999999999997E-2</v>
+      </c>
+      <c r="K9">
+        <v>0.1048</v>
+      </c>
+      <c r="L9">
+        <v>0.1193</v>
+      </c>
+      <c r="M9">
+        <v>0.13400000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>9.1000000000000004E-3</v>
+      </c>
+      <c r="E10">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="F10">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="G10">
+        <v>6.0400000000000002E-2</v>
+      </c>
+      <c r="H10">
+        <v>7.5200000000000003E-2</v>
+      </c>
+      <c r="I10">
+        <v>8.9700000000000002E-2</v>
+      </c>
+      <c r="J10">
+        <v>0.1048</v>
+      </c>
+      <c r="K10">
+        <v>0.12180000000000001</v>
+      </c>
+      <c r="L10">
+        <v>0.13980000000000001</v>
+      </c>
+      <c r="M10">
+        <v>0.1578</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="E11">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="F11">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="G11">
+        <v>6.6799999999999998E-2</v>
+      </c>
+      <c r="H11">
+        <v>8.9800000000000005E-2</v>
+      </c>
+      <c r="I11">
+        <v>0.10680000000000001</v>
+      </c>
+      <c r="J11">
+        <v>0.12659999999999999</v>
+      </c>
+      <c r="K11">
+        <v>0.1515</v>
+      </c>
+      <c r="L11">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="M11">
+        <v>0.19769999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="E12">
+        <v>3.39E-2</v>
+      </c>
+      <c r="F12">
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="G12">
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="H12">
+        <v>9.69E-2</v>
+      </c>
+      <c r="I12">
+        <v>0.1237</v>
+      </c>
+      <c r="J12">
+        <v>0.14729999999999999</v>
+      </c>
+      <c r="K12">
+        <v>0.17249999999999999</v>
+      </c>
+      <c r="L12">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="M12">
+        <v>0.22700000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="F13">
+        <v>4.87E-2</v>
+      </c>
+      <c r="G13">
+        <v>7.7600000000000002E-2</v>
+      </c>
+      <c r="H13">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="I13">
+        <v>0.1288</v>
+      </c>
+      <c r="J13">
+        <v>0.1527</v>
+      </c>
+      <c r="K13">
+        <v>0.18079999999999999</v>
+      </c>
+      <c r="L13">
+        <v>0.20830000000000001</v>
+      </c>
+      <c r="M13">
+        <v>0.23849999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <v>0.06</v>
+      </c>
+      <c r="F14">
+        <v>5.6399999999999999E-2</v>
+      </c>
+      <c r="G14">
+        <v>8.8400000000000006E-2</v>
+      </c>
+      <c r="H14">
+        <v>0.10929999999999999</v>
+      </c>
+      <c r="I14">
+        <v>0.1326</v>
+      </c>
+      <c r="J14">
+        <v>0.15629999999999999</v>
+      </c>
+      <c r="K14">
+        <v>0.1825</v>
+      </c>
+      <c r="L14">
+        <v>0.2112</v>
+      </c>
+      <c r="M14">
+        <v>0.2364</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>9.4399999999999998E-2</v>
+      </c>
+      <c r="G15">
+        <v>0.10589999999999999</v>
+      </c>
+      <c r="H15">
+        <v>0.1227</v>
+      </c>
+      <c r="I15">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="J15">
+        <v>0.1638</v>
+      </c>
+      <c r="K15">
+        <v>0.18820000000000001</v>
+      </c>
+      <c r="L15">
+        <v>0.21440000000000001</v>
+      </c>
+      <c r="M15">
+        <v>0.2402</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>0.14130000000000001</v>
+      </c>
+      <c r="H16">
+        <v>0.14530000000000001</v>
+      </c>
+      <c r="I16">
+        <v>0.15890000000000001</v>
+      </c>
+      <c r="J16">
+        <v>0.17630000000000001</v>
+      </c>
+      <c r="K16">
+        <v>0.19750000000000001</v>
+      </c>
+      <c r="L16">
+        <v>0.2225</v>
+      </c>
+      <c r="M16">
+        <v>0.24809999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="2:28" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0.2</v>
+      </c>
+      <c r="E19">
+        <v>0.4</v>
+      </c>
+      <c r="F19">
+        <v>0.6</v>
+      </c>
+      <c r="G19">
+        <v>0.8</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1.2</v>
+      </c>
+      <c r="J19">
+        <v>1.4</v>
+      </c>
+      <c r="K19">
+        <v>1.6</v>
+      </c>
+      <c r="L19">
+        <v>1.8</v>
+      </c>
+      <c r="M19">
+        <v>2</v>
+      </c>
+      <c r="N19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="O19">
+        <v>2.4</v>
+      </c>
+      <c r="P19">
+        <v>2.6</v>
+      </c>
+      <c r="Q19">
+        <v>2.8</v>
+      </c>
+      <c r="R19">
+        <v>3</v>
+      </c>
+      <c r="S19">
+        <v>3.2</v>
+      </c>
+      <c r="T19">
+        <v>3.4</v>
+      </c>
+      <c r="U19">
+        <v>3.6</v>
+      </c>
+      <c r="V19">
+        <v>3.8</v>
+      </c>
+      <c r="W19">
+        <v>4</v>
+      </c>
+      <c r="X19">
+        <v>4.2</v>
+      </c>
+      <c r="Y19">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Z19">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AA19">
+        <v>4.8</v>
+      </c>
+      <c r="AB19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>0.7</v>
+      </c>
+      <c r="C20">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="D20">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="E20">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="F20">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="G20">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="H20">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="I20">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="J20">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="K20">
+        <v>6.1100000000000002E-2</v>
+      </c>
+      <c r="L20">
+        <v>6.9500000000000006E-2</v>
+      </c>
+      <c r="M20">
+        <v>7.8200000000000006E-2</v>
+      </c>
+      <c r="N20">
+        <v>8.6900000000000005E-2</v>
+      </c>
+      <c r="O20">
+        <v>9.5699999999999993E-2</v>
+      </c>
+      <c r="P20">
+        <v>0.1043</v>
+      </c>
+      <c r="Q20">
+        <v>0.11749999999999999</v>
+      </c>
+      <c r="R20">
+        <v>0.12180000000000001</v>
+      </c>
+      <c r="S20">
+        <v>0.1305</v>
+      </c>
+      <c r="T20" t="s">
+        <v>18</v>
+      </c>
+      <c r="U20">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="V20">
+        <v>0.15670000000000001</v>
+      </c>
+      <c r="W20">
+        <v>0.16539999999999999</v>
+      </c>
+      <c r="X20">
+        <v>0.17530000000000001</v>
+      </c>
+      <c r="Y20">
+        <v>0.18379999999999999</v>
+      </c>
+      <c r="Z20">
+        <v>0.1923</v>
+      </c>
+      <c r="AA20">
+        <v>0.20030000000000001</v>
+      </c>
+      <c r="AB20">
+        <v>0.20910000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>0.8</v>
+      </c>
+      <c r="C21">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="D21">
+        <v>3.8E-3</v>
+      </c>
+      <c r="E21">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="F21">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="G21">
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="H21">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="I21">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="J21">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="K21">
+        <v>4.7199999999999999E-2</v>
+      </c>
+      <c r="L21">
+        <v>5.4399999999999997E-2</v>
+      </c>
+      <c r="M21">
+        <v>6.1499999999999999E-2</v>
+      </c>
+      <c r="N21">
+        <v>6.8699999999999997E-2</v>
+      </c>
+      <c r="O21">
+        <v>7.6100000000000001E-2</v>
+      </c>
+      <c r="P21">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="Q21">
+        <v>9.0200000000000002E-2</v>
+      </c>
+      <c r="R21">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="S21">
+        <v>0.1046</v>
+      </c>
+      <c r="T21">
+        <v>0.1119</v>
+      </c>
+      <c r="U21">
+        <v>0.1191</v>
+      </c>
+      <c r="V21">
+        <v>0.1263</v>
+      </c>
+      <c r="W21">
+        <v>0.13350000000000001</v>
+      </c>
+      <c r="X21">
+        <v>0.1419</v>
+      </c>
+      <c r="Y21">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="Z21">
+        <v>0.15590000000000001</v>
+      </c>
+      <c r="AA21">
+        <v>0.16289999999999999</v>
+      </c>
+      <c r="AB21">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>0.9</v>
+      </c>
+      <c r="C22">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="D22">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="E22">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="F22">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="G22">
+        <v>1.23E-2</v>
+      </c>
+      <c r="H22">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="I22">
+        <v>2.35E-2</v>
+      </c>
+      <c r="J22">
+        <v>2.92E-2</v>
+      </c>
+      <c r="K22">
+        <v>3.49E-2</v>
+      </c>
+      <c r="L22">
+        <v>4.0599999999999997E-2</v>
+      </c>
+      <c r="M22">
+        <v>4.6399999999999997E-2</v>
+      </c>
+      <c r="N22">
+        <v>5.21E-2</v>
+      </c>
+      <c r="O22">
+        <v>5.79E-2</v>
+      </c>
+      <c r="P22">
+        <v>6.3700000000000007E-2</v>
+      </c>
+      <c r="Q22">
+        <v>6.9699999999999998E-2</v>
+      </c>
+      <c r="R22">
+        <v>7.5399999999999995E-2</v>
+      </c>
+      <c r="S22">
+        <v>8.1299999999999997E-2</v>
+      </c>
+      <c r="T22">
+        <v>8.7099999999999997E-2</v>
+      </c>
+      <c r="U22">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="V22">
+        <v>9.8900000000000002E-2</v>
+      </c>
+      <c r="W22">
+        <v>0.105</v>
+      </c>
+      <c r="X22">
+        <v>0.1109</v>
+      </c>
+      <c r="Y22">
+        <v>0.1167</v>
+      </c>
+      <c r="Z22">
+        <v>0.1226</v>
+      </c>
+      <c r="AA22">
+        <v>0.1305</v>
+      </c>
+      <c r="AB22">
+        <v>0.1346</v>
+      </c>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="D23">
+        <v>2.8E-3</v>
+      </c>
+      <c r="E23">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="F23">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G23">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H23">
+        <v>2.3E-3</v>
+      </c>
+      <c r="I23">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="J23">
+        <v>5.3E-3</v>
+      </c>
+      <c r="K23">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="L23">
+        <v>1.9300000000000001E-2</v>
+      </c>
+      <c r="M23">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="N23">
+        <v>1.2E-2</v>
+      </c>
+      <c r="O23">
+        <v>7.6E-3</v>
+      </c>
+      <c r="P23">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="Q23">
+        <v>4.8599999999999997E-2</v>
+      </c>
+      <c r="R23">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="S23">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="T23">
+        <v>6.5699999999999995E-2</v>
+      </c>
+      <c r="U23">
+        <v>7.0499999999999993E-2</v>
+      </c>
+      <c r="V23">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="W23">
+        <v>8.0100000000000005E-2</v>
+      </c>
+      <c r="X23">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="Y23">
+        <v>8.9899999999999994E-2</v>
+      </c>
+      <c r="Z23">
+        <v>9.4600000000000004E-2</v>
+      </c>
+      <c r="AA23">
+        <v>9.9699999999999997E-2</v>
+      </c>
+      <c r="AB23">
+        <v>0.1043</v>
+      </c>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="E24">
+        <v>6.3E-3</v>
+      </c>
+      <c r="F24">
+        <v>3.3E-3</v>
+      </c>
+      <c r="G24">
+        <v>6.6E-3</v>
+      </c>
+      <c r="H24">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="I24">
+        <v>1.8100000000000002E-2</v>
+      </c>
+      <c r="J24">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="K24">
+        <v>2.5100000000000001E-2</v>
+      </c>
+      <c r="L24">
+        <v>3.61E-2</v>
+      </c>
+      <c r="M24">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="N24">
+        <v>4.5600000000000002E-2</v>
+      </c>
+      <c r="O24">
+        <v>5.0299999999999997E-2</v>
+      </c>
+      <c r="P24">
+        <v>5.6500000000000002E-2</v>
+      </c>
+      <c r="Q24">
+        <v>6.0199999999999997E-2</v>
+      </c>
+      <c r="R24">
+        <v>6.5199999999999994E-2</v>
+      </c>
+      <c r="S24">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="T24">
+        <v>7.51E-2</v>
+      </c>
+      <c r="U24">
+        <v>8.0199999999999994E-2</v>
+      </c>
+      <c r="V24">
+        <v>8.5500000000000007E-2</v>
+      </c>
+      <c r="W24">
+        <v>9.0499999999999997E-2</v>
+      </c>
+      <c r="X24">
+        <v>9.5799999999999996E-2</v>
+      </c>
+      <c r="Y24">
+        <v>0.1009</v>
+      </c>
+      <c r="Z24">
+        <v>0.1062</v>
+      </c>
+      <c r="AA24">
+        <v>0.1116</v>
+      </c>
+      <c r="AB24">
+        <v>0.1168</v>
+      </c>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>1.2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="E25">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="F25">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="G25">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="H25">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="I25">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="J25">
+        <v>2.75E-2</v>
+      </c>
+      <c r="K25">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="L25">
+        <v>4.5600000000000002E-2</v>
+      </c>
+      <c r="M25">
+        <v>5.1499999999999997E-2</v>
+      </c>
+      <c r="N25">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="O25">
+        <v>6.2899999999999998E-2</v>
+      </c>
+      <c r="P25">
+        <v>6.5699999999999995E-2</v>
+      </c>
+      <c r="Q25">
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="R25">
+        <v>7.6600000000000001E-2</v>
+      </c>
+      <c r="S25">
+        <v>8.2400000000000001E-2</v>
+      </c>
+      <c r="T25">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="U25">
+        <v>9.3399999999999997E-2</v>
+      </c>
+      <c r="V25">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="W25">
+        <v>0.1048</v>
+      </c>
+      <c r="X25">
+        <v>0.1105</v>
+      </c>
+      <c r="Y25">
+        <v>0.1163</v>
+      </c>
+      <c r="Z25">
+        <v>0.12230000000000001</v>
+      </c>
+      <c r="AA25">
+        <v>0.12809999999999999</v>
+      </c>
+      <c r="AB25">
+        <v>0.13400000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>1.3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26">
+        <v>2.5100000000000001E-2</v>
+      </c>
+      <c r="F26">
+        <v>1.12E-2</v>
+      </c>
+      <c r="G26">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="H26">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="I26">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="J26">
+        <v>3.1899999999999998E-2</v>
+      </c>
+      <c r="K26">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="L26">
+        <v>5.0900000000000001E-2</v>
+      </c>
+      <c r="M26">
+        <v>6.0900000000000003E-2</v>
+      </c>
+      <c r="N26">
+        <v>6.8500000000000005E-2</v>
+      </c>
+      <c r="O26">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="P26">
+        <v>7.7299999999999994E-2</v>
+      </c>
+      <c r="Q26">
+        <v>9.0700000000000003E-2</v>
+      </c>
+      <c r="R26">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="S26">
+        <v>9.5200000000000007E-2</v>
+      </c>
+      <c r="T26">
+        <v>0.10150000000000001</v>
+      </c>
+      <c r="U26">
+        <v>0.1113</v>
+      </c>
+      <c r="V26">
+        <v>0.1197</v>
+      </c>
+      <c r="W26">
+        <v>0.1203</v>
+      </c>
+      <c r="X26">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="Y26">
+        <v>0.1356</v>
+      </c>
+      <c r="Z26">
+        <v>0.14080000000000001</v>
+      </c>
+      <c r="AA26">
+        <v>0.1489</v>
+      </c>
+      <c r="AB26">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>1.4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27">
+        <v>3.15E-2</v>
+      </c>
+      <c r="F27">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="G27">
+        <v>1.49E-2</v>
+      </c>
+      <c r="H27">
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="I27">
+        <v>3.1300000000000001E-2</v>
+      </c>
+      <c r="J27">
+        <v>3.8600000000000002E-2</v>
+      </c>
+      <c r="K27">
+        <v>4.7100000000000003E-2</v>
+      </c>
+      <c r="L27">
+        <v>5.6500000000000002E-2</v>
+      </c>
+      <c r="M27">
+        <v>6.6900000000000001E-2</v>
+      </c>
+      <c r="N27">
+        <v>7.7899999999999997E-2</v>
+      </c>
+      <c r="O27">
+        <v>8.5400000000000004E-2</v>
+      </c>
+      <c r="P27">
+        <v>9.4200000000000006E-2</v>
+      </c>
+      <c r="Q27">
+        <v>0.10150000000000001</v>
+      </c>
+      <c r="R27">
+        <v>0.1072</v>
+      </c>
+      <c r="S27">
+        <v>0.11559999999999999</v>
+      </c>
+      <c r="T27">
+        <v>0.1236</v>
+      </c>
+      <c r="U27">
+        <v>0.1308</v>
+      </c>
+      <c r="V27">
+        <v>0.14169999999999999</v>
+      </c>
+      <c r="W27">
+        <v>0.1515</v>
+      </c>
+      <c r="X27">
+        <v>0.161</v>
+      </c>
+      <c r="Y27">
+        <v>0.16889999999999999</v>
+      </c>
+      <c r="Z27">
+        <v>0.1888</v>
+      </c>
+      <c r="AA27">
+        <v>0.19070000000000001</v>
+      </c>
+      <c r="AB27">
+        <v>0.19639999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>1.5</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="G28">
+        <v>3.1899999999999998E-2</v>
+      </c>
+      <c r="H28">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="I28">
+        <v>3.32E-2</v>
+      </c>
+      <c r="J28">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="K28">
+        <v>5.28E-2</v>
+      </c>
+      <c r="L28">
+        <v>6.1699999999999998E-2</v>
+      </c>
+      <c r="M28">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="N28">
+        <v>8.1299999999999997E-2</v>
+      </c>
+      <c r="O28">
+        <v>9.1800000000000007E-2</v>
+      </c>
+      <c r="P28">
+        <v>0.1022</v>
+      </c>
+      <c r="Q28">
+        <v>0.1132</v>
+      </c>
+      <c r="R28">
+        <v>0.1235</v>
+      </c>
+      <c r="S28">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="T28">
+        <v>0.14219999999999999</v>
+      </c>
+      <c r="U28">
+        <v>0.15290000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.16220000000000001</v>
+      </c>
+      <c r="W28">
+        <v>0.17230000000000001</v>
+      </c>
+      <c r="X28">
+        <v>0.18279999999999999</v>
+      </c>
+      <c r="Y28">
+        <v>0.1938</v>
+      </c>
+      <c r="Z28">
+        <v>0.20569999999999999</v>
+      </c>
+      <c r="AA28">
+        <v>0.2157</v>
+      </c>
+      <c r="AB28">
+        <v>0.22700000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>1.6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="G29">
+        <v>4.24E-2</v>
+      </c>
+      <c r="H29">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="I29">
+        <v>4.8399999999999999E-2</v>
+      </c>
+      <c r="J29">
+        <v>5.4300000000000001E-2</v>
+      </c>
+      <c r="K29">
+        <v>6.13E-2</v>
+      </c>
+      <c r="L29">
+        <v>6.9099999999999995E-2</v>
+      </c>
+      <c r="M29">
+        <v>7.7600000000000002E-2</v>
+      </c>
+      <c r="N29">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="O29">
+        <v>9.6600000000000005E-2</v>
+      </c>
+      <c r="P29">
+        <v>0.10589999999999999</v>
+      </c>
+      <c r="Q29">
+        <v>0.1159</v>
+      </c>
+      <c r="R29">
+        <v>0.12620000000000001</v>
+      </c>
+      <c r="S29">
+        <v>0.13669999999999999</v>
+      </c>
+      <c r="T29">
+        <v>0.1489</v>
+      </c>
+      <c r="U29">
+        <v>0.1585</v>
+      </c>
+      <c r="V29">
+        <v>0.16919999999999999</v>
+      </c>
+      <c r="W29">
+        <v>0.18</v>
+      </c>
+      <c r="X29">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="Y29">
+        <v>0.2031</v>
+      </c>
+      <c r="Z29">
+        <v>0.21640000000000001</v>
+      </c>
+      <c r="AA29">
+        <v>0.2261</v>
+      </c>
+      <c r="AB29">
+        <v>0.23780000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>1.7</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30">
+        <v>5.96E-2</v>
+      </c>
+      <c r="H30">
+        <v>0.06</v>
+      </c>
+      <c r="I30">
+        <v>6.3200000000000006E-2</v>
+      </c>
+      <c r="J30">
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="K30">
+        <v>7.4200000000000002E-2</v>
+      </c>
+      <c r="L30">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="M30">
+        <v>8.8499999999999995E-2</v>
+      </c>
+      <c r="N30">
+        <v>9.64E-2</v>
+      </c>
+      <c r="O30">
+        <v>0.10489999999999999</v>
+      </c>
+      <c r="P30">
+        <v>0.1135</v>
+      </c>
+      <c r="Q30">
+        <v>0.1225</v>
+      </c>
+      <c r="R30">
+        <v>0.1331</v>
+      </c>
+      <c r="S30">
+        <v>0.1419</v>
+      </c>
+      <c r="T30">
+        <v>0.15129999999999999</v>
+      </c>
+      <c r="U30">
+        <v>0.16139999999999999</v>
+      </c>
+      <c r="V30">
+        <v>0.1716</v>
+      </c>
+      <c r="W30">
+        <v>0.18310000000000001</v>
+      </c>
+      <c r="X30">
+        <v>0.1928</v>
+      </c>
+      <c r="Y30">
+        <v>0.20349999999999999</v>
+      </c>
+      <c r="Z30">
+        <v>0.216</v>
+      </c>
+      <c r="AA30">
+        <v>0.2281</v>
+      </c>
+      <c r="AB30">
+        <v>0.2364</v>
+      </c>
+    </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>1.8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31">
+        <v>9.3200000000000005E-2</v>
+      </c>
+      <c r="J31">
+        <v>9.3399999999999997E-2</v>
+      </c>
+      <c r="K31">
+        <v>9.5799999999999996E-2</v>
+      </c>
+      <c r="L31">
+        <v>0.1004</v>
+      </c>
+      <c r="M31">
+        <v>0.106</v>
+      </c>
+      <c r="N31">
+        <v>0.11219999999999999</v>
+      </c>
+      <c r="O31">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="P31">
+        <v>0.1265</v>
+      </c>
+      <c r="Q31">
+        <v>0.1341</v>
+      </c>
+      <c r="R31">
+        <v>0.14230000000000001</v>
+      </c>
+      <c r="S31">
+        <v>0.15090000000000001</v>
+      </c>
+      <c r="T31">
+        <v>0.15920000000000001</v>
+      </c>
+      <c r="U31">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="V31">
+        <v>0.17810000000000001</v>
+      </c>
+      <c r="W31">
+        <v>0.1885</v>
+      </c>
+      <c r="X31">
+        <v>0.19839999999999999</v>
+      </c>
+      <c r="Y31">
+        <v>0.2087</v>
+      </c>
+      <c r="Z31">
+        <v>0.21909999999999999</v>
+      </c>
+      <c r="AA31">
+        <v>0.22969999999999999</v>
+      </c>
+      <c r="AB31">
+        <v>0.2429</v>
+      </c>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>1.9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" t="s">
+        <v>10</v>
+      </c>
+      <c r="J32" t="s">
+        <v>10</v>
+      </c>
+      <c r="K32" t="s">
+        <v>10</v>
+      </c>
+      <c r="L32">
+        <v>0.14649999999999999</v>
+      </c>
+      <c r="M32">
+        <v>0.1414</v>
+      </c>
+      <c r="N32">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="O32">
+        <v>0.1452</v>
+      </c>
+      <c r="P32">
+        <v>0.1484</v>
+      </c>
+      <c r="Q32">
+        <v>0.1532</v>
+      </c>
+      <c r="R32">
+        <v>0.1588</v>
+      </c>
+      <c r="S32">
+        <v>0.16830000000000001</v>
+      </c>
+      <c r="T32">
+        <v>0.17180000000000001</v>
+      </c>
+      <c r="U32">
+        <v>0.1799</v>
+      </c>
+      <c r="V32">
+        <v>0.1883</v>
+      </c>
+      <c r="W32">
+        <v>0.1976</v>
+      </c>
+      <c r="X32">
+        <v>0.2074</v>
+      </c>
+      <c r="Y32">
+        <v>0.21829999999999999</v>
+      </c>
+      <c r="Z32">
+        <v>0.22989999999999999</v>
+      </c>
+      <c r="AA32">
+        <v>0.23769999999999999</v>
+      </c>
+      <c r="AB32">
+        <v>0.24859999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/files/Controller Design/ZNMethods_ITAE_Errors.xlsx
+++ b/files/Controller Design/ZNMethods_ITAE_Errors.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulisboa-my.sharepoint.com/personal/ist1100262_tecnico_ulisboa_pt/Documents/MEMec/Thesis/files/Controller Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="8_{95F32091-D855-4402-ADD3-8991BE5FE270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{367E1D4A-7834-4649-B229-0E4FB1D0DB96}"/>
+  <xr:revisionPtr revIDLastSave="185" documentId="8_{95F32091-D855-4402-ADD3-8991BE5FE270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26216FB3-8594-41EA-B495-AA1D8894687A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" activeTab="1" xr2:uid="{6BCB78A0-0C46-4270-8084-079A19E30873}"/>
+    <workbookView xWindow="-3696" yWindow="-17388" windowWidth="30936" windowHeight="17496" activeTab="3" xr2:uid="{6BCB78A0-0C46-4270-8084-079A19E30873}"/>
   </bookViews>
   <sheets>
     <sheet name="CritGain" sheetId="1" r:id="rId1"/>
     <sheet name="PID_Models" sheetId="3" r:id="rId2"/>
     <sheet name="Gains" sheetId="5" r:id="rId3"/>
+    <sheet name="PID_Models_Noise" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="663">
   <si>
     <t>ν/ζ</t>
   </si>
@@ -2024,13 +2025,19 @@
   </si>
   <si>
     <t>1.5865</t>
+  </si>
+  <si>
+    <t>NOTE</t>
+  </si>
+  <si>
+    <t>Simulations kept over 30 seconds</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2054,6 +2061,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2456,7 +2470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -2513,6 +2527,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2905,15 +2920,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E4CF69-D65E-4E98-B411-A1D521930B25}">
   <dimension ref="B1:P43"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" customWidth="1"/>
-    <col min="2" max="2" width="5.90625" customWidth="1"/>
-    <col min="3" max="12" width="7.6328125" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" customWidth="1"/>
+    <col min="3" max="12" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="33" t="s">
         <v>2</v>
       </c>
@@ -2921,7 +2936,7 @@
       <c r="D2" s="34"/>
       <c r="E2" s="35"/>
     </row>
-    <row r="3" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="30" t="s">
         <v>9</v>
       </c>
@@ -2929,15 +2944,15 @@
       <c r="D3" s="31"/>
       <c r="E3" s="32"/>
     </row>
-    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="30" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="32"/>
     </row>
-    <row r="7" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="20" t="s">
         <v>0</v>
       </c>
@@ -2978,7 +2993,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="13">
         <v>0.5</v>
       </c>
@@ -3020,7 +3035,7 @@
         <v>13.904676086956519</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
         <v>0.7</v>
       </c>
@@ -3062,7 +3077,7 @@
         <v>2.8556499999999998</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
         <v>0.9</v>
       </c>
@@ -3104,7 +3119,7 @@
         <v>111.7454</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <v>1.1000000000000001</v>
       </c>
@@ -3146,7 +3161,7 @@
         <v>0.1535</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <v>1.3</v>
       </c>
@@ -3183,7 +3198,7 @@
       <c r="M12" s="4"/>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <v>1.5</v>
       </c>
@@ -3220,7 +3235,7 @@
       <c r="M13" s="4"/>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <v>1.7</v>
       </c>
@@ -3257,7 +3272,7 @@
       <c r="M14" s="4"/>
       <c r="N14" s="5"/>
     </row>
-    <row r="15" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24">
         <v>1.9</v>
       </c>
@@ -3294,7 +3309,7 @@
       <c r="M15" s="6"/>
       <c r="N15" s="8"/>
     </row>
-    <row r="16" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="25" t="s">
         <v>11</v>
       </c>
@@ -3311,15 +3326,15 @@
       <c r="M16" s="26"/>
       <c r="N16" s="27"/>
     </row>
-    <row r="18" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="19" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="30" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="31"/>
       <c r="D19" s="32"/>
     </row>
-    <row r="20" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="20" t="s">
         <v>0</v>
       </c>
@@ -3360,7 +3375,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B21" s="13">
         <v>0.5</v>
       </c>
@@ -3402,7 +3417,7 @@
         <v>9.6706896551724139E-2</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B22" s="11">
         <v>0.7</v>
       </c>
@@ -3444,7 +3459,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B23" s="11">
         <v>0.9</v>
       </c>
@@ -3486,7 +3501,7 @@
         <v>0.65229999999999999</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" s="11">
         <v>1.1000000000000001</v>
       </c>
@@ -3528,7 +3543,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B25" s="11">
         <v>1.3</v>
       </c>
@@ -3565,7 +3580,7 @@
       <c r="M25" s="4"/>
       <c r="N25" s="5"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B26" s="11">
         <v>1.5</v>
       </c>
@@ -3602,7 +3617,7 @@
       <c r="M26" s="4"/>
       <c r="N26" s="5"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B27" s="11">
         <v>1.7</v>
       </c>
@@ -3639,7 +3654,7 @@
       <c r="M27" s="4"/>
       <c r="N27" s="5"/>
     </row>
-    <row r="28" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="12">
         <v>1.9</v>
       </c>
@@ -3676,7 +3691,7 @@
       <c r="M28" s="6"/>
       <c r="N28" s="8"/>
     </row>
-    <row r="29" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="25" t="s">
         <v>12</v>
       </c>
@@ -3693,15 +3708,15 @@
       <c r="M29" s="26"/>
       <c r="N29" s="27"/>
     </row>
-    <row r="31" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="32" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="31"/>
       <c r="D32" s="32"/>
     </row>
-    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="20" t="s">
         <v>0</v>
       </c>
@@ -3748,7 +3763,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B34" s="13">
         <v>0.5</v>
       </c>
@@ -3796,7 +3811,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="11">
         <v>0.7</v>
       </c>
@@ -3838,7 +3853,7 @@
         <v>0.10395</v>
       </c>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="11">
         <v>0.9</v>
       </c>
@@ -3880,7 +3895,7 @@
         <v>0.30299999999999999</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="11">
         <v>1.1000000000000001</v>
       </c>
@@ -3922,7 +3937,7 @@
         <v>2.3999999999999998E-3</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="11">
         <v>1.3</v>
       </c>
@@ -3959,7 +3974,7 @@
       <c r="M38" s="4"/>
       <c r="N38" s="5"/>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="11">
         <v>1.5</v>
       </c>
@@ -3996,7 +4011,7 @@
       <c r="M39" s="4"/>
       <c r="N39" s="5"/>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B40" s="11">
         <v>1.7</v>
       </c>
@@ -4033,7 +4048,7 @@
       <c r="M40" s="4"/>
       <c r="N40" s="5"/>
     </row>
-    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="12">
         <v>1.9</v>
       </c>
@@ -4070,7 +4085,7 @@
       <c r="M41" s="6"/>
       <c r="N41" s="8"/>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="25" t="s">
         <v>12</v>
       </c>
@@ -4087,7 +4102,7 @@
       <c r="M42" s="26"/>
       <c r="N42" s="27"/>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>25</v>
       </c>
@@ -4194,13 +4209,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6B8581E-0797-42DF-A936-58B89916A70A}">
   <dimension ref="B1:BP51"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="51" width="5.90625" customWidth="1"/>
+    <col min="3" max="51" width="5.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:68" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="2:68" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:68" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:68" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="20" t="s">
         <v>0</v>
       </c>
@@ -4397,7 +4412,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="3" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B3" s="1">
         <v>0.6</v>
       </c>
@@ -4594,7 +4609,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>0.7</v>
       </c>
@@ -4791,7 +4806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>0.8</v>
       </c>
@@ -4988,7 +5003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>0.9</v>
       </c>
@@ -5185,7 +5200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>1</v>
       </c>
@@ -5382,7 +5397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>1.1000000000000001</v>
       </c>
@@ -5579,7 +5594,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>1.2</v>
       </c>
@@ -5776,7 +5791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>1.3</v>
       </c>
@@ -5973,7 +5988,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>1.4</v>
       </c>
@@ -6170,7 +6185,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>1.5</v>
       </c>
@@ -6367,7 +6382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>1.6</v>
       </c>
@@ -6564,7 +6579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>1.7</v>
       </c>
@@ -6761,7 +6776,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>1.8</v>
       </c>
@@ -6958,7 +6973,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>1.9</v>
       </c>
@@ -7155,7 +7170,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:68" x14ac:dyDescent="0.3">
       <c r="BB17" s="1">
         <v>1.6</v>
       </c>
@@ -7202,7 +7217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:68" x14ac:dyDescent="0.3">
       <c r="BB18" s="1">
         <v>1.7</v>
       </c>
@@ -7249,7 +7264,7 @@
         <v>18.8813</v>
       </c>
     </row>
-    <row r="19" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>24</v>
       </c>
@@ -7299,7 +7314,7 @@
         <v>16.979299999999999</v>
       </c>
     </row>
-    <row r="20" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:68" x14ac:dyDescent="0.3">
       <c r="BB20" s="1">
         <v>1.9</v>
       </c>
@@ -7346,7 +7361,7 @@
         <v>15.0428</v>
       </c>
     </row>
-    <row r="21" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:68" x14ac:dyDescent="0.3">
       <c r="BB21" s="1">
         <v>2</v>
       </c>
@@ -7393,7 +7408,7 @@
         <v>13.154400000000001</v>
       </c>
     </row>
-    <row r="22" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:68" x14ac:dyDescent="0.3">
       <c r="BB22" s="1">
         <v>2.1</v>
       </c>
@@ -7440,7 +7455,7 @@
         <v>11.366099999999999</v>
       </c>
     </row>
-    <row r="23" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:68" x14ac:dyDescent="0.3">
       <c r="BB23" s="1">
         <v>2.2000000000000002</v>
       </c>
@@ -7487,7 +7502,7 @@
         <v>9.7006999999999994</v>
       </c>
     </row>
-    <row r="24" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:68" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>283</v>
       </c>
@@ -7681,7 +7696,7 @@
         <v>8.1714000000000002</v>
       </c>
     </row>
-    <row r="25" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:68" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>304</v>
       </c>
@@ -7875,7 +7890,7 @@
         <v>6.7784000000000004</v>
       </c>
     </row>
-    <row r="26" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:68" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>315</v>
       </c>
@@ -8069,7 +8084,7 @@
         <v>5.5202999999999998</v>
       </c>
     </row>
-    <row r="27" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:68" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>339</v>
       </c>
@@ -8263,7 +8278,7 @@
         <v>4.3936999999999999</v>
       </c>
     </row>
-    <row r="28" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:68" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>354</v>
       </c>
@@ -8457,7 +8472,7 @@
         <v>3.3972000000000002</v>
       </c>
     </row>
-    <row r="29" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:68" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
         <v>360</v>
       </c>
@@ -8651,7 +8666,7 @@
         <v>2.5360999999999998</v>
       </c>
     </row>
-    <row r="30" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:68" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
         <v>389</v>
       </c>
@@ -8845,7 +8860,7 @@
         <v>1.8302</v>
       </c>
     </row>
-    <row r="31" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:68" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
         <v>10</v>
       </c>
@@ -9039,7 +9054,7 @@
         <v>1.3324</v>
       </c>
     </row>
-    <row r="32" spans="2:68" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:68" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>10</v>
       </c>
@@ -9233,7 +9248,7 @@
         <v>1.1324000000000001</v>
       </c>
     </row>
-    <row r="33" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:68" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>10</v>
       </c>
@@ -9427,7 +9442,7 @@
         <v>1.2544</v>
       </c>
     </row>
-    <row r="34" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:68" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>10</v>
       </c>
@@ -9621,7 +9636,7 @@
         <v>1.5032000000000001</v>
       </c>
     </row>
-    <row r="35" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:68" x14ac:dyDescent="0.3">
       <c r="C35" t="s">
         <v>10</v>
       </c>
@@ -9815,7 +9830,7 @@
         <v>1.7546999999999999</v>
       </c>
     </row>
-    <row r="36" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:68" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>10</v>
       </c>
@@ -10009,7 +10024,7 @@
         <v>1.9636</v>
       </c>
     </row>
-    <row r="37" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:68" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>10</v>
       </c>
@@ -10203,7 +10218,7 @@
         <v>2.1153</v>
       </c>
     </row>
-    <row r="38" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:68" x14ac:dyDescent="0.3">
       <c r="BB38" s="1">
         <v>3.7</v>
       </c>
@@ -10250,7 +10265,7 @@
         <v>2.2073999999999998</v>
       </c>
     </row>
-    <row r="39" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:68" x14ac:dyDescent="0.3">
       <c r="BB39" s="1">
         <v>3.8</v>
       </c>
@@ -10297,7 +10312,7 @@
         <v>2.2433999999999998</v>
       </c>
     </row>
-    <row r="40" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:68" x14ac:dyDescent="0.3">
       <c r="BB40" s="1">
         <v>3.9</v>
       </c>
@@ -10344,7 +10359,7 @@
         <v>2.2296</v>
       </c>
     </row>
-    <row r="41" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:68" x14ac:dyDescent="0.3">
       <c r="BB41" s="1">
         <v>4</v>
       </c>
@@ -10391,7 +10406,7 @@
         <v>2.1762000000000001</v>
       </c>
     </row>
-    <row r="42" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:68" x14ac:dyDescent="0.3">
       <c r="BB42" s="1">
         <v>4.0999999999999996</v>
       </c>
@@ -10438,7 +10453,7 @@
         <v>2.0937000000000001</v>
       </c>
     </row>
-    <row r="43" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:68" x14ac:dyDescent="0.3">
       <c r="BB43" s="1">
         <v>4.2</v>
       </c>
@@ -10485,7 +10500,7 @@
         <v>1.9947999999999999</v>
       </c>
     </row>
-    <row r="44" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:68" x14ac:dyDescent="0.3">
       <c r="BB44" s="1">
         <v>4.3</v>
       </c>
@@ -10532,7 +10547,7 @@
         <v>1.8925000000000001</v>
       </c>
     </row>
-    <row r="45" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="45" spans="3:68" x14ac:dyDescent="0.3">
       <c r="BB45" s="1">
         <v>4.4000000000000004</v>
       </c>
@@ -10579,7 +10594,7 @@
         <v>1.7986</v>
       </c>
     </row>
-    <row r="46" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="46" spans="3:68" x14ac:dyDescent="0.3">
       <c r="BB46" s="1">
         <v>4.5</v>
       </c>
@@ -10626,7 +10641,7 @@
         <v>1.7218</v>
       </c>
     </row>
-    <row r="47" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="47" spans="3:68" x14ac:dyDescent="0.3">
       <c r="BB47" s="1">
         <v>4.5999999999999996</v>
       </c>
@@ -10673,7 +10688,7 @@
         <v>1.6656</v>
       </c>
     </row>
-    <row r="48" spans="3:68" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:68" x14ac:dyDescent="0.3">
       <c r="BB48" s="1">
         <v>4.7</v>
       </c>
@@ -10720,7 +10735,7 @@
         <v>1.6288</v>
       </c>
     </row>
-    <row r="49" spans="54:68" x14ac:dyDescent="0.35">
+    <row r="49" spans="54:68" x14ac:dyDescent="0.3">
       <c r="BB49" s="1">
         <v>4.8</v>
       </c>
@@ -10767,7 +10782,7 @@
         <v>1.6087</v>
       </c>
     </row>
-    <row r="50" spans="54:68" x14ac:dyDescent="0.35">
+    <row r="50" spans="54:68" x14ac:dyDescent="0.3">
       <c r="BB50" s="1">
         <v>4.9000000000000004</v>
       </c>
@@ -10814,7 +10829,7 @@
         <v>1.6042000000000001</v>
       </c>
     </row>
-    <row r="51" spans="54:68" x14ac:dyDescent="0.35">
+    <row r="51" spans="54:68" x14ac:dyDescent="0.3">
       <c r="BB51" s="1">
         <v>5</v>
       </c>
@@ -10894,32 +10909,32 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D68FACB-5B63-4831-A1B2-5F33785D9AB1}">
   <dimension ref="B2:AY81"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="51" width="6.26953125" customWidth="1"/>
+    <col min="3" max="51" width="6.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:51" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:51" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="2:51" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:51" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="2:51" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:51" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="2:51" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:51" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="2:51" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:51" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="20" t="s">
         <v>0</v>
       </c>
@@ -11071,7 +11086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>0.6</v>
       </c>
@@ -11223,7 +11238,7 @@
         <v>48.9788</v>
       </c>
     </row>
-    <row r="12" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>0.7</v>
       </c>
@@ -11375,7 +11390,7 @@
         <v>81.417500000000004</v>
       </c>
     </row>
-    <row r="13" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>0.8</v>
       </c>
@@ -11527,7 +11542,7 @@
         <v>92.267099999999999</v>
       </c>
     </row>
-    <row r="14" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>0.9</v>
       </c>
@@ -11679,7 +11694,7 @@
         <v>81.819000000000003</v>
       </c>
     </row>
-    <row r="15" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>1</v>
       </c>
@@ -11831,7 +11846,7 @@
         <v>63.426099999999998</v>
       </c>
     </row>
-    <row r="16" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>1.1000000000000001</v>
       </c>
@@ -11983,7 +11998,7 @@
         <v>46.739899999999999</v>
       </c>
     </row>
-    <row r="17" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>1.2</v>
       </c>
@@ -12135,7 +12150,7 @@
         <v>34.656199999999998</v>
       </c>
     </row>
-    <row r="18" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>1.3</v>
       </c>
@@ -12287,7 +12302,7 @@
         <v>26.637</v>
       </c>
     </row>
-    <row r="19" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>1.4</v>
       </c>
@@ -12439,7 +12454,7 @@
         <v>21.2818</v>
       </c>
     </row>
-    <row r="20" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B20" s="1">
         <v>1.5</v>
       </c>
@@ -12591,7 +12606,7 @@
         <v>17.2515</v>
       </c>
     </row>
-    <row r="21" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B21" s="1">
         <v>1.6</v>
       </c>
@@ -12743,7 +12758,7 @@
         <v>13.48</v>
       </c>
     </row>
-    <row r="22" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B22" s="1">
         <v>1.7</v>
       </c>
@@ -12895,7 +12910,7 @@
         <v>9.3887999999999998</v>
       </c>
     </row>
-    <row r="23" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B23" s="1">
         <v>1.8</v>
       </c>
@@ -13047,7 +13062,7 @@
         <v>5.2465999999999999</v>
       </c>
     </row>
-    <row r="24" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B24" s="1">
         <v>1.9</v>
       </c>
@@ -13199,15 +13214,15 @@
         <v>2.0608</v>
       </c>
     </row>
-    <row r="25" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="20" t="s">
         <v>0</v>
       </c>
@@ -13359,7 +13374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B30" s="1">
         <v>0.6</v>
       </c>
@@ -13511,7 +13526,7 @@
         <v>4.6848999999999998</v>
       </c>
     </row>
-    <row r="31" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B31" s="1">
         <v>0.7</v>
       </c>
@@ -13663,7 +13678,7 @@
         <v>4.9732000000000003</v>
       </c>
     </row>
-    <row r="32" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B32" s="1">
         <v>0.8</v>
       </c>
@@ -13815,7 +13830,7 @@
         <v>5.3418999999999999</v>
       </c>
     </row>
-    <row r="33" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B33" s="1">
         <v>0.9</v>
       </c>
@@ -13967,7 +13982,7 @@
         <v>5.7504999999999997</v>
       </c>
     </row>
-    <row r="34" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B34" s="1">
         <v>1</v>
       </c>
@@ -14119,7 +14134,7 @@
         <v>6.1510999999999996</v>
       </c>
     </row>
-    <row r="35" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B35" s="1">
         <v>1.1000000000000001</v>
       </c>
@@ -14271,7 +14286,7 @@
         <v>6.4897999999999998</v>
       </c>
     </row>
-    <row r="36" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B36" s="1">
         <v>1.2</v>
       </c>
@@ -14423,7 +14438,7 @@
         <v>6.7114000000000003</v>
       </c>
     </row>
-    <row r="37" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B37" s="1">
         <v>1.3</v>
       </c>
@@ -14575,7 +14590,7 @@
         <v>6.7676999999999996</v>
       </c>
     </row>
-    <row r="38" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B38" s="1">
         <v>1.4</v>
       </c>
@@ -14727,7 +14742,7 @@
         <v>6.6273999999999997</v>
       </c>
     </row>
-    <row r="39" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B39" s="1">
         <v>1.5</v>
       </c>
@@ -14879,7 +14894,7 @@
         <v>6.2840999999999996</v>
       </c>
     </row>
-    <row r="40" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B40" s="1">
         <v>1.6</v>
       </c>
@@ -15031,7 +15046,7 @@
         <v>5.7587999999999999</v>
       </c>
     </row>
-    <row r="41" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B41" s="1">
         <v>1.7</v>
       </c>
@@ -15183,7 +15198,7 @@
         <v>5.0965999999999996</v>
       </c>
     </row>
-    <row r="42" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B42" s="1">
         <v>1.8</v>
       </c>
@@ -15335,7 +15350,7 @@
         <v>4.3577000000000004</v>
       </c>
     </row>
-    <row r="43" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B43" s="1">
         <v>1.9</v>
       </c>
@@ -15487,15 +15502,15 @@
         <v>3.6049000000000002</v>
       </c>
     </row>
-    <row r="44" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="46" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="20" t="s">
         <v>0</v>
       </c>
@@ -15647,7 +15662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B49" s="1">
         <v>0.6</v>
       </c>
@@ -15799,7 +15814,7 @@
         <v>0.216</v>
       </c>
     </row>
-    <row r="50" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B50" s="1">
         <v>0.7</v>
       </c>
@@ -15951,7 +15966,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="51" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B51" s="1">
         <v>0.8</v>
       </c>
@@ -16103,7 +16118,7 @@
         <v>0.71130000000000004</v>
       </c>
     </row>
-    <row r="52" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B52" s="1">
         <v>0.9</v>
       </c>
@@ -16255,7 +16270,7 @@
         <v>2.1046999999999998</v>
       </c>
     </row>
-    <row r="53" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B53" s="1">
         <v>1</v>
       </c>
@@ -16407,7 +16422,7 @@
         <v>6.7112999999999996</v>
       </c>
     </row>
-    <row r="54" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B54" s="1">
         <v>1.1000000000000001</v>
       </c>
@@ -16559,7 +16574,7 @@
         <v>19.967700000000001</v>
       </c>
     </row>
-    <row r="55" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B55" s="1">
         <v>1.2</v>
       </c>
@@ -16711,7 +16726,7 @@
         <v>49.717100000000002</v>
       </c>
     </row>
-    <row r="56" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B56" s="1">
         <v>1.3</v>
       </c>
@@ -16863,7 +16878,7 @@
         <v>96.262900000000002</v>
       </c>
     </row>
-    <row r="57" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B57" s="1">
         <v>1.4</v>
       </c>
@@ -17015,7 +17030,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B58" s="1">
         <v>1.5</v>
       </c>
@@ -17167,7 +17182,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B59" s="1">
         <v>1.6</v>
       </c>
@@ -17319,7 +17334,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B60" s="1">
         <v>1.7</v>
       </c>
@@ -17471,7 +17486,7 @@
         <v>86.854799999999997</v>
       </c>
     </row>
-    <row r="61" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B61" s="1">
         <v>1.8</v>
       </c>
@@ -17623,7 +17638,7 @@
         <v>54.804000000000002</v>
       </c>
     </row>
-    <row r="62" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B62" s="1">
         <v>1.9</v>
       </c>
@@ -17775,15 +17790,15 @@
         <v>36.372300000000003</v>
       </c>
     </row>
-    <row r="63" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="65" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="2:51" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="29" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="20" t="s">
         <v>0</v>
       </c>
@@ -17935,7 +17950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B68" s="1">
         <v>0.6</v>
       </c>
@@ -18087,7 +18102,7 @@
         <v>122.8081</v>
       </c>
     </row>
-    <row r="69" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B69" s="1">
         <v>0.7</v>
       </c>
@@ -18239,7 +18254,7 @@
         <v>92.479100000000003</v>
       </c>
     </row>
-    <row r="70" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B70" s="1">
         <v>0.8</v>
       </c>
@@ -18391,7 +18406,7 @@
         <v>77.405799999999999</v>
       </c>
     </row>
-    <row r="71" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B71" s="1">
         <v>0.9</v>
       </c>
@@ -18543,7 +18558,7 @@
         <v>73.097499999999997</v>
       </c>
     </row>
-    <row r="72" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B72" s="1">
         <v>1</v>
       </c>
@@ -18695,7 +18710,7 @@
         <v>75.684700000000007</v>
       </c>
     </row>
-    <row r="73" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B73" s="1">
         <v>1.1000000000000001</v>
       </c>
@@ -18847,7 +18862,7 @@
         <v>81.919300000000007</v>
       </c>
     </row>
-    <row r="74" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B74" s="1">
         <v>1.2</v>
       </c>
@@ -18999,7 +19014,7 @@
         <v>89.174700000000001</v>
       </c>
     </row>
-    <row r="75" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B75" s="1">
         <v>1.3</v>
       </c>
@@ -19151,7 +19166,7 @@
         <v>95.445499999999996</v>
       </c>
     </row>
-    <row r="76" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B76" s="1">
         <v>1.4</v>
       </c>
@@ -19303,7 +19318,7 @@
         <v>99.347899999999996</v>
       </c>
     </row>
-    <row r="77" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B77" s="1">
         <v>1.5</v>
       </c>
@@ -19455,7 +19470,7 @@
         <v>100.1193</v>
       </c>
     </row>
-    <row r="78" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B78" s="1">
         <v>1.6</v>
       </c>
@@ -19607,7 +19622,7 @@
         <v>97.618499999999997</v>
       </c>
     </row>
-    <row r="79" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B79" s="1">
         <v>1.7</v>
       </c>
@@ -19759,7 +19774,7 @@
         <v>92.325900000000004</v>
       </c>
     </row>
-    <row r="80" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B80" s="1">
         <v>1.8</v>
       </c>
@@ -19911,7 +19926,7 @@
         <v>85.343000000000004</v>
       </c>
     </row>
-    <row r="81" spans="2:51" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:51" x14ac:dyDescent="0.3">
       <c r="B81" s="1">
         <v>1.9</v>
       </c>
@@ -20066,4 +20081,2318 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29424509-3824-4FC3-A99C-410B82A3A8E8}">
+  <dimension ref="B1:AY20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="51" width="6.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="P2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="R2" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="S2" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="T2" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="U2" s="1">
+        <v>2</v>
+      </c>
+      <c r="V2" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="W2" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X2" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>4</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B3" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="C3" s="1">
+        <v>7.0049999999999999</v>
+      </c>
+      <c r="D3" s="1">
+        <v>6.9410999999999996</v>
+      </c>
+      <c r="E3" s="1">
+        <v>6.8811</v>
+      </c>
+      <c r="F3" s="1">
+        <v>6.8255999999999997</v>
+      </c>
+      <c r="G3" s="1">
+        <v>6.7751000000000001</v>
+      </c>
+      <c r="H3" s="1">
+        <v>6.7259000000000002</v>
+      </c>
+      <c r="I3" s="1">
+        <v>6.673</v>
+      </c>
+      <c r="J3" s="1">
+        <v>6.6176000000000004</v>
+      </c>
+      <c r="K3" s="1">
+        <v>6.5576999999999996</v>
+      </c>
+      <c r="L3" s="1">
+        <v>6.49</v>
+      </c>
+      <c r="M3" s="1">
+        <v>6.4139999999999997</v>
+      </c>
+      <c r="N3" s="1">
+        <v>6.3312999999999997</v>
+      </c>
+      <c r="O3" s="1">
+        <v>6.2419000000000002</v>
+      </c>
+      <c r="P3" s="1">
+        <v>6.1445999999999996</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>6.0410000000000004</v>
+      </c>
+      <c r="R3" s="1">
+        <v>5.9336000000000002</v>
+      </c>
+      <c r="S3" s="1">
+        <v>5.8242000000000003</v>
+      </c>
+      <c r="T3" s="1">
+        <v>5.7130000000000001</v>
+      </c>
+      <c r="U3" s="1">
+        <v>5.6035000000000004</v>
+      </c>
+      <c r="V3" s="1">
+        <v>5.4987000000000004</v>
+      </c>
+      <c r="W3" s="1">
+        <v>5.3977000000000004</v>
+      </c>
+      <c r="X3" s="1">
+        <v>5.3037999999999998</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>5.2172999999999998</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>5.1360000000000001</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>5.0602</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>4.9874000000000001</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>4.9223999999999997</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>4.8632</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>4.8102</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>4.7584</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>4.7129000000000003</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>4.6741999999999999</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>4.6376999999999997</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>4.6052999999999997</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>4.5789999999999997</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>4.5557999999999996</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>4.5376000000000003</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>4.5248999999999997</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>4.5267999999999997</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>4.5429000000000004</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>4.5609999999999999</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>4.5742000000000003</v>
+      </c>
+      <c r="AT3" s="1">
+        <v>4.5773000000000001</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>4.5648</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>4.5331000000000001</v>
+      </c>
+      <c r="AW3" s="1">
+        <v>4.4847999999999999</v>
+      </c>
+      <c r="AX3" s="1">
+        <v>4.4279000000000002</v>
+      </c>
+      <c r="AY3" s="1">
+        <v>4.3754999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="C4" s="1">
+        <v>6.7342000000000004</v>
+      </c>
+      <c r="D4" s="1">
+        <v>6.6505999999999998</v>
+      </c>
+      <c r="E4" s="1">
+        <v>6.5789999999999997</v>
+      </c>
+      <c r="F4" s="1">
+        <v>6.5175000000000001</v>
+      </c>
+      <c r="G4" s="1">
+        <v>6.4650999999999996</v>
+      </c>
+      <c r="H4" s="1">
+        <v>6.4203000000000001</v>
+      </c>
+      <c r="I4" s="1">
+        <v>6.3788999999999998</v>
+      </c>
+      <c r="J4" s="1">
+        <v>6.3380000000000001</v>
+      </c>
+      <c r="K4" s="1">
+        <v>6.2950999999999997</v>
+      </c>
+      <c r="L4" s="1">
+        <v>6.2480000000000002</v>
+      </c>
+      <c r="M4" s="1">
+        <v>6.1954000000000002</v>
+      </c>
+      <c r="N4" s="1">
+        <v>6.1357999999999997</v>
+      </c>
+      <c r="O4" s="1">
+        <v>6.0701999999999998</v>
+      </c>
+      <c r="P4" s="1">
+        <v>5.9996</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>5.9252000000000002</v>
+      </c>
+      <c r="R4" s="1">
+        <v>5.8456000000000001</v>
+      </c>
+      <c r="S4" s="1">
+        <v>5.7614999999999998</v>
+      </c>
+      <c r="T4" s="1">
+        <v>5.6742999999999997</v>
+      </c>
+      <c r="U4" s="1">
+        <v>5.5853999999999999</v>
+      </c>
+      <c r="V4" s="1">
+        <v>5.4965000000000002</v>
+      </c>
+      <c r="W4" s="1">
+        <v>5.4089</v>
+      </c>
+      <c r="X4" s="1">
+        <v>5.3217999999999996</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>5.2370000000000001</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>5.1581999999999999</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>5.0838999999999999</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>5.0171999999999999</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>4.9573</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>4.9065000000000003</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>4.8619000000000003</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>4.8235999999999999</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>4.7945000000000002</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>4.7735000000000003</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>4.7615999999999996</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>4.7576000000000001</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>4.7610999999999999</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>4.7850000000000001</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>4.8076999999999996</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>4.8335999999999997</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>4.8582000000000001</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>4.8788999999999998</v>
+      </c>
+      <c r="AR4" s="1">
+        <v>4.8941999999999997</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AT4" s="1">
+        <v>4.8924000000000003</v>
+      </c>
+      <c r="AU4" s="1">
+        <v>4.8682999999999996</v>
+      </c>
+      <c r="AV4" s="1">
+        <v>4.8253000000000004</v>
+      </c>
+      <c r="AW4" s="1">
+        <v>4.7580999999999998</v>
+      </c>
+      <c r="AX4" s="1">
+        <v>4.6626000000000003</v>
+      </c>
+      <c r="AY4" s="1">
+        <v>4.5313999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C5" s="1">
+        <v>6.4707999999999997</v>
+      </c>
+      <c r="D5" s="1">
+        <v>6.3737000000000004</v>
+      </c>
+      <c r="E5" s="1">
+        <v>6.2859999999999996</v>
+      </c>
+      <c r="F5" s="1">
+        <v>6.2130999999999998</v>
+      </c>
+      <c r="G5" s="1">
+        <v>6.1551</v>
+      </c>
+      <c r="H5" s="1">
+        <v>6.1085000000000003</v>
+      </c>
+      <c r="I5" s="1">
+        <v>6.0694999999999997</v>
+      </c>
+      <c r="J5" s="1">
+        <v>6.0353000000000003</v>
+      </c>
+      <c r="K5" s="1">
+        <v>6.0050999999999997</v>
+      </c>
+      <c r="L5" s="1">
+        <v>5.9774000000000003</v>
+      </c>
+      <c r="M5" s="1">
+        <v>5.9470000000000001</v>
+      </c>
+      <c r="N5" s="1">
+        <v>5.9130000000000003</v>
+      </c>
+      <c r="O5" s="1">
+        <v>5.8738000000000001</v>
+      </c>
+      <c r="P5" s="1">
+        <v>5.8291000000000004</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>5.7797999999999998</v>
+      </c>
+      <c r="R5" s="1">
+        <v>5.7256</v>
+      </c>
+      <c r="S5" s="1">
+        <v>5.6670999999999996</v>
+      </c>
+      <c r="T5" s="1">
+        <v>5.6059000000000001</v>
+      </c>
+      <c r="U5" s="1">
+        <v>5.5423999999999998</v>
+      </c>
+      <c r="V5" s="1">
+        <v>5.4771999999999998</v>
+      </c>
+      <c r="W5" s="1">
+        <v>5.4109999999999996</v>
+      </c>
+      <c r="X5" s="1">
+        <v>5.3461999999999996</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>5.2835000000000001</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>5.2224000000000004</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>5.1646999999999998</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>5.1124999999999998</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>5.0643000000000002</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>5.0217999999999998</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>4.9858000000000002</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>4.9553000000000003</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>4.9314</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>4.9127000000000001</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>4.8998999999999997</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>4.8928000000000003</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>4.8903999999999996</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>4.8921999999999999</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>4.8979999999999997</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>4.9058000000000002</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>4.9141000000000004</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>4.9227999999999996</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>4.9275000000000002</v>
+      </c>
+      <c r="AR5" s="1">
+        <v>4.9259000000000004</v>
+      </c>
+      <c r="AS5" s="1">
+        <v>4.9147999999999996</v>
+      </c>
+      <c r="AT5" s="1">
+        <v>4.8905000000000003</v>
+      </c>
+      <c r="AU5" s="1">
+        <v>4.8513999999999999</v>
+      </c>
+      <c r="AV5" s="1">
+        <v>4.7927999999999997</v>
+      </c>
+      <c r="AW5" s="1">
+        <v>4.7089999999999996</v>
+      </c>
+      <c r="AX5" s="1">
+        <v>4.5964</v>
+      </c>
+      <c r="AY5" s="1">
+        <v>4.4503000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="C6" s="1">
+        <v>6.1817000000000002</v>
+      </c>
+      <c r="D6" s="1">
+        <v>6.0883000000000003</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5.9993999999999996</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5.9195000000000002</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5.8539000000000003</v>
+      </c>
+      <c r="H6" s="1">
+        <v>5.8041999999999998</v>
+      </c>
+      <c r="I6" s="1">
+        <v>5.7672999999999996</v>
+      </c>
+      <c r="J6" s="1">
+        <v>5.7397999999999998</v>
+      </c>
+      <c r="K6" s="1">
+        <v>5.718</v>
+      </c>
+      <c r="L6" s="1">
+        <v>5.6989000000000001</v>
+      </c>
+      <c r="M6" s="1">
+        <v>5.6805000000000003</v>
+      </c>
+      <c r="N6" s="1">
+        <v>5.6616</v>
+      </c>
+      <c r="O6" s="1">
+        <v>5.6405000000000003</v>
+      </c>
+      <c r="P6" s="1">
+        <v>5.6158999999999999</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>5.5875000000000004</v>
+      </c>
+      <c r="R6" s="1">
+        <v>5.5553999999999997</v>
+      </c>
+      <c r="S6" s="1">
+        <v>5.5198</v>
+      </c>
+      <c r="T6" s="1">
+        <v>5.4809999999999999</v>
+      </c>
+      <c r="U6" s="1">
+        <v>5.4397000000000002</v>
+      </c>
+      <c r="V6" s="1">
+        <v>5.3963999999999999</v>
+      </c>
+      <c r="W6" s="1">
+        <v>5.3521000000000001</v>
+      </c>
+      <c r="X6" s="1">
+        <v>5.3078000000000003</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>5.2630999999999997</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>5.2180999999999997</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>5.1734999999999998</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>5.1295000000000002</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>5.0872999999999999</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>5.0483000000000002</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>5.0114000000000001</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>4.9771999999999998</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>4.9477000000000002</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>4.9222000000000001</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>4.9001999999999999</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>4.8807999999999998</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>4.8646000000000003</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>4.8506999999999998</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>4.8376999999999999</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>4.8251999999999997</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>4.8120000000000003</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>4.8010999999999999</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>4.7869000000000002</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>4.7656999999999998</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>4.7343000000000002</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>4.6902999999999997</v>
+      </c>
+      <c r="AU6" s="1">
+        <v>4.6334999999999997</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>4.5559000000000003</v>
+      </c>
+      <c r="AW6" s="1">
+        <v>4.4527000000000001</v>
+      </c>
+      <c r="AX6" s="1">
+        <v>4.3193999999999999</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>4.1529999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5.7971000000000004</v>
+      </c>
+      <c r="D7" s="1">
+        <v>5.7145999999999999</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5.6444999999999999</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5.5877999999999997</v>
+      </c>
+      <c r="G7" s="1">
+        <v>5.5431999999999997</v>
+      </c>
+      <c r="H7" s="1">
+        <v>5.5044000000000004</v>
+      </c>
+      <c r="I7" s="1">
+        <v>5.4739000000000004</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5.4550000000000001</v>
+      </c>
+      <c r="K7" s="1">
+        <v>5.4451000000000001</v>
+      </c>
+      <c r="L7" s="1">
+        <v>5.4408000000000003</v>
+      </c>
+      <c r="M7" s="1">
+        <v>5.4386000000000001</v>
+      </c>
+      <c r="N7" s="1">
+        <v>5.4367000000000001</v>
+      </c>
+      <c r="O7" s="1">
+        <v>5.4337999999999997</v>
+      </c>
+      <c r="P7" s="1">
+        <v>5.4291999999999998</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>5.4222999999999999</v>
+      </c>
+      <c r="R7" s="1">
+        <v>5.4127999999999998</v>
+      </c>
+      <c r="S7" s="1">
+        <v>5.4008000000000003</v>
+      </c>
+      <c r="T7" s="1">
+        <v>5.3861999999999997</v>
+      </c>
+      <c r="U7" s="1">
+        <v>5.3695000000000004</v>
+      </c>
+      <c r="V7" s="1">
+        <v>5.3506999999999998</v>
+      </c>
+      <c r="W7" s="1">
+        <v>5.3303000000000003</v>
+      </c>
+      <c r="X7" s="1">
+        <v>5.3085000000000004</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>5.2853000000000003</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>5.2607999999999997</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>5.2351000000000001</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>5.2081</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>5.1802000000000001</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>5.1512000000000002</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>5.1208</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>5.0892999999999997</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>5.0567000000000002</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>5.0229999999999997</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>4.9881000000000002</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>4.9523000000000001</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>4.9168000000000003</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>4.8817000000000004</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>4.8460999999999999</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>4.8076999999999996</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>4.7676999999999996</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>4.7237</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>4.6741999999999999</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>4.6214000000000004</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>4.5654000000000003</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>4.4988000000000001</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>4.4192</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>4.3177000000000003</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>4.1917</v>
+      </c>
+      <c r="AX7" s="1">
+        <v>4.0472000000000001</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>3.8944999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5.1003999999999996</v>
+      </c>
+      <c r="D8" s="1">
+        <v>5.1925999999999997</v>
+      </c>
+      <c r="E8" s="1">
+        <v>5.2519999999999998</v>
+      </c>
+      <c r="F8" s="1">
+        <v>5.2332000000000001</v>
+      </c>
+      <c r="G8" s="1">
+        <v>5.19</v>
+      </c>
+      <c r="H8" s="1">
+        <v>5.1543000000000001</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5.1253000000000002</v>
+      </c>
+      <c r="J8" s="1">
+        <v>5.1146000000000003</v>
+      </c>
+      <c r="K8" s="1">
+        <v>5.1196999999999999</v>
+      </c>
+      <c r="L8" s="1">
+        <v>5.1349</v>
+      </c>
+      <c r="M8" s="1">
+        <v>5.1546000000000003</v>
+      </c>
+      <c r="N8" s="1">
+        <v>5.1775000000000002</v>
+      </c>
+      <c r="O8" s="1">
+        <v>5.2007000000000003</v>
+      </c>
+      <c r="P8" s="1">
+        <v>5.2225999999999999</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>5.2431000000000001</v>
+      </c>
+      <c r="R8" s="1">
+        <v>5.2609000000000004</v>
+      </c>
+      <c r="S8" s="1">
+        <v>5.2763</v>
+      </c>
+      <c r="T8" s="1">
+        <v>5.2910000000000004</v>
+      </c>
+      <c r="U8" s="1">
+        <v>5.3029999999999999</v>
+      </c>
+      <c r="V8" s="1">
+        <v>5.3128000000000002</v>
+      </c>
+      <c r="W8" s="1">
+        <v>5.3205999999999998</v>
+      </c>
+      <c r="X8" s="1">
+        <v>5.3262</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>5.33</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>5.3315999999999999</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>5.3311999999999999</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>5.3288000000000002</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>5.3242000000000003</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>5.3174000000000001</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>5.3080999999999996</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>5.2961999999999998</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>5.2816000000000001</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>5.2640000000000002</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>5.2431999999999999</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>5.2194000000000003</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>5.1923000000000004</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>5.1614000000000004</v>
+      </c>
+      <c r="AM8" s="1">
+        <v>5.1261000000000001</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>5.0872000000000002</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>5.0435999999999996</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>4.9935</v>
+      </c>
+      <c r="AQ8" s="1">
+        <v>4.9375999999999998</v>
+      </c>
+      <c r="AR8" s="1">
+        <v>4.8734000000000002</v>
+      </c>
+      <c r="AS8" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="AT8" s="1">
+        <v>4.7153</v>
+      </c>
+      <c r="AU8" s="1">
+        <v>4.6193999999999997</v>
+      </c>
+      <c r="AV8" s="1">
+        <v>4.5124000000000004</v>
+      </c>
+      <c r="AW8" s="1">
+        <v>4.3978999999999999</v>
+      </c>
+      <c r="AX8" s="1">
+        <v>4.2811000000000003</v>
+      </c>
+      <c r="AY8" s="1">
+        <v>4.1715</v>
+      </c>
+    </row>
+    <row r="9" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5.2290000000000001</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5.2933000000000003</v>
+      </c>
+      <c r="E9" s="1">
+        <v>5.1527000000000003</v>
+      </c>
+      <c r="F9" s="1">
+        <v>4.9878</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4.8154000000000003</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4.7541000000000002</v>
+      </c>
+      <c r="I9" s="1">
+        <v>4.7270000000000003</v>
+      </c>
+      <c r="J9" s="1">
+        <v>4.7089999999999996</v>
+      </c>
+      <c r="K9" s="1">
+        <v>4.7178000000000004</v>
+      </c>
+      <c r="L9" s="1">
+        <v>4.7398999999999996</v>
+      </c>
+      <c r="M9" s="1">
+        <v>4.7835000000000001</v>
+      </c>
+      <c r="N9" s="1">
+        <v>4.8327999999999998</v>
+      </c>
+      <c r="O9" s="1">
+        <v>4.8826999999999998</v>
+      </c>
+      <c r="P9" s="1">
+        <v>4.9313000000000002</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>4.9778000000000002</v>
+      </c>
+      <c r="R9" s="1">
+        <v>5.0209000000000001</v>
+      </c>
+      <c r="S9" s="1">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="T9" s="1">
+        <v>5.0971000000000002</v>
+      </c>
+      <c r="U9" s="1">
+        <v>5.1330999999999998</v>
+      </c>
+      <c r="V9" s="1">
+        <v>5.1681999999999997</v>
+      </c>
+      <c r="W9" s="1">
+        <v>5.2019000000000002</v>
+      </c>
+      <c r="X9" s="1">
+        <v>5.2348999999999997</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>5.266</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>5.2965999999999998</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>5.3250999999999999</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>5.3506999999999998</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>5.3731</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>5.3925999999999998</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>5.4089999999999998</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>5.4226999999999999</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>5.4337</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>5.4414999999999996</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>5.4459</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>5.4473000000000003</v>
+      </c>
+      <c r="AK9" s="1">
+        <v>5.4452999999999996</v>
+      </c>
+      <c r="AL9" s="1">
+        <v>5.4398</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>5.4307999999999996</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>5.4179000000000004</v>
+      </c>
+      <c r="AO9" s="1">
+        <v>5.4013999999999998</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>5.3807</v>
+      </c>
+      <c r="AQ9" s="1">
+        <v>5.3552999999999997</v>
+      </c>
+      <c r="AR9" s="1">
+        <v>5.3246000000000002</v>
+      </c>
+      <c r="AS9" s="1">
+        <v>5.2885</v>
+      </c>
+      <c r="AT9" s="1">
+        <v>5.2468000000000004</v>
+      </c>
+      <c r="AU9" s="1">
+        <v>5.2011000000000003</v>
+      </c>
+      <c r="AV9" s="1">
+        <v>5.1513</v>
+      </c>
+      <c r="AW9" s="1">
+        <v>5.1001000000000003</v>
+      </c>
+      <c r="AX9" s="1">
+        <v>5.0537999999999998</v>
+      </c>
+      <c r="AY9" s="1">
+        <v>5.0296000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1">
+        <v>5.5411000000000001</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5.0861000000000001</v>
+      </c>
+      <c r="F10" s="1">
+        <v>4.8479999999999999</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4.6717000000000004</v>
+      </c>
+      <c r="H10" s="1">
+        <v>4.4744999999999999</v>
+      </c>
+      <c r="I10" s="1">
+        <v>4.3411</v>
+      </c>
+      <c r="J10" s="1">
+        <v>4.2411000000000003</v>
+      </c>
+      <c r="K10" s="1">
+        <v>4.2054999999999998</v>
+      </c>
+      <c r="L10" s="1">
+        <v>4.2323000000000004</v>
+      </c>
+      <c r="M10" s="1">
+        <v>4.2927</v>
+      </c>
+      <c r="N10" s="1">
+        <v>4.3624000000000001</v>
+      </c>
+      <c r="O10" s="1">
+        <v>4.4328000000000003</v>
+      </c>
+      <c r="P10" s="1">
+        <v>4.5026000000000002</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>4.5709999999999997</v>
+      </c>
+      <c r="R10" s="1">
+        <v>4.6375999999999999</v>
+      </c>
+      <c r="S10" s="1">
+        <v>4.6996000000000002</v>
+      </c>
+      <c r="T10" s="1">
+        <v>4.7615999999999996</v>
+      </c>
+      <c r="U10" s="1">
+        <v>4.8231000000000002</v>
+      </c>
+      <c r="V10" s="1">
+        <v>4.8783000000000003</v>
+      </c>
+      <c r="W10" s="1">
+        <v>4.9336000000000002</v>
+      </c>
+      <c r="X10" s="1">
+        <v>4.9866999999999999</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>5.0374999999999996</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>5.0850999999999997</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>5.1311</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>5.1759000000000004</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>5.2198000000000002</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>5.2630999999999997</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>5.3045999999999998</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>5.3448000000000002</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>5.3826000000000001</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>5.4170999999999996</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>5.4477000000000002</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>5.4751000000000003</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>5.4988999999999999</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>5.5197000000000003</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>5.5377999999999998</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>5.5532000000000004</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>5.5659999999999998</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>5.5762999999999998</v>
+      </c>
+      <c r="AQ10" s="1">
+        <v>5.5845000000000002</v>
+      </c>
+      <c r="AR10" s="1">
+        <v>5.5911999999999997</v>
+      </c>
+      <c r="AS10" s="1">
+        <v>5.5963000000000003</v>
+      </c>
+      <c r="AT10" s="1">
+        <v>5.6003999999999996</v>
+      </c>
+      <c r="AU10" s="1">
+        <v>5.6067999999999998</v>
+      </c>
+      <c r="AV10" s="1">
+        <v>5.6181999999999999</v>
+      </c>
+      <c r="AW10" s="1">
+        <v>5.6394000000000002</v>
+      </c>
+      <c r="AX10" s="1">
+        <v>5.6792999999999996</v>
+      </c>
+      <c r="AY10" s="1">
+        <v>5.7618999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1">
+        <v>5.6300999999999997</v>
+      </c>
+      <c r="F11" s="1">
+        <v>5.0602999999999998</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4.7470999999999997</v>
+      </c>
+      <c r="H11" s="1">
+        <v>4.4408000000000003</v>
+      </c>
+      <c r="I11" s="1">
+        <v>4.1014999999999997</v>
+      </c>
+      <c r="J11" s="1">
+        <v>3.8090999999999999</v>
+      </c>
+      <c r="K11" s="1">
+        <v>3.6943000000000001</v>
+      </c>
+      <c r="L11" s="1">
+        <v>3.7033999999999998</v>
+      </c>
+      <c r="M11" s="1">
+        <v>3.7475000000000001</v>
+      </c>
+      <c r="N11" s="1">
+        <v>3.8107000000000002</v>
+      </c>
+      <c r="O11" s="1">
+        <v>3.8866000000000001</v>
+      </c>
+      <c r="P11" s="1">
+        <v>3.9714999999999998</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>4.0469999999999997</v>
+      </c>
+      <c r="R11" s="1">
+        <v>4.1285999999999996</v>
+      </c>
+      <c r="S11" s="1">
+        <v>4.2176999999999998</v>
+      </c>
+      <c r="T11" s="1">
+        <v>4.3003999999999998</v>
+      </c>
+      <c r="U11" s="1">
+        <v>4.3738999999999999</v>
+      </c>
+      <c r="V11" s="1">
+        <v>4.4413</v>
+      </c>
+      <c r="W11" s="1">
+        <v>4.5106999999999999</v>
+      </c>
+      <c r="X11" s="1">
+        <v>4.5777999999999999</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>4.6402000000000001</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>4.6985000000000001</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>4.7622</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>4.8235999999999999</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>4.8823999999999996</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>4.9416000000000002</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>4.9991000000000003</v>
+      </c>
+      <c r="AF11" s="1">
+        <v>5.0534999999999997</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>5.1055000000000001</v>
+      </c>
+      <c r="AH11" s="1">
+        <v>5.1534000000000004</v>
+      </c>
+      <c r="AI11" s="1">
+        <v>5.2000999999999999</v>
+      </c>
+      <c r="AJ11" s="1">
+        <v>5.2432999999999996</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>5.2869000000000002</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>5.3292999999999999</v>
+      </c>
+      <c r="AM11" s="1">
+        <v>5.3691000000000004</v>
+      </c>
+      <c r="AN11" s="1">
+        <v>5.4081000000000001</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>5.4466999999999999</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>5.4837999999999996</v>
+      </c>
+      <c r="AQ11" s="1">
+        <v>5.5191999999999997</v>
+      </c>
+      <c r="AR11" s="1">
+        <v>5.5530999999999997</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>5.5861000000000001</v>
+      </c>
+      <c r="AT11" s="1">
+        <v>5.6192000000000002</v>
+      </c>
+      <c r="AU11" s="1">
+        <v>5.6562000000000001</v>
+      </c>
+      <c r="AV11" s="1">
+        <v>5.6997999999999998</v>
+      </c>
+      <c r="AW11" s="1">
+        <v>5.7531999999999996</v>
+      </c>
+      <c r="AX11" s="1">
+        <v>5.8211000000000004</v>
+      </c>
+      <c r="AY11" s="1">
+        <v>5.9131</v>
+      </c>
+    </row>
+    <row r="12" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="28">
+        <v>6.1296999999999997</v>
+      </c>
+      <c r="G12" s="1">
+        <v>5.1375999999999999</v>
+      </c>
+      <c r="H12" s="1">
+        <v>4.6134000000000004</v>
+      </c>
+      <c r="I12" s="1">
+        <v>4.1098999999999997</v>
+      </c>
+      <c r="J12" s="1">
+        <v>3.71</v>
+      </c>
+      <c r="K12" s="1">
+        <v>3.5565000000000002</v>
+      </c>
+      <c r="L12" s="1">
+        <v>3.5167000000000002</v>
+      </c>
+      <c r="M12" s="1">
+        <v>3.5402999999999998</v>
+      </c>
+      <c r="N12" s="1">
+        <v>3.5709</v>
+      </c>
+      <c r="O12" s="1">
+        <v>3.5884999999999998</v>
+      </c>
+      <c r="P12" s="1">
+        <v>3.6080000000000001</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>3.6375999999999999</v>
+      </c>
+      <c r="R12" s="1">
+        <v>3.6827000000000001</v>
+      </c>
+      <c r="S12" s="1">
+        <v>3.7280000000000002</v>
+      </c>
+      <c r="T12" s="1">
+        <v>3.7787999999999999</v>
+      </c>
+      <c r="U12" s="1">
+        <v>3.8344</v>
+      </c>
+      <c r="V12" s="1">
+        <v>3.8938999999999999</v>
+      </c>
+      <c r="W12" s="1">
+        <v>3.9535</v>
+      </c>
+      <c r="X12" s="1">
+        <v>4.0195999999999996</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>4.0932000000000004</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>4.1717000000000004</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>4.2478999999999996</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>4.3171999999999997</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>4.3818999999999999</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>4.4499000000000004</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>4.5179999999999998</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>4.5811000000000002</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>4.6414</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>4.6993999999999998</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>4.7577999999999996</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>4.8170999999999999</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>4.8730000000000002</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>4.9250999999999996</v>
+      </c>
+      <c r="AM12" s="1">
+        <v>4.9739000000000004</v>
+      </c>
+      <c r="AN12" s="1">
+        <v>5.0225999999999997</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>5.0712999999999999</v>
+      </c>
+      <c r="AP12" s="1">
+        <v>5.1195000000000004</v>
+      </c>
+      <c r="AQ12" s="1">
+        <v>5.1680000000000001</v>
+      </c>
+      <c r="AR12" s="1">
+        <v>5.2160000000000002</v>
+      </c>
+      <c r="AS12" s="1">
+        <v>5.2643000000000004</v>
+      </c>
+      <c r="AT12" s="1">
+        <v>5.3171999999999997</v>
+      </c>
+      <c r="AU12" s="1">
+        <v>5.3733000000000004</v>
+      </c>
+      <c r="AV12" s="1">
+        <v>5.4317000000000002</v>
+      </c>
+      <c r="AW12" s="1">
+        <v>5.4951999999999996</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>5.5696000000000003</v>
+      </c>
+      <c r="AY12" s="1">
+        <v>5.6551999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="28">
+        <v>13.6363</v>
+      </c>
+      <c r="H13" s="28">
+        <v>7.7502000000000004</v>
+      </c>
+      <c r="I13" s="1">
+        <v>5.8710000000000004</v>
+      </c>
+      <c r="J13" s="1">
+        <v>4.9850000000000003</v>
+      </c>
+      <c r="K13" s="1">
+        <v>4.4832999999999998</v>
+      </c>
+      <c r="L13" s="1">
+        <v>4.2836999999999996</v>
+      </c>
+      <c r="M13" s="1">
+        <v>4.1977000000000002</v>
+      </c>
+      <c r="N13" s="1">
+        <v>4.0949</v>
+      </c>
+      <c r="O13" s="1">
+        <v>3.9712000000000001</v>
+      </c>
+      <c r="P13" s="1">
+        <v>3.847</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>3.7265999999999999</v>
+      </c>
+      <c r="R13" s="1">
+        <v>3.6303999999999998</v>
+      </c>
+      <c r="S13" s="1">
+        <v>3.5623</v>
+      </c>
+      <c r="T13" s="1">
+        <v>3.5133000000000001</v>
+      </c>
+      <c r="U13" s="1">
+        <v>3.4857999999999998</v>
+      </c>
+      <c r="V13" s="1">
+        <v>3.4771999999999998</v>
+      </c>
+      <c r="W13" s="1">
+        <v>3.4822000000000002</v>
+      </c>
+      <c r="X13" s="1">
+        <v>3.5085999999999999</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>3.5472000000000001</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>3.5861999999999998</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>3.6337999999999999</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>3.6913999999999998</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>3.7462</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>3.8083999999999998</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>3.8702000000000001</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>3.9350999999999998</v>
+      </c>
+      <c r="AG13" s="1">
+        <v>4.0026000000000002</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>4.0726000000000004</v>
+      </c>
+      <c r="AI13" s="1">
+        <v>4.1437999999999997</v>
+      </c>
+      <c r="AJ13" s="1">
+        <v>4.2119</v>
+      </c>
+      <c r="AK13" s="1">
+        <v>4.2763999999999998</v>
+      </c>
+      <c r="AL13" s="1">
+        <v>4.3372999999999999</v>
+      </c>
+      <c r="AM13" s="1">
+        <v>4.3962000000000003</v>
+      </c>
+      <c r="AN13" s="1">
+        <v>4.4538000000000002</v>
+      </c>
+      <c r="AO13" s="1">
+        <v>4.5170000000000003</v>
+      </c>
+      <c r="AP13" s="1">
+        <v>4.5791000000000004</v>
+      </c>
+      <c r="AQ13" s="1">
+        <v>4.6384999999999996</v>
+      </c>
+      <c r="AR13" s="1">
+        <v>4.6952999999999996</v>
+      </c>
+      <c r="AS13" s="1">
+        <v>4.7514000000000003</v>
+      </c>
+      <c r="AT13" s="1">
+        <v>4.8090999999999999</v>
+      </c>
+      <c r="AU13" s="1">
+        <v>4.8677999999999999</v>
+      </c>
+      <c r="AV13" s="1">
+        <v>4.9291</v>
+      </c>
+      <c r="AW13" s="1">
+        <v>5.0015999999999998</v>
+      </c>
+      <c r="AX13" s="1">
+        <v>5.0843999999999996</v>
+      </c>
+      <c r="AY13" s="1">
+        <v>5.1821000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="1">
+        <v>20.132000000000001</v>
+      </c>
+      <c r="J14" s="1">
+        <v>12.0137</v>
+      </c>
+      <c r="K14" s="1">
+        <v>8.5829000000000004</v>
+      </c>
+      <c r="L14" s="1">
+        <v>6.8143000000000002</v>
+      </c>
+      <c r="M14" s="1">
+        <v>5.8784999999999998</v>
+      </c>
+      <c r="N14" s="1">
+        <v>5.3715000000000002</v>
+      </c>
+      <c r="O14" s="1">
+        <v>5.0137999999999998</v>
+      </c>
+      <c r="P14" s="1">
+        <v>4.7043999999999997</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>4.4112</v>
+      </c>
+      <c r="R14" s="1">
+        <v>4.1558999999999999</v>
+      </c>
+      <c r="S14" s="1">
+        <v>3.9337</v>
+      </c>
+      <c r="T14" s="1">
+        <v>3.7406999999999999</v>
+      </c>
+      <c r="U14" s="1">
+        <v>3.5798999999999999</v>
+      </c>
+      <c r="V14" s="1">
+        <v>3.4582999999999999</v>
+      </c>
+      <c r="W14" s="1">
+        <v>3.3816000000000002</v>
+      </c>
+      <c r="X14" s="1">
+        <v>3.3567999999999998</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>3.3374999999999999</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>3.3184</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>3.3094000000000001</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>3.3006000000000002</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>3.3062999999999998</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>3.3174999999999999</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>3.3279999999999998</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>3.3473999999999999</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>3.3736000000000002</v>
+      </c>
+      <c r="AH14" s="1">
+        <v>3.4070999999999998</v>
+      </c>
+      <c r="AI14" s="1">
+        <v>3.4466000000000001</v>
+      </c>
+      <c r="AJ14" s="1">
+        <v>3.4904999999999999</v>
+      </c>
+      <c r="AK14" s="1">
+        <v>3.5434000000000001</v>
+      </c>
+      <c r="AL14" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="AM14" s="1">
+        <v>3.6570999999999998</v>
+      </c>
+      <c r="AN14" s="1">
+        <v>3.714</v>
+      </c>
+      <c r="AO14" s="1">
+        <v>3.7717000000000001</v>
+      </c>
+      <c r="AP14" s="1">
+        <v>3.8300999999999998</v>
+      </c>
+      <c r="AQ14" s="1">
+        <v>3.8894000000000002</v>
+      </c>
+      <c r="AR14" s="1">
+        <v>3.9527000000000001</v>
+      </c>
+      <c r="AS14" s="1">
+        <v>4.0224000000000002</v>
+      </c>
+      <c r="AT14" s="1">
+        <v>4.0972</v>
+      </c>
+      <c r="AU14" s="1">
+        <v>4.1711999999999998</v>
+      </c>
+      <c r="AV14" s="1">
+        <v>4.2466999999999997</v>
+      </c>
+      <c r="AW14" s="1">
+        <v>4.3269000000000002</v>
+      </c>
+      <c r="AX14" s="1">
+        <v>4.4142999999999999</v>
+      </c>
+      <c r="AY14" s="1">
+        <v>4.5170000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1">
+        <v>13.6188</v>
+      </c>
+      <c r="M15" s="1">
+        <v>10.5471</v>
+      </c>
+      <c r="N15" s="1">
+        <v>9.0310000000000006</v>
+      </c>
+      <c r="O15" s="1">
+        <v>7.7653999999999996</v>
+      </c>
+      <c r="P15" s="1">
+        <v>6.6026999999999996</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>5.6485000000000003</v>
+      </c>
+      <c r="R15" s="1">
+        <v>5.0031999999999996</v>
+      </c>
+      <c r="S15" s="1">
+        <v>4.5316999999999998</v>
+      </c>
+      <c r="T15" s="1">
+        <v>4.1296999999999997</v>
+      </c>
+      <c r="U15" s="1">
+        <v>3.7978000000000001</v>
+      </c>
+      <c r="V15" s="1">
+        <v>3.5533000000000001</v>
+      </c>
+      <c r="W15" s="1">
+        <v>3.3820000000000001</v>
+      </c>
+      <c r="X15" s="1">
+        <v>3.4013</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>3.4626999999999999</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>3.5213999999999999</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>3.5928</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>3.6677</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>3.7097000000000002</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>3.7225000000000001</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>3.6966999999999999</v>
+      </c>
+      <c r="AF15" s="1">
+        <v>3.6398000000000001</v>
+      </c>
+      <c r="AG15" s="1">
+        <v>3.5569999999999999</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>3.4634</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>3.3620000000000001</v>
+      </c>
+      <c r="AJ15" s="1">
+        <v>3.2608999999999999</v>
+      </c>
+      <c r="AK15" s="1">
+        <v>3.1815000000000002</v>
+      </c>
+      <c r="AL15" s="1">
+        <v>3.1299000000000001</v>
+      </c>
+      <c r="AM15" s="1">
+        <v>3.0960999999999999</v>
+      </c>
+      <c r="AN15" s="1">
+        <v>3.0819000000000001</v>
+      </c>
+      <c r="AO15" s="1">
+        <v>3.0863999999999998</v>
+      </c>
+      <c r="AP15" s="1">
+        <v>3.1137999999999999</v>
+      </c>
+      <c r="AQ15" s="1">
+        <v>3.15</v>
+      </c>
+      <c r="AR15" s="1">
+        <v>3.1941000000000002</v>
+      </c>
+      <c r="AS15" s="1">
+        <v>3.2425999999999999</v>
+      </c>
+      <c r="AT15" s="1">
+        <v>3.2995999999999999</v>
+      </c>
+      <c r="AU15" s="1">
+        <v>3.3609</v>
+      </c>
+      <c r="AV15" s="1">
+        <v>3.4264999999999999</v>
+      </c>
+      <c r="AW15" s="1">
+        <v>3.5032999999999999</v>
+      </c>
+      <c r="AX15" s="1">
+        <v>3.5941999999999998</v>
+      </c>
+      <c r="AY15" s="1">
+        <v>3.6985000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B16" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R16" s="1">
+        <v>15.6333</v>
+      </c>
+      <c r="S16" s="1">
+        <v>14.414300000000001</v>
+      </c>
+      <c r="T16" s="1">
+        <v>13.0663</v>
+      </c>
+      <c r="U16" s="1">
+        <v>11.670199999999999</v>
+      </c>
+      <c r="V16" s="1">
+        <v>10.2904</v>
+      </c>
+      <c r="W16" s="1">
+        <v>8.9641999999999999</v>
+      </c>
+      <c r="X16" s="1">
+        <v>7.7187000000000001</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>6.5884999999999998</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>5.6035000000000004</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>4.8209999999999997</v>
+      </c>
+      <c r="AB16" s="1">
+        <v>4.2192999999999996</v>
+      </c>
+      <c r="AC16" s="1">
+        <v>3.7688999999999999</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>3.4289999999999998</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>3.1920999999999999</v>
+      </c>
+      <c r="AF16" s="1">
+        <v>3.0390000000000001</v>
+      </c>
+      <c r="AG16" s="1">
+        <v>2.9691999999999998</v>
+      </c>
+      <c r="AH16" s="1">
+        <v>2.9363999999999999</v>
+      </c>
+      <c r="AI16" s="1">
+        <v>2.9159999999999999</v>
+      </c>
+      <c r="AJ16" s="1">
+        <v>2.9190999999999998</v>
+      </c>
+      <c r="AK16" s="1">
+        <v>2.9222000000000001</v>
+      </c>
+      <c r="AL16" s="1">
+        <v>2.9188000000000001</v>
+      </c>
+      <c r="AM16" s="1">
+        <v>2.9091999999999998</v>
+      </c>
+      <c r="AN16" s="1">
+        <v>2.8959000000000001</v>
+      </c>
+      <c r="AO16" s="1">
+        <v>2.8814000000000002</v>
+      </c>
+      <c r="AP16" s="1">
+        <v>2.8675999999999999</v>
+      </c>
+      <c r="AQ16" s="1">
+        <v>2.8584999999999998</v>
+      </c>
+      <c r="AR16" s="1">
+        <v>2.8557000000000001</v>
+      </c>
+      <c r="AS16" s="1">
+        <v>2.8624999999999998</v>
+      </c>
+      <c r="AT16" s="1">
+        <v>2.8757999999999999</v>
+      </c>
+      <c r="AU16" s="1">
+        <v>2.8936000000000002</v>
+      </c>
+      <c r="AV16" s="1">
+        <v>2.9165000000000001</v>
+      </c>
+      <c r="AW16" s="1">
+        <v>2.9426000000000001</v>
+      </c>
+      <c r="AX16" s="1">
+        <v>2.9811000000000001</v>
+      </c>
+      <c r="AY16" s="1">
+        <v>3.0274000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="36" t="s">
+        <v>661</v>
+      </c>
+      <c r="C20" t="s">
+        <v>662</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C3:AY16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="10"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/files/Controller Design/ZNMethods_ITAE_Errors.xlsx
+++ b/files/Controller Design/ZNMethods_ITAE_Errors.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulisboa-my.sharepoint.com/personal/ist1100262_tecnico_ulisboa_pt/Documents/MEMec/Thesis/files/Controller Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="185" documentId="8_{95F32091-D855-4402-ADD3-8991BE5FE270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26216FB3-8594-41EA-B495-AA1D8894687A}"/>
+  <xr:revisionPtr revIDLastSave="221" documentId="8_{95F32091-D855-4402-ADD3-8991BE5FE270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B41285B-FE26-4CBF-88BF-4A2E64C0AD6D}"/>
   <bookViews>
-    <workbookView xWindow="-3696" yWindow="-17388" windowWidth="30936" windowHeight="17496" activeTab="3" xr2:uid="{6BCB78A0-0C46-4270-8084-079A19E30873}"/>
+    <workbookView xWindow="-3696" yWindow="-17388" windowWidth="30936" windowHeight="17496" activeTab="5" xr2:uid="{6BCB78A0-0C46-4270-8084-079A19E30873}"/>
   </bookViews>
   <sheets>
     <sheet name="CritGain" sheetId="1" r:id="rId1"/>
     <sheet name="PID_Models" sheetId="3" r:id="rId2"/>
     <sheet name="Gains" sheetId="5" r:id="rId3"/>
     <sheet name="PID_Models_Noise" sheetId="6" r:id="rId4"/>
+    <sheet name="id_ctrl_val" sheetId="7" r:id="rId5"/>
+    <sheet name="id_ctrl_noise" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="665">
   <si>
     <t>ν/ζ</t>
   </si>
@@ -2031,6 +2033,12 @@
   </si>
   <si>
     <t>Simulations kept over 30 seconds</t>
+  </si>
+  <si>
+    <t>need to add Wcp fallback</t>
+  </si>
+  <si>
+    <t>Noise level 0.03</t>
   </si>
 </sst>
 </file>
@@ -2509,6 +2517,7 @@
     </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2527,7 +2536,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2929,28 +2937,28 @@
   <sheetData>
     <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="36"/>
     </row>
     <row r="3" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
     </row>
     <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
     </row>
     <row r="7" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="20" t="s">
@@ -3328,11 +3336,11 @@
     </row>
     <row r="18" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="33"/>
     </row>
     <row r="20" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="20" t="s">
@@ -3710,11 +3718,11 @@
     </row>
     <row r="31" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="33"/>
     </row>
     <row r="33" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="20" t="s">
@@ -22373,7 +22381,7 @@
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="30" t="s">
         <v>661</v>
       </c>
       <c r="C20" t="s">
@@ -22395,4 +22403,4325 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E237936-F695-4675-B42C-B0BF8FA4F476}">
+  <dimension ref="B1:AY15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="51" width="6.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="P2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="R2" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="S2" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="T2" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="U2" s="1">
+        <v>2</v>
+      </c>
+      <c r="V2" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="W2" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X2" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>4</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B3" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.4713</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.1545</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.15390000000000001</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.21429999999999999</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.21379999999999999</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.24809999999999999</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.29780000000000001</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0.3503</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0.40450000000000003</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0.53539999999999999</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0.70140000000000002</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0.61360000000000003</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0.58840000000000003</v>
+      </c>
+      <c r="U3" s="1">
+        <v>0.57620000000000005</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0.89529999999999998</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.97740000000000005</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.3125</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.1119</v>
+      </c>
+      <c r="F4" s="1">
+        <v>7.5700000000000003E-2</v>
+      </c>
+      <c r="G4" s="1">
+        <v>8.6800000000000002E-2</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.11020000000000001</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.1201</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.124</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0.13089999999999999</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0.14069999999999999</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.1532</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0.1681</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0.185</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0.2031</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0.2218</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0.2409</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0.26050000000000001</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0.28129999999999999</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0.30420000000000003</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0.33050000000000002</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0.3619</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>0.37859999999999999</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0.39960000000000001</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>0.42459999999999998</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>0.4526</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>0.48220000000000002</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>0.51219999999999999</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>0.54110000000000003</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>0.56810000000000005</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>0.59319999999999995</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>0.61729999999999996</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>0.64319999999999999</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>0.67510000000000003</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>0.71819999999999995</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>0.77690000000000003</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>0.85219999999999996</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>0.94010000000000005</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>1.0319</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2.2170000000000001</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.65310000000000001</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.29580000000000001</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="G5" s="1">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3.9300000000000002E-2</v>
+      </c>
+      <c r="I5" s="1">
+        <v>5.16E-2</v>
+      </c>
+      <c r="J5" s="1">
+        <v>6.1600000000000002E-2</v>
+      </c>
+      <c r="K5" s="1">
+        <v>6.8500000000000005E-2</v>
+      </c>
+      <c r="L5" s="1">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="M5" s="1">
+        <v>8.2799999999999999E-2</v>
+      </c>
+      <c r="N5" s="1">
+        <v>9.2399999999999996E-2</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0.1032</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0.1143</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0.125</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0.13519999999999999</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0.1452</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0.15570000000000001</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0.1676</v>
+      </c>
+      <c r="V5" s="1">
+        <v>0.2298</v>
+      </c>
+      <c r="W5" s="1">
+        <v>0.22359999999999999</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>0.21929999999999999</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>0.2218</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>0.22770000000000001</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>0.2369</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>0.24970000000000001</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>0.26619999999999999</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0.28710000000000002</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>0.31380000000000002</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>0.3478</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>0.39090000000000003</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>0.44490000000000002</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>0.58979999999999999</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>0.67989999999999995</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>0.77859999999999996</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>0.87549999999999994</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>0.96309999999999996</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>1.0374000000000001</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>1.0952</v>
+      </c>
+      <c r="AR5" s="1">
+        <v>1.1339999999999999</v>
+      </c>
+      <c r="AS5" s="1">
+        <v>1.1516</v>
+      </c>
+      <c r="AT5" s="1">
+        <v>1.1469</v>
+      </c>
+      <c r="AU5" s="1">
+        <v>1.119</v>
+      </c>
+      <c r="AV5" s="1">
+        <v>1.0671999999999999</v>
+      </c>
+      <c r="AW5" s="1">
+        <v>0.99170000000000003</v>
+      </c>
+      <c r="AX5" s="1">
+        <v>0.89259999999999995</v>
+      </c>
+      <c r="AY5" s="1">
+        <v>0.77559999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3.4996999999999998</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.8875</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.56779999999999997</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.42959999999999998</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.17469999999999999</v>
+      </c>
+      <c r="H6" s="1">
+        <v>5.0599999999999999E-2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="J6" s="1">
+        <v>5.8999999999999999E-3</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.0200000000000001E-2</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1.46E-2</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>2.92E-2</v>
+      </c>
+      <c r="O6" s="1">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="P6" s="1">
+        <v>5.79E-2</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>7.46E-2</v>
+      </c>
+      <c r="R6" s="1">
+        <v>9.1399999999999995E-2</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0.1095</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0.1711</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0.17910000000000001</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0.18640000000000001</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0.19489999999999999</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0.20630000000000001</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0.22170000000000001</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0.24229999999999999</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0.26879999999999998</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0.3019</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0.34189999999999998</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>0.38869999999999999</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0.44190000000000002</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>0.50039999999999996</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>0.56320000000000003</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>0.62839999999999996</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>0.69410000000000005</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>0.75839999999999996</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>0.81930000000000003</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>0.87490000000000001</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>0.92379999999999995</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>0.96479999999999999</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>0.99680000000000002</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>1.0192000000000001</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>1.0316000000000001</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>1.0339</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>1.0262</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>1.0086999999999999</v>
+      </c>
+      <c r="AU6" s="1">
+        <v>0.98180000000000001</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>0.94579999999999997</v>
+      </c>
+      <c r="AW6" s="1">
+        <v>0.90149999999999997</v>
+      </c>
+      <c r="AX6" s="1">
+        <v>0.84930000000000005</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="7" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3.6701000000000001</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3.8868999999999998</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1.9161999999999999</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.56740000000000002</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.69479999999999997</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.52810000000000001</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.31659999999999999</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.22459999999999999</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="L7" s="1">
+        <v>5.8200000000000002E-2</v>
+      </c>
+      <c r="M7" s="1">
+        <v>6.25E-2</v>
+      </c>
+      <c r="N7" s="1">
+        <v>7.1400000000000005E-2</v>
+      </c>
+      <c r="O7" s="1">
+        <v>8.1600000000000006E-2</v>
+      </c>
+      <c r="P7" s="1">
+        <v>9.0300000000000005E-2</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>9.6299999999999997E-2</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0.1014</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0.10829999999999999</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0.1179</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0.13059999999999999</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0.1396</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0.14879999999999999</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0.15759999999999999</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0.1671</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0.1908</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>0.2059</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>0.2235</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>0.24379999999999999</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0.26690000000000003</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>0.29249999999999998</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>0.32029999999999997</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>0.3498</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>0.38040000000000002</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>0.41139999999999999</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>0.44219999999999998</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>0.47220000000000001</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>0.501</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>0.52810000000000001</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>0.57550000000000001</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>0.59540000000000004</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>0.61240000000000006</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>0.62660000000000005</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>0.63780000000000003</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>0.64610000000000001</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>0.65159999999999996</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>0.65439999999999998</v>
+      </c>
+      <c r="AX7" s="1">
+        <v>0.65459999999999996</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>0.65249999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3.8708999999999998</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3.8222</v>
+      </c>
+      <c r="E8" s="1">
+        <v>4.1124000000000001</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2.2105999999999999</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.3871</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1.2366999999999999</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.92830000000000001</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.59179999999999999</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.4002</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0.24210000000000001</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0.2137</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0.19739999999999999</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0.1867</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0.191</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0.20549999999999999</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0.2114</v>
+      </c>
+      <c r="V8" s="1">
+        <v>0.21529999999999999</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0.25559999999999999</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0.25409999999999999</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0.2576</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0.26929999999999998</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0.28220000000000001</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>0.29070000000000001</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>0.30270000000000002</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>0.31619999999999998</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0.3322</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>0.3538</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>0.38679999999999998</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>0.441</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>0.52359999999999995</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>0.62260000000000004</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>0.62509999999999999</v>
+      </c>
+      <c r="AM8" s="1">
+        <v>0.72750000000000004</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>0.65480000000000005</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>0.73839999999999995</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>0.48830000000000001</v>
+      </c>
+      <c r="AQ8" s="1">
+        <v>0.57130000000000003</v>
+      </c>
+      <c r="AR8" s="1">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="AS8" s="1">
+        <v>0.75749999999999995</v>
+      </c>
+      <c r="AT8" s="1">
+        <v>0.64810000000000001</v>
+      </c>
+      <c r="AU8" s="1">
+        <v>0.55259999999999998</v>
+      </c>
+      <c r="AV8" s="1">
+        <v>0.65490000000000004</v>
+      </c>
+      <c r="AW8" s="1">
+        <v>0.71140000000000003</v>
+      </c>
+      <c r="AX8" s="1">
+        <v>0.7056</v>
+      </c>
+      <c r="AY8" s="1">
+        <v>0.60619999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4.0770999999999997</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3.6833</v>
+      </c>
+      <c r="F9" s="1">
+        <v>3.8306</v>
+      </c>
+      <c r="G9" s="1">
+        <v>3.5510000000000002</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2.6949000000000001</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2.1476999999999999</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1.5486</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.048</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0.75590000000000002</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0.54390000000000005</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0.47539999999999999</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0.38650000000000001</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0.28970000000000001</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0.29139999999999999</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0.2944</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0.309</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0.30249999999999999</v>
+      </c>
+      <c r="V9" s="1">
+        <v>0.37469999999999998</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0.36349999999999999</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0.36270000000000002</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>0.3644</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0.36730000000000002</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0.37059999999999998</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0.37369999999999998</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>0.37669999999999998</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0.3856</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>0.40689999999999998</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>0.47149999999999997</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0.43430000000000002</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>0.53569999999999995</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>0.49509999999999998</v>
+      </c>
+      <c r="AK9" s="1">
+        <v>0.47720000000000001</v>
+      </c>
+      <c r="AL9" s="1">
+        <v>0.59909999999999997</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>0.57609999999999995</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>0.55940000000000001</v>
+      </c>
+      <c r="AO9" s="1">
+        <v>0.55369999999999997</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>0.66859999999999997</v>
+      </c>
+      <c r="AQ9" s="1">
+        <v>0.66180000000000005</v>
+      </c>
+      <c r="AR9" s="1">
+        <v>0.65610000000000002</v>
+      </c>
+      <c r="AS9" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="AT9" s="1">
+        <v>0.64839999999999998</v>
+      </c>
+      <c r="AU9" s="1">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="AV9" s="1">
+        <v>0.65920000000000001</v>
+      </c>
+      <c r="AW9" s="1">
+        <v>0.67410000000000003</v>
+      </c>
+      <c r="AX9" s="1">
+        <v>0.70660000000000001</v>
+      </c>
+      <c r="AY9" s="1">
+        <v>0.71289999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4.1971999999999996</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3.6046999999999998</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3.3809</v>
+      </c>
+      <c r="H10" s="1">
+        <v>3.4356</v>
+      </c>
+      <c r="I10" s="1">
+        <v>3.3374000000000001</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2.8334999999999999</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.9409000000000001</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1.6054999999999999</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1.0538000000000001</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0.69920000000000004</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0.49859999999999999</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0.4073</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0.57189999999999996</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0.57150000000000001</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0.61439999999999995</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0.54430000000000001</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0.55730000000000002</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0.4985</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0.46260000000000001</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0.4587</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0.44869999999999999</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0.43869999999999998</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>0.47099999999999997</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>0.45910000000000001</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>0.45069999999999999</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>0.54730000000000001</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>0.54590000000000005</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>0.54990000000000006</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>0.55920000000000003</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>0.57379999999999998</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>0.59350000000000003</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>0.61729999999999996</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>0.64339999999999997</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>0.66749999999999998</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>0.6825</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>0.61529999999999996</v>
+      </c>
+      <c r="AQ10" s="1">
+        <v>0.64959999999999996</v>
+      </c>
+      <c r="AR10" s="1">
+        <v>0.66769999999999996</v>
+      </c>
+      <c r="AS10" s="1">
+        <v>0.65129999999999999</v>
+      </c>
+      <c r="AT10" s="1">
+        <v>0.65059999999999996</v>
+      </c>
+      <c r="AU10" s="1">
+        <v>0.64649999999999996</v>
+      </c>
+      <c r="AV10" s="1">
+        <v>0.59770000000000001</v>
+      </c>
+      <c r="AW10" s="1">
+        <v>0.6341</v>
+      </c>
+      <c r="AX10" s="1">
+        <v>0.62180000000000002</v>
+      </c>
+      <c r="AY10" s="1">
+        <v>0.62290000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="28">
+        <v>5.0037000000000003</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3.8614999999999999</v>
+      </c>
+      <c r="H11" s="1">
+        <v>3.0076999999999998</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2.4432</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2.3041999999999998</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1.7255</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1.9196</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1.2383</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0.72760000000000002</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0.56569999999999998</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1.0287999999999999</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>1.0107999999999999</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0.94379999999999997</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0.84560000000000002</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0.87819999999999998</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0.74250000000000005</v>
+      </c>
+      <c r="V11" s="1">
+        <v>0.63480000000000003</v>
+      </c>
+      <c r="W11" s="1">
+        <v>0.70930000000000004</v>
+      </c>
+      <c r="X11" s="1">
+        <v>0.60540000000000005</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>0.53700000000000003</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0.56169999999999998</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>0.51370000000000005</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>0.52090000000000003</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>0.50649999999999995</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>0.501</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>0.53610000000000002</v>
+      </c>
+      <c r="AF11" s="1">
+        <v>0.52329999999999999</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>0.51429999999999998</v>
+      </c>
+      <c r="AH11" s="1">
+        <v>0.64670000000000005</v>
+      </c>
+      <c r="AI11" s="1">
+        <v>0.60250000000000004</v>
+      </c>
+      <c r="AJ11" s="1">
+        <v>0.59630000000000005</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>0.59770000000000001</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>0.60289999999999999</v>
+      </c>
+      <c r="AM11" s="1">
+        <v>0.61180000000000001</v>
+      </c>
+      <c r="AN11" s="1">
+        <v>0.62409999999999999</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>0.63919999999999999</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>0.65580000000000005</v>
+      </c>
+      <c r="AQ11" s="1">
+        <v>0.67159999999999997</v>
+      </c>
+      <c r="AR11" s="1">
+        <v>0.68269999999999997</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="AT11" s="1">
+        <v>0.71150000000000002</v>
+      </c>
+      <c r="AU11" s="1">
+        <v>0.66469999999999996</v>
+      </c>
+      <c r="AV11" s="1">
+        <v>0.67369999999999997</v>
+      </c>
+      <c r="AW11" s="1">
+        <v>0.65580000000000005</v>
+      </c>
+      <c r="AX11" s="1">
+        <v>0.66990000000000005</v>
+      </c>
+      <c r="AY11" s="1">
+        <v>0.66190000000000004</v>
+      </c>
+    </row>
+    <row r="12" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="28">
+        <v>6.8117000000000001</v>
+      </c>
+      <c r="H12" s="28">
+        <v>4.9020000000000001</v>
+      </c>
+      <c r="I12" s="1">
+        <v>3.5665</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2.4251999999999998</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1.7601</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1.4361999999999999</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1.3228</v>
+      </c>
+      <c r="N12" s="1">
+        <v>2.1444000000000001</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1.9611000000000001</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1.8125</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>1.6415</v>
+      </c>
+      <c r="R12" s="1">
+        <v>1.5130999999999999</v>
+      </c>
+      <c r="S12" s="1">
+        <v>1.4021999999999999</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0.85309999999999997</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0.86080000000000001</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0.84150000000000003</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0.80289999999999995</v>
+      </c>
+      <c r="X12" s="1">
+        <v>0.75670000000000004</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>0.69989999999999997</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0.63360000000000005</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0.56950000000000001</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>0.50860000000000005</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>0.4869</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0.51580000000000004</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>0.54559999999999997</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>0.50219999999999998</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>0.58830000000000005</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>0.52129999999999999</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>0.5595</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>0.54139999999999999</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>0.59350000000000003</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>0.55030000000000001</v>
+      </c>
+      <c r="AM12" s="1">
+        <v>0.68530000000000002</v>
+      </c>
+      <c r="AN12" s="1">
+        <v>0.58069999999999999</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>0.84540000000000004</v>
+      </c>
+      <c r="AP12" s="1">
+        <v>0.67659999999999998</v>
+      </c>
+      <c r="AQ12" s="1">
+        <v>0.61319999999999997</v>
+      </c>
+      <c r="AR12" s="1">
+        <v>0.61580000000000001</v>
+      </c>
+      <c r="AS12" s="1">
+        <v>0.75290000000000001</v>
+      </c>
+      <c r="AT12" s="1">
+        <v>0.67879999999999996</v>
+      </c>
+      <c r="AU12" s="1">
+        <v>0.65339999999999998</v>
+      </c>
+      <c r="AV12" s="1">
+        <v>0.65380000000000005</v>
+      </c>
+      <c r="AW12" s="1">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>0.72889999999999999</v>
+      </c>
+      <c r="AY12" s="1">
+        <v>0.68689999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="1">
+        <v>12.1676</v>
+      </c>
+      <c r="J13" s="1">
+        <v>8.8137000000000008</v>
+      </c>
+      <c r="K13" s="1">
+        <v>7.8342000000000001</v>
+      </c>
+      <c r="L13" s="1">
+        <v>6.2252000000000001</v>
+      </c>
+      <c r="M13" s="1">
+        <v>5.8059000000000003</v>
+      </c>
+      <c r="N13" s="1">
+        <v>5.1135000000000002</v>
+      </c>
+      <c r="O13" s="1">
+        <v>4.2605000000000004</v>
+      </c>
+      <c r="P13" s="1">
+        <v>3.3521000000000001</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>3.7713000000000001</v>
+      </c>
+      <c r="R13" s="1">
+        <v>2.9750999999999999</v>
+      </c>
+      <c r="S13" s="1">
+        <v>2.1888000000000001</v>
+      </c>
+      <c r="T13" s="1">
+        <v>1.0874999999999999</v>
+      </c>
+      <c r="U13" s="1">
+        <v>1.9521999999999999</v>
+      </c>
+      <c r="V13" s="1">
+        <v>1.6859999999999999</v>
+      </c>
+      <c r="W13" s="1">
+        <v>1.1573</v>
+      </c>
+      <c r="X13" s="1">
+        <v>2.0760000000000001</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>1.2547999999999999</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>1.9915</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>0.97989999999999999</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>1.5638000000000001</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>0.46820000000000001</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>0.82330000000000003</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>1.2124999999999999</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>1.5492999999999999</v>
+      </c>
+      <c r="AG13" s="1">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>0.54310000000000003</v>
+      </c>
+      <c r="AI13" s="1">
+        <v>0.63149999999999995</v>
+      </c>
+      <c r="AJ13" s="1">
+        <v>0.69889999999999997</v>
+      </c>
+      <c r="AK13" s="1">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="AL13" s="1">
+        <v>0.76329999999999998</v>
+      </c>
+      <c r="AM13" s="1">
+        <v>0.76770000000000005</v>
+      </c>
+      <c r="AN13" s="1">
+        <v>0.76290000000000002</v>
+      </c>
+      <c r="AO13" s="1">
+        <v>0.76060000000000005</v>
+      </c>
+      <c r="AP13" s="1">
+        <v>0.7762</v>
+      </c>
+      <c r="AQ13" s="1">
+        <v>0.82379999999999998</v>
+      </c>
+      <c r="AR13" s="1">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="AS13" s="1">
+        <v>1.1672</v>
+      </c>
+      <c r="AT13" s="1">
+        <v>0.95609999999999995</v>
+      </c>
+      <c r="AU13" s="1">
+        <v>0.87660000000000005</v>
+      </c>
+      <c r="AV13" s="1">
+        <v>0.88439999999999996</v>
+      </c>
+      <c r="AW13" s="1">
+        <v>0.94540000000000002</v>
+      </c>
+      <c r="AX13" s="1">
+        <v>0.99639999999999995</v>
+      </c>
+      <c r="AY13" s="1">
+        <v>0.90959999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="1">
+        <v>63.092700000000001</v>
+      </c>
+      <c r="M14" s="1">
+        <v>45.0334</v>
+      </c>
+      <c r="N14" s="1">
+        <v>18.486699999999999</v>
+      </c>
+      <c r="O14" s="1">
+        <v>18.608000000000001</v>
+      </c>
+      <c r="P14" s="1">
+        <v>7.6725000000000003</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>8.3720999999999997</v>
+      </c>
+      <c r="R14" s="1">
+        <v>4.8342999999999998</v>
+      </c>
+      <c r="S14" s="1">
+        <v>4.7374999999999998</v>
+      </c>
+      <c r="T14" s="1">
+        <v>12.7255</v>
+      </c>
+      <c r="U14" s="1">
+        <v>8.7452000000000005</v>
+      </c>
+      <c r="V14" s="1">
+        <v>5.149</v>
+      </c>
+      <c r="W14" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X14" s="1">
+        <v>2.6092</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>1.653</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>1.8393999999999999</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>2.3845000000000001</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>2.7690000000000001</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>2.883</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>2.7164000000000001</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>1.6960999999999999</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>1.0224</v>
+      </c>
+      <c r="AH14" s="1">
+        <v>5.0904999999999996</v>
+      </c>
+      <c r="AI14" s="1">
+        <v>3.7869000000000002</v>
+      </c>
+      <c r="AJ14" s="1">
+        <v>2.4685000000000001</v>
+      </c>
+      <c r="AK14" s="1">
+        <v>1.339</v>
+      </c>
+      <c r="AL14" s="1">
+        <v>4.4321000000000002</v>
+      </c>
+      <c r="AM14" s="1">
+        <v>2.6738</v>
+      </c>
+      <c r="AN14" s="1">
+        <v>1.4107000000000001</v>
+      </c>
+      <c r="AO14" s="1">
+        <v>3.7309999999999999</v>
+      </c>
+      <c r="AP14" s="1">
+        <v>1.9461999999999999</v>
+      </c>
+      <c r="AQ14" s="1">
+        <v>4.3182999999999998</v>
+      </c>
+      <c r="AR14" s="1">
+        <v>2.2423999999999999</v>
+      </c>
+      <c r="AS14" s="1">
+        <v>1.4419</v>
+      </c>
+      <c r="AT14" s="1">
+        <v>2.2458</v>
+      </c>
+      <c r="AU14" s="1">
+        <v>4.0513000000000003</v>
+      </c>
+      <c r="AV14" s="1">
+        <v>2.0459000000000001</v>
+      </c>
+      <c r="AW14" s="1">
+        <v>3.3957999999999999</v>
+      </c>
+      <c r="AX14" s="1">
+        <v>1.7762</v>
+      </c>
+      <c r="AY14" s="1">
+        <v>2.6551</v>
+      </c>
+    </row>
+    <row r="15" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="1">
+        <v>14.9594</v>
+      </c>
+      <c r="S15" s="1">
+        <v>14.3116</v>
+      </c>
+      <c r="T15" s="1">
+        <v>12.2311</v>
+      </c>
+      <c r="U15" s="1">
+        <v>9.6115999999999993</v>
+      </c>
+      <c r="V15" s="1">
+        <v>33.480800000000002</v>
+      </c>
+      <c r="W15" s="1">
+        <v>27.402899999999999</v>
+      </c>
+      <c r="X15" s="1">
+        <v>21.174399999999999</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>15.769500000000001</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>11.569800000000001</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>8.5905000000000005</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>5.4943999999999997</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>3.1288</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>2.347</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>3.0129000000000001</v>
+      </c>
+      <c r="AF15" s="1">
+        <v>2.9232999999999998</v>
+      </c>
+      <c r="AG15" s="1">
+        <v>1.8461000000000001</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>6.1643999999999997</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>3.1227</v>
+      </c>
+      <c r="AJ15" s="1">
+        <v>7.9588999999999999</v>
+      </c>
+      <c r="AK15" s="1">
+        <v>3.6326999999999998</v>
+      </c>
+      <c r="AL15" s="1">
+        <v>7.9225000000000003</v>
+      </c>
+      <c r="AM15" s="1">
+        <v>3.3125</v>
+      </c>
+      <c r="AN15" s="1">
+        <v>6.3601000000000001</v>
+      </c>
+      <c r="AO15" s="1">
+        <v>10.616300000000001</v>
+      </c>
+      <c r="AP15" s="1">
+        <v>4.2582000000000004</v>
+      </c>
+      <c r="AQ15" s="1">
+        <v>6.9177999999999997</v>
+      </c>
+      <c r="AR15" s="1">
+        <v>10.2485</v>
+      </c>
+      <c r="AS15" s="1">
+        <v>3.8751000000000002</v>
+      </c>
+      <c r="AT15" s="1">
+        <v>5.3685</v>
+      </c>
+      <c r="AU15" s="1">
+        <v>7.3761999999999999</v>
+      </c>
+      <c r="AV15" s="1">
+        <v>9.6674000000000007</v>
+      </c>
+      <c r="AW15" s="1">
+        <v>12.0786</v>
+      </c>
+      <c r="AX15" s="1">
+        <v>4.2385999999999999</v>
+      </c>
+      <c r="AY15" s="1">
+        <v>5.0271999999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C3:AY15">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="10"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F192E7DF-432D-405C-9CC1-E8A78B1D27F2}">
+  <dimension ref="B1:AY20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="51" width="5.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="P2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="R2" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="S2" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="T2" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="U2" s="1">
+        <v>2</v>
+      </c>
+      <c r="V2" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="W2" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X2" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>4</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B3" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.41610000000000003</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.11559999999999999</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.2923</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.1144</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.12039999999999999</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.1719</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.15890000000000001</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.1792</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0.17929999999999999</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0.23169999999999999</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0.26669999999999999</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0.32169999999999999</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0.40039999999999998</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.59670000000000001</v>
+      </c>
+      <c r="D4" s="1">
+        <v>5.11E-2</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>4.7E-2</v>
+      </c>
+      <c r="G4" s="1">
+        <v>7.6300000000000007E-2</v>
+      </c>
+      <c r="H4" s="1">
+        <v>7.2300000000000003E-2</v>
+      </c>
+      <c r="I4" s="1">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="J4" s="1">
+        <v>9.5100000000000004E-2</v>
+      </c>
+      <c r="K4" s="1">
+        <v>8.9899999999999994E-2</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0.17249999999999999</v>
+      </c>
+      <c r="M4" s="1">
+        <v>9.9099999999999994E-2</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0.1168</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0.16339999999999999</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0.15479999999999999</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0.1258</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0.25340000000000001</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0.16370000000000001</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0.2223</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0.24360000000000001</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0.23719999999999999</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0.25219999999999998</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0.2064</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1.8207</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.1791</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.26729999999999998</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.78559999999999997</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.58189999999999997</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3.04E-2</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.1696</v>
+      </c>
+      <c r="J5" s="1">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="K5" s="1">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="L5" s="1">
+        <v>4.3700000000000003E-2</v>
+      </c>
+      <c r="M5" s="1">
+        <v>4.87E-2</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0.4173</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0.10489999999999999</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0.1308</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0.1522</v>
+      </c>
+      <c r="R5" s="1">
+        <v>8.1100000000000005E-2</v>
+      </c>
+      <c r="S5" s="1">
+        <v>9.4299999999999995E-2</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0.2671</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0.24640000000000001</v>
+      </c>
+      <c r="V5" s="1">
+        <v>0.18210000000000001</v>
+      </c>
+      <c r="W5" s="1">
+        <v>0.19539999999999999</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0.1041</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>0.30940000000000001</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>0.124</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>0.1285</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>0.36449999999999999</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>0.31759999999999999</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>0.1986</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>1.0629</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>0.15060000000000001</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>0.63370000000000004</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>1.14E-2</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>0.94020000000000004</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>0.83409999999999995</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>0.215</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>0.187</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>0.21260000000000001</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>0.86419999999999997</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>0.34670000000000001</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>0.25929999999999997</v>
+      </c>
+      <c r="AR5" s="28">
+        <v>5.5511E-17</v>
+      </c>
+      <c r="AS5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2.7145000000000001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1.1274999999999999</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.21510000000000001</v>
+      </c>
+      <c r="G6" s="1">
+        <v>3.8800000000000001E-2</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.4342999999999999</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="J6" s="1">
+        <v>3.1E-2</v>
+      </c>
+      <c r="K6" s="1">
+        <v>9.1800000000000007E-2</v>
+      </c>
+      <c r="L6" s="1">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>5.11E-2</v>
+      </c>
+      <c r="O6" s="1">
+        <v>4.6399999999999997E-2</v>
+      </c>
+      <c r="P6" s="1">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0.2198</v>
+      </c>
+      <c r="R6" s="1">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0.1923</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0.14729999999999999</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0.2253</v>
+      </c>
+      <c r="W6" s="28">
+        <v>5476.3</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0.14729999999999999</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>9.0700000000000003E-2</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>6.6400000000000001E-2</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0.21729999999999999</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0.90790000000000004</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0.72219999999999995</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>0.91349999999999998</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0.85070000000000001</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>0.84530000000000005</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>0.2452</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>0.51759999999999995</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>9.06E-2</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>0.1358</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>0.79059999999999997</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>0.48</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>0.58889999999999998</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>0.4824</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>0.71140000000000003</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>0.57050000000000001</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>0.47410000000000002</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>0.2331</v>
+      </c>
+      <c r="AU6" s="28">
+        <v>1.3718000000000001E-8</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>0.19109999999999999</v>
+      </c>
+      <c r="AW6" s="1">
+        <v>0.58150000000000002</v>
+      </c>
+      <c r="AX6" s="1">
+        <v>0.5353</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>0.3715</v>
+      </c>
+    </row>
+    <row r="7" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4.0782999999999996</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3.2130000000000001</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.105</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2.3033999999999999</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.89649999999999996</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2.4318</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.1091</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0.42430000000000001</v>
+      </c>
+      <c r="M7" s="28">
+        <v>5.9971999999999999E-13</v>
+      </c>
+      <c r="N7" s="28">
+        <v>4.9631000000000002E-14</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="28">
+        <v>3.6123999999999998E-12</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0.87819999999999998</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0.1087</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="28">
+        <v>1.1102000000000001E-18</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="28">
+        <v>2.7089E-16</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>0.76749999999999996</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0.24709999999999999</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>0.58340000000000003</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>0.62219999999999998</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>0.1656</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>0.6714</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>0.47039999999999998</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>0.1978</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>0.46879999999999999</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>0.57530000000000003</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>0.2429</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>0.30740000000000001</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>0.2127</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>0.4657</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>0.41370000000000001</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>0.21440000000000001</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>0.21010000000000001</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>1.3754</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>0.43280000000000002</v>
+      </c>
+      <c r="AX7" s="1">
+        <v>0.4143</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>0.28510000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.1888</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3.9087999999999998</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2.9902000000000002</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1.4116</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.9235</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1.6049</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.194</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1.1792</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.27139999999999997</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0.36930000000000002</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0.86760000000000004</v>
+      </c>
+      <c r="N8" s="28">
+        <v>2.8721999999999998E-12</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0.1908</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>2.621</v>
+      </c>
+      <c r="R8" s="1">
+        <v>1.4684999999999999</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0.36630000000000001</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0.17019999999999999</v>
+      </c>
+      <c r="V8" s="1">
+        <v>0.55969999999999998</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0.23630000000000001</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0.24560000000000001</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0.28670000000000001</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0.22159999999999999</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>0.35460000000000003</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0.63539999999999996</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>0.43190000000000001</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>4.3151000000000002</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>0.56040000000000001</v>
+      </c>
+      <c r="AJ8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>0.40939999999999999</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>3.2928999999999999</v>
+      </c>
+      <c r="AM8" s="1">
+        <v>0.5202</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>6.4207000000000001</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>0.64510000000000001</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>1.4396</v>
+      </c>
+      <c r="AQ8" s="1">
+        <v>0.52339999999999998</v>
+      </c>
+      <c r="AR8" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="AS8" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="AT8" s="1">
+        <v>0.58220000000000005</v>
+      </c>
+      <c r="AU8" s="1">
+        <v>0.6079</v>
+      </c>
+      <c r="AV8" s="1">
+        <v>0.82430000000000003</v>
+      </c>
+      <c r="AW8" s="1">
+        <v>0.68240000000000001</v>
+      </c>
+      <c r="AX8" s="1">
+        <v>0.97860000000000003</v>
+      </c>
+      <c r="AY8" s="1">
+        <v>0.73360000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1">
+        <v>3.8849999999999998</v>
+      </c>
+      <c r="E9" s="1">
+        <v>6.2121000000000004</v>
+      </c>
+      <c r="F9" s="1">
+        <v>3.3452000000000002</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4.7830000000000004</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1.3882000000000001</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.6618999999999999</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2.1051000000000002</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.0148999999999999</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0.62109999999999999</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1.6282000000000001</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0.2452</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0.28810000000000002</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0.60409999999999997</v>
+      </c>
+      <c r="R9" s="1">
+        <v>2.7989999999999999</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0.54090000000000005</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0.87319999999999998</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0.39510000000000001</v>
+      </c>
+      <c r="V9" s="1">
+        <v>0.36430000000000001</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0.38490000000000002</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0.50229999999999997</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>0.44579999999999997</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>0.84340000000000004</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0.39150000000000001</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>2.0506000000000002</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>4.1798999999999999</v>
+      </c>
+      <c r="AG9" s="28">
+        <v>7.5494999999999995E-17</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0.5252</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>0.88739999999999997</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="28">
+        <v>1.6954000000000001E-8</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>0.56930000000000003</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>1.0162</v>
+      </c>
+      <c r="AO9" s="28">
+        <v>6.2172000000000005E-17</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>0.94279999999999997</v>
+      </c>
+      <c r="AQ9" s="1">
+        <v>1.1197999999999999</v>
+      </c>
+      <c r="AR9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV9" s="1">
+        <v>1.0342</v>
+      </c>
+      <c r="AW9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="28">
+        <v>1.6679999999999999E-4</v>
+      </c>
+      <c r="AY9" s="1">
+        <v>1.7331000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1">
+        <v>6.5934999999999997</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3.9708999999999999</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.7565</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2.1267</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.8552999999999999</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1.9495</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.94169999999999998</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0.85440000000000005</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1.4011</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1.8972</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1.9249000000000001</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0.34010000000000001</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0.57469999999999999</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0.48849999999999999</v>
+      </c>
+      <c r="T10" s="28">
+        <v>4.9569999999999997E-14</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0.88549999999999995</v>
+      </c>
+      <c r="V10" s="1">
+        <v>1.1872</v>
+      </c>
+      <c r="W10" s="1">
+        <v>1.9753000000000001</v>
+      </c>
+      <c r="X10" s="1">
+        <v>1.1806000000000001</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0.66149999999999998</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>2.3E-3</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0.73970000000000002</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0.74370000000000003</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>0.70089999999999997</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>2.9554</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>1.5248999999999999</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>0.68279999999999996</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>0.39810000000000001</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>1.9433</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>0.95089999999999997</v>
+      </c>
+      <c r="AK10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>1.7458</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>1.2222999999999999</v>
+      </c>
+      <c r="AP10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ10" s="1">
+        <v>1.4177</v>
+      </c>
+      <c r="AR10" s="1">
+        <v>1.2301</v>
+      </c>
+      <c r="AS10" s="1">
+        <v>0.93810000000000004</v>
+      </c>
+      <c r="AT10" s="1">
+        <v>0.90229999999999999</v>
+      </c>
+      <c r="AU10" s="28">
+        <v>4.6494E-12</v>
+      </c>
+      <c r="AV10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW10" s="1">
+        <v>2.3016000000000001</v>
+      </c>
+      <c r="AX10" s="1">
+        <v>1.1776</v>
+      </c>
+      <c r="AY10" s="1">
+        <v>0.63449999999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="28">
+        <v>5.7084000000000001</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3.5228000000000002</v>
+      </c>
+      <c r="H11" s="1">
+        <v>3.4794</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.53779999999999994</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2.8347000000000002</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2.6903000000000001</v>
+      </c>
+      <c r="L11" s="1">
+        <v>4.7827999999999999</v>
+      </c>
+      <c r="M11" s="1">
+        <v>2.387</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1.1605000000000001</v>
+      </c>
+      <c r="O11" s="1">
+        <v>1.9159999999999999</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1.4534</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>2.6374</v>
+      </c>
+      <c r="R11" s="1">
+        <v>1.0477000000000001</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0.75649999999999995</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0.86670000000000003</v>
+      </c>
+      <c r="U11" s="1">
+        <v>1.5668</v>
+      </c>
+      <c r="V11" s="28">
+        <v>3.2862999999999998E-16</v>
+      </c>
+      <c r="W11" s="1">
+        <v>2.6602999999999999</v>
+      </c>
+      <c r="X11" s="1">
+        <v>1.7577</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>0.55930000000000002</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0.98450000000000004</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>0.62560000000000004</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>1.1798999999999999</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>0.89459999999999995</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>0.82179999999999997</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>0.8911</v>
+      </c>
+      <c r="AF11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>0.78390000000000004</v>
+      </c>
+      <c r="AH11" s="1">
+        <v>0.97309999999999997</v>
+      </c>
+      <c r="AI11" s="1">
+        <v>0.50029999999999997</v>
+      </c>
+      <c r="AJ11" s="1">
+        <v>1.0402</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>1.0073000000000001</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>4.8658999999999999</v>
+      </c>
+      <c r="AM11" s="28">
+        <v>7.2440000000000002E-13</v>
+      </c>
+      <c r="AN11" s="1">
+        <v>4.0883000000000003</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>5.91E-2</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>1.1760999999999999</v>
+      </c>
+      <c r="AQ11" s="1">
+        <v>3.1154999999999999</v>
+      </c>
+      <c r="AR11" s="1">
+        <v>3.1511999999999998</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>6.2747000000000002</v>
+      </c>
+      <c r="AT11" s="28">
+        <v>4.9342000000000001E-14</v>
+      </c>
+      <c r="AU11" s="1">
+        <v>5.1928000000000001</v>
+      </c>
+      <c r="AV11" s="1">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="AW11" s="1">
+        <v>2.0621</v>
+      </c>
+      <c r="AX11" s="1">
+        <v>1.0154000000000001</v>
+      </c>
+      <c r="AY11" s="28">
+        <v>9.8405999999999995E-14</v>
+      </c>
+    </row>
+    <row r="12" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="28">
+        <v>2.2482000000000002</v>
+      </c>
+      <c r="H12" s="28">
+        <v>3.8944000000000001</v>
+      </c>
+      <c r="I12" s="1">
+        <v>5.2839</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2.1116999999999999</v>
+      </c>
+      <c r="K12" s="1">
+        <v>3.6751</v>
+      </c>
+      <c r="L12" s="1">
+        <v>2.8553999999999999</v>
+      </c>
+      <c r="M12" s="1">
+        <v>2.7161</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1.5026999999999999</v>
+      </c>
+      <c r="O12" s="1">
+        <v>2.8572000000000002</v>
+      </c>
+      <c r="P12" s="1">
+        <v>4.8402000000000003</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>6.2297000000000002</v>
+      </c>
+      <c r="R12" s="1">
+        <v>4.9635999999999996</v>
+      </c>
+      <c r="S12" s="28">
+        <v>9.9256999999999996E-14</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0.6482</v>
+      </c>
+      <c r="U12" s="1">
+        <v>1.5059</v>
+      </c>
+      <c r="V12" s="1">
+        <v>5.9149000000000003</v>
+      </c>
+      <c r="W12" s="1">
+        <v>3.4169999999999998</v>
+      </c>
+      <c r="X12" s="1">
+        <v>2.2343000000000002</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>0.69650000000000001</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>1.3874</v>
+      </c>
+      <c r="AA12" s="28">
+        <v>1.8679999999999999E-4</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>0.94389999999999996</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>1.9322999999999999</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>1.3861000000000001</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>1.7461</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>1.5733999999999999</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>8.4276999999999997</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>2E-3</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>1.9380999999999999</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>2.1078999999999999</v>
+      </c>
+      <c r="AM12" s="1">
+        <v>2.1017999999999999</v>
+      </c>
+      <c r="AN12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>13.4237</v>
+      </c>
+      <c r="AP12" s="1">
+        <v>2.5270999999999999</v>
+      </c>
+      <c r="AQ12" s="1">
+        <v>1.2738</v>
+      </c>
+      <c r="AR12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="28">
+        <v>1.0658E-16</v>
+      </c>
+      <c r="AT12" s="1">
+        <v>2.3751000000000002</v>
+      </c>
+      <c r="AU12" s="1">
+        <v>10.742900000000001</v>
+      </c>
+      <c r="AV12" s="1">
+        <v>1.3691</v>
+      </c>
+      <c r="AW12" s="28">
+        <v>1.5084E-5</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>4.9781000000000004</v>
+      </c>
+      <c r="AY12" s="1">
+        <v>4.2257999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="1">
+        <v>14.4291</v>
+      </c>
+      <c r="J13" s="1">
+        <v>6.1852</v>
+      </c>
+      <c r="K13" s="1">
+        <v>10.341200000000001</v>
+      </c>
+      <c r="L13" s="1">
+        <v>4.7329999999999997</v>
+      </c>
+      <c r="M13" s="1">
+        <v>2.1503999999999999</v>
+      </c>
+      <c r="N13" s="1">
+        <v>2.9497</v>
+      </c>
+      <c r="O13" s="1">
+        <v>4.4478</v>
+      </c>
+      <c r="P13" s="1">
+        <v>2.8793000000000002</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>9.6168999999999993</v>
+      </c>
+      <c r="R13" s="1">
+        <v>3.8395000000000001</v>
+      </c>
+      <c r="S13" s="1">
+        <v>1.7901</v>
+      </c>
+      <c r="T13" s="1">
+        <v>3.8222</v>
+      </c>
+      <c r="U13" s="1">
+        <v>24.678899999999999</v>
+      </c>
+      <c r="V13" s="1">
+        <v>2.7585999999999999</v>
+      </c>
+      <c r="W13" s="1">
+        <v>13.604699999999999</v>
+      </c>
+      <c r="X13" s="1">
+        <v>2.6004</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>2.48</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>0.22359999999999999</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>2.1991999999999998</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>0.39579999999999999</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>6.2619999999999996</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>13.936999999999999</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>0.90180000000000005</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>0.95750000000000002</v>
+      </c>
+      <c r="AG13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>0.51080000000000003</v>
+      </c>
+      <c r="AI13" s="28">
+        <v>6.6130999999999996E-10</v>
+      </c>
+      <c r="AJ13" s="28">
+        <v>3.8858E-16</v>
+      </c>
+      <c r="AK13" s="1">
+        <v>15.8522</v>
+      </c>
+      <c r="AL13" s="1">
+        <v>5.8545999999999996</v>
+      </c>
+      <c r="AM13" s="1">
+        <v>2.9828000000000001</v>
+      </c>
+      <c r="AN13" s="1">
+        <v>38.828699999999998</v>
+      </c>
+      <c r="AO13" s="1">
+        <v>1.0666</v>
+      </c>
+      <c r="AP13" s="1">
+        <v>0.66869999999999996</v>
+      </c>
+      <c r="AQ13" s="1">
+        <v>1.1839</v>
+      </c>
+      <c r="AR13" s="1">
+        <v>1.2215</v>
+      </c>
+      <c r="AS13" s="1">
+        <v>13.1357</v>
+      </c>
+      <c r="AT13" s="1">
+        <v>34.671199999999999</v>
+      </c>
+      <c r="AU13" s="1">
+        <v>6.2782</v>
+      </c>
+      <c r="AV13" s="28">
+        <v>9.9183000000000003E-14</v>
+      </c>
+      <c r="AW13" s="28">
+        <v>6.3061000000000001E-16</v>
+      </c>
+      <c r="AX13" s="1">
+        <v>21.1496</v>
+      </c>
+      <c r="AY13" s="1">
+        <v>1.4510000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="1">
+        <v>14.7263</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0.48359999999999997</v>
+      </c>
+      <c r="N14" s="1">
+        <v>11.6005</v>
+      </c>
+      <c r="O14" s="1">
+        <v>15.3027</v>
+      </c>
+      <c r="P14" s="1">
+        <v>43.913400000000003</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>14.9612</v>
+      </c>
+      <c r="R14" s="1">
+        <v>4.6788999999999996</v>
+      </c>
+      <c r="S14" s="1">
+        <v>6.2796000000000003</v>
+      </c>
+      <c r="T14" s="1">
+        <v>9.6432000000000002</v>
+      </c>
+      <c r="U14" s="1">
+        <v>51.548400000000001</v>
+      </c>
+      <c r="V14" s="28">
+        <v>1.1408E-5</v>
+      </c>
+      <c r="W14" s="1">
+        <v>21.5229</v>
+      </c>
+      <c r="X14" s="1">
+        <v>2.9426999999999999</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>27.292400000000001</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>20.045000000000002</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>5.4419000000000004</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>33.802100000000003</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>47.579700000000003</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>29.305399999999999</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>1.3345</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>21.610499999999998</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>2.5678000000000001</v>
+      </c>
+      <c r="AH14" s="1">
+        <v>2.3793000000000002</v>
+      </c>
+      <c r="AI14" s="1">
+        <v>16.147300000000001</v>
+      </c>
+      <c r="AJ14" s="1">
+        <v>1.2095</v>
+      </c>
+      <c r="AK14" s="1">
+        <v>74.941500000000005</v>
+      </c>
+      <c r="AL14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="28">
+        <v>3.0071999999999998E-4</v>
+      </c>
+      <c r="AN14" s="1">
+        <v>1.3160000000000001</v>
+      </c>
+      <c r="AO14" s="28">
+        <v>7.3287999999999999E-4</v>
+      </c>
+      <c r="AP14" s="1">
+        <v>5.0194000000000001</v>
+      </c>
+      <c r="AQ14" s="1">
+        <v>38.413699999999999</v>
+      </c>
+      <c r="AR14" s="1">
+        <v>100.9654</v>
+      </c>
+      <c r="AS14" s="1">
+        <v>1.3474999999999999</v>
+      </c>
+      <c r="AT14" s="28">
+        <v>1.3867E-15</v>
+      </c>
+      <c r="AU14" s="1">
+        <v>7.4104000000000001</v>
+      </c>
+      <c r="AV14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="1">
+        <v>2.5329999999999999</v>
+      </c>
+      <c r="AX14" s="1">
+        <v>1.4908999999999999</v>
+      </c>
+      <c r="AY14" s="1">
+        <v>11.254099999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="1">
+        <v>134.4787</v>
+      </c>
+      <c r="S15" s="1">
+        <v>2.8925000000000001</v>
+      </c>
+      <c r="T15" s="1">
+        <v>160.3175</v>
+      </c>
+      <c r="U15" s="1">
+        <v>10.509499999999999</v>
+      </c>
+      <c r="V15" s="1">
+        <v>89.633899999999997</v>
+      </c>
+      <c r="W15" s="1">
+        <v>150.1146</v>
+      </c>
+      <c r="X15" s="1">
+        <v>6.7298</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>5.0404</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>67.253900000000002</v>
+      </c>
+      <c r="AA15" s="28">
+        <v>1.4794999999999999E-8</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>221.55369999999999</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>2.8452999999999999</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>2.7501000000000002</v>
+      </c>
+      <c r="AE15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="1">
+        <v>8.4471000000000007</v>
+      </c>
+      <c r="AG15" s="1">
+        <v>1.1531</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>3.3759000000000001</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>1.8809</v>
+      </c>
+      <c r="AJ15" s="1">
+        <v>3.0916000000000001</v>
+      </c>
+      <c r="AK15" s="1">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="AL15" s="1">
+        <v>77.834699999999998</v>
+      </c>
+      <c r="AM15" s="1">
+        <v>2.5325000000000002</v>
+      </c>
+      <c r="AN15" s="1">
+        <v>29.884899999999998</v>
+      </c>
+      <c r="AO15" s="1">
+        <v>1.8037000000000001</v>
+      </c>
+      <c r="AP15" s="1">
+        <v>0.58989999999999998</v>
+      </c>
+      <c r="AQ15" s="1">
+        <v>11.464700000000001</v>
+      </c>
+      <c r="AR15" s="1">
+        <v>6.9961000000000002</v>
+      </c>
+      <c r="AS15" s="1">
+        <v>0.56259999999999999</v>
+      </c>
+      <c r="AT15" s="1">
+        <v>13.069000000000001</v>
+      </c>
+      <c r="AU15" s="1">
+        <v>5.1165000000000003</v>
+      </c>
+      <c r="AV15" s="1">
+        <v>12.5739</v>
+      </c>
+      <c r="AW15" s="28">
+        <v>1.4433E-16</v>
+      </c>
+      <c r="AX15" s="28">
+        <v>1.6875000000000001E-16</v>
+      </c>
+      <c r="AY15" s="1">
+        <v>491.94220000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="30" t="s">
+        <v>661</v>
+      </c>
+      <c r="C19" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>663</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C3:AY15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="10"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/files/Controller Design/ZNMethods_ITAE_Errors.xlsx
+++ b/files/Controller Design/ZNMethods_ITAE_Errors.xlsx
@@ -8,17 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ulisboa-my.sharepoint.com/personal/ist1100262_tecnico_ulisboa_pt/Documents/MEMec/Thesis/files/Controller Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="8_{95F32091-D855-4402-ADD3-8991BE5FE270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B41285B-FE26-4CBF-88BF-4A2E64C0AD6D}"/>
+  <xr:revisionPtr revIDLastSave="271" documentId="8_{95F32091-D855-4402-ADD3-8991BE5FE270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC88825A-C231-41EC-85FA-D7AFBE30E740}"/>
   <bookViews>
-    <workbookView xWindow="-3696" yWindow="-17388" windowWidth="30936" windowHeight="17496" activeTab="5" xr2:uid="{6BCB78A0-0C46-4270-8084-079A19E30873}"/>
+    <workbookView xWindow="-3696" yWindow="-17388" windowWidth="30936" windowHeight="17496" activeTab="8" xr2:uid="{6BCB78A0-0C46-4270-8084-079A19E30873}"/>
   </bookViews>
   <sheets>
-    <sheet name="CritGain" sheetId="1" r:id="rId1"/>
+    <sheet name="ZNMethods" sheetId="1" r:id="rId1"/>
     <sheet name="PID_Models" sheetId="3" r:id="rId2"/>
     <sheet name="Gains" sheetId="5" r:id="rId3"/>
     <sheet name="PID_Models_Noise" sheetId="6" r:id="rId4"/>
     <sheet name="id_ctrl_val" sheetId="7" r:id="rId5"/>
     <sheet name="id_ctrl_noise" sheetId="8" r:id="rId6"/>
+    <sheet name="FO_PID" sheetId="9" r:id="rId7"/>
+    <sheet name="FO_id_ctrl" sheetId="10" r:id="rId8"/>
+    <sheet name="FO_id_ctrl_noise" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="667">
   <si>
     <t>ν/ζ</t>
   </si>
@@ -2035,10 +2038,16 @@
     <t>Simulations kept over 30 seconds</t>
   </si>
   <si>
-    <t>need to add Wcp fallback</t>
-  </si>
-  <si>
-    <t>Noise level 0.03</t>
+    <t>Noise level 0.01 no filter</t>
+  </si>
+  <si>
+    <t>ITAE Error</t>
+  </si>
+  <si>
+    <t>ITAE error</t>
+  </si>
+  <si>
+    <t>This is simulating controlling a system with noise inputted to the feedback loop to simulate reading a system thrugh a noisy sensor</t>
   </si>
 </sst>
 </file>
@@ -2478,7 +2487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -2536,6 +2545,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -20093,7 +20103,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29424509-3824-4FC3-A99C-410B82A3A8E8}">
-  <dimension ref="B1:AY20"/>
+  <dimension ref="B1:AY21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="51" width="6.44140625" customWidth="1"/>
@@ -22386,6 +22396,11 @@
       </c>
       <c r="C20" t="s">
         <v>662</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
+        <v>666</v>
       </c>
     </row>
   </sheetData>
@@ -22407,7 +22422,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E237936-F695-4675-B42C-B0BF8FA4F476}">
-  <dimension ref="B1:AY15"/>
+  <dimension ref="B1:AY17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="51" width="6.109375" customWidth="1"/>
@@ -24542,8 +24557,13 @@
         <v>5.0271999999999997</v>
       </c>
     </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C17" s="37" t="s">
+        <v>664</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C3:AY15">
+  <conditionalFormatting sqref="C3:AY15 C17">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -24728,43 +24748,43 @@
         <v>0.41610000000000003</v>
       </c>
       <c r="D3" s="1">
-        <v>0.11559999999999999</v>
+        <v>0.17780000000000001</v>
       </c>
       <c r="E3" s="1">
-        <v>0.2923</v>
+        <v>0.2036</v>
       </c>
       <c r="F3" s="1">
-        <v>0.1144</v>
+        <v>0.151</v>
       </c>
       <c r="G3" s="1">
-        <v>0.12039999999999999</v>
+        <v>0.24540000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>0.1719</v>
+        <v>0.14560000000000001</v>
       </c>
       <c r="I3" s="1">
-        <v>0.15890000000000001</v>
+        <v>0.1618</v>
       </c>
       <c r="J3" s="1">
-        <v>0.1792</v>
+        <v>0.17230000000000001</v>
       </c>
       <c r="K3" s="1">
-        <v>0.17929999999999999</v>
+        <v>0.2009</v>
       </c>
       <c r="L3" s="1">
-        <v>0.23169999999999999</v>
+        <v>0.22470000000000001</v>
       </c>
       <c r="M3" s="1">
-        <v>0.26669999999999999</v>
+        <v>0.28179999999999999</v>
       </c>
       <c r="N3" s="1">
-        <v>0.32169999999999999</v>
+        <v>0.34870000000000001</v>
       </c>
       <c r="O3" s="1">
-        <v>0.44</v>
+        <v>0.38350000000000001</v>
       </c>
       <c r="P3" s="1">
-        <v>0.40039999999999998</v>
+        <v>0.3972</v>
       </c>
       <c r="Q3" s="1" t="s">
         <v>10</v>
@@ -24877,79 +24897,79 @@
         <v>0.8</v>
       </c>
       <c r="C4" s="1">
-        <v>0.59670000000000001</v>
+        <v>0.75290000000000001</v>
       </c>
       <c r="D4" s="1">
-        <v>5.11E-2</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>1</v>
+        <v>0.63380000000000003</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3.49E-2</v>
       </c>
       <c r="F4" s="1">
-        <v>4.7E-2</v>
+        <v>7.5899999999999995E-2</v>
       </c>
       <c r="G4" s="1">
-        <v>7.6300000000000007E-2</v>
+        <v>0.1031</v>
       </c>
       <c r="H4" s="1">
-        <v>7.2300000000000003E-2</v>
+        <v>0.1074</v>
       </c>
       <c r="I4" s="1">
-        <v>8.3299999999999999E-2</v>
+        <v>0.13919999999999999</v>
       </c>
       <c r="J4" s="1">
-        <v>9.5100000000000004E-2</v>
+        <v>0.109</v>
       </c>
       <c r="K4" s="1">
-        <v>8.9899999999999994E-2</v>
+        <v>0.1166</v>
       </c>
       <c r="L4" s="1">
-        <v>0.17249999999999999</v>
+        <v>0.1275</v>
       </c>
       <c r="M4" s="1">
-        <v>9.9099999999999994E-2</v>
+        <v>0.1452</v>
       </c>
       <c r="N4" s="1">
-        <v>0.1168</v>
+        <v>0.1434</v>
       </c>
       <c r="O4" s="1">
-        <v>0.16339999999999999</v>
+        <v>0.15640000000000001</v>
       </c>
       <c r="P4" s="1">
-        <v>0.15479999999999999</v>
+        <v>0.11509999999999999</v>
       </c>
       <c r="Q4" s="1">
-        <v>0.1258</v>
+        <v>0.30170000000000002</v>
       </c>
       <c r="R4" s="1">
-        <v>0.25340000000000001</v>
+        <v>0.29060000000000002</v>
       </c>
       <c r="S4" s="1">
-        <v>0.47199999999999998</v>
+        <v>0.26829999999999998</v>
       </c>
       <c r="T4" s="1">
-        <v>0.16370000000000001</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="U4" s="1">
-        <v>0.2223</v>
+        <v>0.77859999999999996</v>
       </c>
       <c r="V4" s="1">
-        <v>0.24360000000000001</v>
+        <v>0.93889999999999996</v>
       </c>
       <c r="W4" s="1">
-        <v>0.23719999999999999</v>
+        <v>0.99380000000000002</v>
       </c>
       <c r="X4" s="1">
-        <v>0.25219999999999998</v>
+        <v>1.1475</v>
       </c>
       <c r="Y4" s="1">
-        <v>0.27900000000000003</v>
+        <v>1.1680999999999999</v>
       </c>
       <c r="Z4" s="1">
-        <v>0.2064</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>10</v>
+        <v>1.054</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>1.0703</v>
       </c>
       <c r="AB4" s="1" t="s">
         <v>10</v>
@@ -25029,130 +25049,130 @@
         <v>0.9</v>
       </c>
       <c r="C5" s="1">
-        <v>1.8207</v>
+        <v>1.0176000000000001</v>
       </c>
       <c r="D5" s="1">
-        <v>1.1791</v>
+        <v>1.2543</v>
       </c>
       <c r="E5" s="1">
-        <v>0.26729999999999998</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>0.78559999999999997</v>
+        <v>8.2299999999999998E-2</v>
       </c>
       <c r="G5" s="1">
-        <v>0.58189999999999997</v>
+        <v>0.40050000000000002</v>
       </c>
       <c r="H5" s="1">
-        <v>3.04E-2</v>
+        <v>5.6899999999999999E-2</v>
       </c>
       <c r="I5" s="1">
-        <v>0.1696</v>
+        <v>0.15679999999999999</v>
       </c>
       <c r="J5" s="1">
-        <v>4.3499999999999997E-2</v>
+        <v>5.3900000000000003E-2</v>
       </c>
       <c r="K5" s="1">
-        <v>4.7399999999999998E-2</v>
+        <v>4.8599999999999997E-2</v>
       </c>
       <c r="L5" s="1">
-        <v>4.3700000000000003E-2</v>
+        <v>5.7700000000000001E-2</v>
       </c>
       <c r="M5" s="1">
-        <v>4.87E-2</v>
+        <v>5.4399999999999997E-2</v>
       </c>
       <c r="N5" s="1">
-        <v>0.4173</v>
+        <v>7.9399999999999998E-2</v>
       </c>
       <c r="O5" s="1">
-        <v>0.10489999999999999</v>
+        <v>9.6299999999999997E-2</v>
       </c>
       <c r="P5" s="1">
-        <v>0.1308</v>
+        <v>0.434</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.1522</v>
+        <v>0.28149999999999997</v>
       </c>
       <c r="R5" s="1">
-        <v>8.1100000000000005E-2</v>
+        <v>0.42030000000000001</v>
       </c>
       <c r="S5" s="1">
-        <v>9.4299999999999995E-2</v>
+        <v>1.1366000000000001</v>
       </c>
       <c r="T5" s="1">
+        <v>1.0929</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0.99980000000000002</v>
+      </c>
+      <c r="V5" s="1">
+        <v>1.0789</v>
+      </c>
+      <c r="W5" s="1">
+        <v>1.1588000000000001</v>
+      </c>
+      <c r="X5" s="1">
+        <v>1.0157</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>0.68120000000000003</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>1.0490999999999999</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>9.4643999999999995</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>21.874600000000001</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>0.55389999999999995</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0.48349999999999999</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>0.187</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="AH5" s="1">
         <v>0.2671</v>
       </c>
-      <c r="U5" s="1">
-        <v>0.24640000000000001</v>
-      </c>
-      <c r="V5" s="1">
-        <v>0.18210000000000001</v>
-      </c>
-      <c r="W5" s="1">
-        <v>0.19539999999999999</v>
-      </c>
-      <c r="X5" s="1">
-        <v>0.1041</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>0.30940000000000001</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>0.124</v>
-      </c>
-      <c r="AA5" s="1">
-        <v>0.1285</v>
-      </c>
-      <c r="AB5" s="1">
-        <v>0.36449999999999999</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>0.31759999999999999</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>0.1986</v>
-      </c>
-      <c r="AE5" s="1">
-        <v>1.0629</v>
-      </c>
-      <c r="AF5" s="1">
-        <v>0.15060000000000001</v>
-      </c>
-      <c r="AG5" s="1">
-        <v>0.63370000000000004</v>
-      </c>
-      <c r="AH5" s="1">
-        <v>0.36199999999999999</v>
-      </c>
       <c r="AI5" s="1">
-        <v>1.14E-2</v>
+        <v>0.18540000000000001</v>
       </c>
       <c r="AJ5" s="1">
-        <v>0.94020000000000004</v>
+        <v>0.62809999999999999</v>
       </c>
       <c r="AK5" s="1">
-        <v>0.83409999999999995</v>
+        <v>0.4582</v>
       </c>
       <c r="AL5" s="1">
-        <v>0.215</v>
+        <v>0.20710000000000001</v>
       </c>
       <c r="AM5" s="1">
-        <v>0.187</v>
+        <v>0.19189999999999999</v>
       </c>
       <c r="AN5" s="1">
-        <v>0.21260000000000001</v>
+        <v>0.69630000000000003</v>
       </c>
       <c r="AO5" s="1">
-        <v>0.86419999999999997</v>
+        <v>0.69499999999999995</v>
       </c>
       <c r="AP5" s="1">
-        <v>0.34670000000000001</v>
+        <v>0.62419999999999998</v>
       </c>
       <c r="AQ5" s="1">
-        <v>0.25929999999999997</v>
-      </c>
-      <c r="AR5" s="28">
-        <v>5.5511E-17</v>
+        <v>0.50829999999999997</v>
+      </c>
+      <c r="AR5" s="28" t="s">
+        <v>10</v>
       </c>
       <c r="AS5" s="1" t="s">
         <v>10</v>
@@ -25181,151 +25201,151 @@
         <v>1</v>
       </c>
       <c r="C6" s="1">
-        <v>2.7145000000000001</v>
+        <v>0.18190000000000001</v>
       </c>
       <c r="D6" s="1">
-        <v>1.1274999999999999</v>
-      </c>
-      <c r="E6" s="1" t="s">
+        <v>1.6163000000000001</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.24160000000000001</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1.0613999999999999</v>
+      </c>
+      <c r="G6" s="1">
+        <v>8.4400000000000003E-2</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="1">
-        <v>0.21510000000000001</v>
-      </c>
-      <c r="G6" s="1">
-        <v>3.8800000000000001E-2</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1.4342999999999999</v>
-      </c>
       <c r="I6" s="1">
-        <v>1.9699999999999999E-2</v>
+        <v>1.34E-2</v>
       </c>
       <c r="J6" s="1">
-        <v>3.1E-2</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="K6" s="1">
-        <v>9.1800000000000007E-2</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="L6" s="1">
-        <v>9.1999999999999998E-3</v>
+        <v>2.87E-2</v>
       </c>
       <c r="M6" s="1">
-        <v>1.5100000000000001E-2</v>
+        <v>6.6100000000000006E-2</v>
       </c>
       <c r="N6" s="1">
-        <v>5.11E-2</v>
+        <v>0.31109999999999999</v>
       </c>
       <c r="O6" s="1">
-        <v>4.6399999999999997E-2</v>
+        <v>0.36109999999999998</v>
       </c>
       <c r="P6" s="1">
-        <v>2.2800000000000001E-2</v>
+        <v>0.43840000000000001</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.2198</v>
+        <v>0.46610000000000001</v>
       </c>
       <c r="R6" s="1">
-        <v>2.9399999999999999E-2</v>
+        <v>0.75700000000000001</v>
       </c>
       <c r="S6" s="1">
-        <v>0.34899999999999998</v>
+        <v>0.57040000000000002</v>
       </c>
       <c r="T6" s="1">
-        <v>0.1923</v>
+        <v>0.75049999999999994</v>
       </c>
       <c r="U6" s="1">
-        <v>0.14729999999999999</v>
+        <v>0.2833</v>
       </c>
       <c r="V6" s="1">
-        <v>0.2253</v>
+        <v>0.22739999999999999</v>
       </c>
       <c r="W6" s="28">
-        <v>5476.3</v>
+        <v>0.31330000000000002</v>
       </c>
       <c r="X6" s="1">
-        <v>0.14729999999999999</v>
+        <v>0.60589999999999999</v>
       </c>
       <c r="Y6" s="1">
-        <v>9.0700000000000003E-2</v>
+        <v>0.76290000000000002</v>
       </c>
       <c r="Z6" s="1">
-        <v>6.6400000000000001E-2</v>
+        <v>7.4099999999999999E-2</v>
       </c>
       <c r="AA6" s="1">
-        <v>0.21729999999999999</v>
+        <v>6.3799999999999996E-2</v>
       </c>
       <c r="AB6" s="1">
-        <v>0.90790000000000004</v>
+        <v>4.48E-2</v>
       </c>
       <c r="AC6" s="1">
-        <v>0.72219999999999995</v>
+        <v>0.21679999999999999</v>
       </c>
       <c r="AD6" s="1">
-        <v>0.91349999999999998</v>
+        <v>0.84489999999999998</v>
       </c>
       <c r="AE6" s="1">
-        <v>0.85070000000000001</v>
+        <v>0.41749999999999998</v>
       </c>
       <c r="AF6" s="1">
-        <v>0.84530000000000005</v>
+        <v>0.69240000000000002</v>
       </c>
       <c r="AG6" s="1">
-        <v>0.2452</v>
+        <v>0.44319999999999998</v>
       </c>
       <c r="AH6" s="1">
-        <v>0.22</v>
+        <v>0.53180000000000005</v>
       </c>
       <c r="AI6" s="1">
-        <v>0.51759999999999995</v>
+        <v>0.17019999999999999</v>
       </c>
       <c r="AJ6" s="1">
-        <v>9.06E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="AK6" s="1">
-        <v>0.1358</v>
+        <v>0.15509999999999999</v>
       </c>
       <c r="AL6" s="1">
-        <v>0.79059999999999997</v>
+        <v>0.1845</v>
       </c>
       <c r="AM6" s="1">
-        <v>0.48</v>
+        <v>0.17710000000000001</v>
       </c>
       <c r="AN6" s="1">
-        <v>0.58889999999999998</v>
+        <v>0.62790000000000001</v>
       </c>
       <c r="AO6" s="1">
-        <v>0.4824</v>
+        <v>0.46539999999999998</v>
       </c>
       <c r="AP6" s="1">
-        <v>0.89700000000000002</v>
+        <v>0.74760000000000004</v>
       </c>
       <c r="AQ6" s="1">
-        <v>0.71140000000000003</v>
+        <v>0.63880000000000003</v>
       </c>
       <c r="AR6" s="1">
-        <v>0.57050000000000001</v>
+        <v>0.31290000000000001</v>
       </c>
       <c r="AS6" s="1">
-        <v>0.47410000000000002</v>
+        <v>0.60540000000000005</v>
       </c>
       <c r="AT6" s="1">
-        <v>0.2331</v>
+        <v>0.61880000000000002</v>
       </c>
       <c r="AU6" s="28">
-        <v>1.3718000000000001E-8</v>
+        <v>0.54149999999999998</v>
       </c>
       <c r="AV6" s="1">
-        <v>0.19109999999999999</v>
+        <v>0.34620000000000001</v>
       </c>
       <c r="AW6" s="1">
-        <v>0.58150000000000002</v>
+        <v>0.33760000000000001</v>
       </c>
       <c r="AX6" s="1">
-        <v>0.5353</v>
+        <v>0.29409999999999997</v>
       </c>
       <c r="AY6" s="1">
-        <v>0.3715</v>
+        <v>0.42649999999999999</v>
       </c>
     </row>
     <row r="7" spans="2:51" x14ac:dyDescent="0.3">
@@ -25333,151 +25353,151 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="C7" s="1">
-        <v>4.0782999999999996</v>
+        <v>3.8108</v>
       </c>
       <c r="D7" s="1">
-        <v>3.2130000000000001</v>
+        <v>2.6926999999999999</v>
       </c>
       <c r="E7" s="1">
-        <v>0.105</v>
+        <v>0.44059999999999999</v>
       </c>
       <c r="F7" s="1">
-        <v>2.3033999999999999</v>
+        <v>1.456</v>
       </c>
       <c r="G7" s="1">
-        <v>0.89649999999999996</v>
+        <v>8.1100000000000005E-2</v>
       </c>
       <c r="H7" s="1">
-        <v>0.56699999999999995</v>
+        <v>0.373</v>
       </c>
       <c r="I7" s="1">
-        <v>0.39600000000000002</v>
+        <v>0.30270000000000002</v>
       </c>
       <c r="J7" s="1">
-        <v>2.4318</v>
+        <v>0.21629999999999999</v>
       </c>
       <c r="K7" s="1">
-        <v>0.1091</v>
+        <v>0.1406</v>
       </c>
       <c r="L7" s="1">
-        <v>0.42430000000000001</v>
+        <v>1.1946000000000001</v>
       </c>
       <c r="M7" s="28">
-        <v>5.9971999999999999E-13</v>
-      </c>
-      <c r="N7" s="28">
-        <v>4.9631000000000002E-14</v>
+        <v>0</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>1</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="P7" s="1">
+        <v>0.99780000000000002</v>
+      </c>
+      <c r="Q7" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="Q7" s="28">
-        <v>3.6123999999999998E-12</v>
-      </c>
       <c r="R7" s="1">
-        <v>0.87819999999999998</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>1</v>
+        <v>0.95209999999999995</v>
+      </c>
+      <c r="S7" s="1">
+        <v>2.8405999999999998</v>
       </c>
       <c r="T7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="U7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>1</v>
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0.1517</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0.28050000000000003</v>
       </c>
       <c r="X7" s="1">
-        <v>0.1087</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>1</v>
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0.54320000000000002</v>
       </c>
       <c r="Z7" s="28">
-        <v>1.1102000000000001E-18</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AB7" s="1" t="s">
-        <v>1</v>
+      <c r="AB7" s="1">
+        <v>0.1305</v>
       </c>
       <c r="AC7" s="28">
-        <v>2.7089E-16</v>
+        <v>0.19570000000000001</v>
       </c>
       <c r="AD7" s="1">
-        <v>0.76749999999999996</v>
+        <v>0.1946</v>
       </c>
       <c r="AE7" s="1">
-        <v>0.24709999999999999</v>
+        <v>0.17810000000000001</v>
       </c>
       <c r="AF7" s="1">
-        <v>0.58340000000000003</v>
+        <v>0.1651</v>
       </c>
       <c r="AG7" s="1">
-        <v>0.62219999999999998</v>
+        <v>0.1472</v>
       </c>
       <c r="AH7" s="1">
-        <v>0.1656</v>
+        <v>0.17810000000000001</v>
       </c>
       <c r="AI7" s="1">
-        <v>0.6714</v>
+        <v>0.1822</v>
       </c>
       <c r="AJ7" s="1">
-        <v>0.47039999999999998</v>
+        <v>0.2127</v>
       </c>
       <c r="AK7" s="1">
-        <v>0.1978</v>
+        <v>0.20180000000000001</v>
       </c>
       <c r="AL7" s="1">
-        <v>0.46879999999999999</v>
+        <v>0.22459999999999999</v>
       </c>
       <c r="AM7" s="1">
-        <v>0.57530000000000003</v>
+        <v>0.27760000000000001</v>
       </c>
       <c r="AN7" s="1">
-        <v>0.2429</v>
+        <v>0.45469999999999999</v>
       </c>
       <c r="AO7" s="1">
-        <v>0.30740000000000001</v>
+        <v>0.4602</v>
       </c>
       <c r="AP7" s="1">
-        <v>0.2127</v>
+        <v>0.30159999999999998</v>
       </c>
       <c r="AQ7" s="1">
-        <v>0.4657</v>
+        <v>0.25009999999999999</v>
       </c>
       <c r="AR7" s="1">
-        <v>0.41370000000000001</v>
+        <v>0.4289</v>
       </c>
       <c r="AS7" s="1">
-        <v>0.21440000000000001</v>
+        <v>0.23749999999999999</v>
       </c>
       <c r="AT7" s="1">
-        <v>0.21010000000000001</v>
+        <v>0.34420000000000001</v>
       </c>
       <c r="AU7" s="1">
-        <v>5.5999999999999999E-3</v>
+        <v>0.38600000000000001</v>
       </c>
       <c r="AV7" s="1">
-        <v>1.3754</v>
+        <v>0.28520000000000001</v>
       </c>
       <c r="AW7" s="1">
-        <v>0.43280000000000002</v>
+        <v>0.37490000000000001</v>
       </c>
       <c r="AX7" s="1">
-        <v>0.4143</v>
+        <v>0.22639999999999999</v>
       </c>
       <c r="AY7" s="1">
-        <v>0.28510000000000002</v>
+        <v>0.30480000000000002</v>
       </c>
     </row>
     <row r="8" spans="2:51" x14ac:dyDescent="0.3">
@@ -25485,151 +25505,151 @@
         <v>1.2</v>
       </c>
       <c r="C8" s="1">
-        <v>0.1888</v>
+        <v>3.9497</v>
       </c>
       <c r="D8" s="1">
-        <v>3.9087999999999998</v>
+        <v>4.0537999999999998</v>
       </c>
       <c r="E8" s="1">
-        <v>2.9902000000000002</v>
+        <v>3.4306000000000001</v>
       </c>
       <c r="F8" s="1">
-        <v>1.4116</v>
+        <v>2.4961000000000002</v>
       </c>
       <c r="G8" s="1">
-        <v>1.9235</v>
+        <v>0.30640000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>1.6049</v>
+        <v>1.4925999999999999</v>
       </c>
       <c r="I8" s="1">
-        <v>1.194</v>
+        <v>1.4993000000000001</v>
       </c>
       <c r="J8" s="1">
-        <v>1.1792</v>
+        <v>0.49969999999999998</v>
       </c>
       <c r="K8" s="1">
-        <v>0.27139999999999997</v>
+        <v>0.20269999999999999</v>
       </c>
       <c r="L8" s="1">
-        <v>0.36930000000000002</v>
+        <v>0.28179999999999999</v>
       </c>
       <c r="M8" s="1">
-        <v>0.86760000000000004</v>
+        <v>0.18390000000000001</v>
       </c>
       <c r="N8" s="28">
-        <v>2.8721999999999998E-12</v>
-      </c>
-      <c r="O8" s="1" t="s">
+        <v>1E-4</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0.378</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="P8" s="1">
-        <v>0.1908</v>
-      </c>
       <c r="Q8" s="1">
-        <v>2.621</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="R8" s="1">
-        <v>1.4684999999999999</v>
+        <v>0.24030000000000001</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="T8" s="1">
-        <v>0.36630000000000001</v>
+      <c r="T8" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="U8" s="1">
-        <v>0.17019999999999999</v>
+        <v>0.19189999999999999</v>
       </c>
       <c r="V8" s="1">
-        <v>0.55969999999999998</v>
+        <v>0</v>
       </c>
       <c r="W8" s="1">
-        <v>0.23630000000000001</v>
+        <v>0</v>
       </c>
       <c r="X8" s="1">
-        <v>0.24560000000000001</v>
+        <v>3.7761999999999998</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.22550000000000001</v>
+        <v>0.22220000000000001</v>
       </c>
       <c r="Z8" s="1">
-        <v>0.28670000000000001</v>
+        <v>0.68689999999999996</v>
       </c>
       <c r="AA8" s="1">
-        <v>0.22159999999999999</v>
+        <v>0.29630000000000001</v>
       </c>
       <c r="AB8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AC8" s="1">
-        <v>0.35460000000000003</v>
-      </c>
-      <c r="AD8" s="1" t="s">
+        <v>2.6435</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>37.174599999999998</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>5.3315999999999999</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>0.48449999999999999</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>1.6091</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>5.5441000000000003</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>0.58819999999999995</v>
+      </c>
+      <c r="AM8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AE8" s="1">
-        <v>0.63539999999999996</v>
-      </c>
-      <c r="AF8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="1">
-        <v>0.43190000000000001</v>
-      </c>
-      <c r="AH8" s="1">
-        <v>4.3151000000000002</v>
-      </c>
-      <c r="AI8" s="1">
-        <v>0.56040000000000001</v>
-      </c>
-      <c r="AJ8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AK8" s="1">
-        <v>0.40939999999999999</v>
-      </c>
-      <c r="AL8" s="1">
-        <v>3.2928999999999999</v>
-      </c>
-      <c r="AM8" s="1">
-        <v>0.5202</v>
-      </c>
       <c r="AN8" s="1">
-        <v>6.4207000000000001</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="1">
-        <v>0.64510000000000001</v>
+        <v>0.51380000000000003</v>
       </c>
       <c r="AP8" s="1">
-        <v>1.4396</v>
+        <v>0.61919999999999997</v>
       </c>
       <c r="AQ8" s="1">
-        <v>0.52339999999999998</v>
+        <v>0</v>
       </c>
       <c r="AR8" s="1">
-        <v>0.62</v>
+        <v>0.43909999999999999</v>
       </c>
       <c r="AS8" s="1">
-        <v>0.53</v>
+        <v>1.454</v>
       </c>
       <c r="AT8" s="1">
-        <v>0.58220000000000005</v>
+        <v>0.6492</v>
       </c>
       <c r="AU8" s="1">
-        <v>0.6079</v>
+        <v>0.79120000000000001</v>
       </c>
       <c r="AV8" s="1">
-        <v>0.82430000000000003</v>
+        <v>0.59860000000000002</v>
       </c>
       <c r="AW8" s="1">
-        <v>0.68240000000000001</v>
+        <v>0.79579999999999995</v>
       </c>
       <c r="AX8" s="1">
-        <v>0.97860000000000003</v>
+        <v>0.43259999999999998</v>
       </c>
       <c r="AY8" s="1">
-        <v>0.73360000000000003</v>
+        <v>0.81810000000000005</v>
       </c>
     </row>
     <row r="9" spans="2:51" x14ac:dyDescent="0.3">
@@ -25640,148 +25660,148 @@
         <v>10</v>
       </c>
       <c r="D9" s="1">
-        <v>3.8849999999999998</v>
+        <v>3.6438999999999999</v>
       </c>
       <c r="E9" s="1">
-        <v>6.2121000000000004</v>
+        <v>3.6453000000000002</v>
       </c>
       <c r="F9" s="1">
-        <v>3.3452000000000002</v>
+        <v>4.1271000000000004</v>
       </c>
       <c r="G9" s="1">
-        <v>4.7830000000000004</v>
+        <v>0.79430000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>1.3882000000000001</v>
+        <v>2.5872999999999999</v>
       </c>
       <c r="I9" s="1">
-        <v>1.6618999999999999</v>
+        <v>0.42980000000000002</v>
       </c>
       <c r="J9" s="1">
-        <v>2.1051000000000002</v>
+        <v>1.0133000000000001</v>
       </c>
       <c r="K9" s="1">
-        <v>1.0148999999999999</v>
+        <v>0.44409999999999999</v>
       </c>
       <c r="L9" s="1">
-        <v>0.62109999999999999</v>
+        <v>1.4812000000000001</v>
       </c>
       <c r="M9" s="1">
-        <v>1.6282000000000001</v>
+        <v>0.4163</v>
       </c>
       <c r="N9" s="1">
-        <v>0.2452</v>
+        <v>0.44230000000000003</v>
       </c>
       <c r="O9" s="1">
-        <v>0.28810000000000002</v>
+        <v>0.42730000000000001</v>
       </c>
       <c r="P9" s="1">
-        <v>0.42299999999999999</v>
+        <v>5.4199999999999998E-2</v>
       </c>
       <c r="Q9" s="1">
-        <v>0.60409999999999997</v>
+        <v>0.6915</v>
       </c>
       <c r="R9" s="1">
-        <v>2.7989999999999999</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0.54090000000000005</v>
+        <v>0.24540000000000001</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="T9" s="1">
-        <v>0.87319999999999998</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="U9" s="1">
-        <v>0.39510000000000001</v>
+        <v>0.43519999999999998</v>
       </c>
       <c r="V9" s="1">
-        <v>0.36430000000000001</v>
+        <v>0.25380000000000003</v>
       </c>
       <c r="W9" s="1">
-        <v>0.38490000000000002</v>
-      </c>
-      <c r="X9" s="1">
-        <v>0.50229999999999997</v>
+        <v>0.38250000000000001</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="Y9" s="1">
-        <v>0.44579999999999997</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="Z9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AA9" s="1">
-        <v>0.32100000000000001</v>
-      </c>
-      <c r="AB9" s="1" t="s">
+        <v>0.67420000000000002</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0.53710000000000002</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>6.3399999999999998E-2</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0.51280000000000003</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="AG9" s="28">
+        <v>0.57720000000000005</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0.57840000000000003</v>
+      </c>
+      <c r="AI9" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>0.84340000000000004</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>0.39150000000000001</v>
-      </c>
-      <c r="AE9" s="1">
-        <v>2.0506000000000002</v>
-      </c>
-      <c r="AF9" s="1">
-        <v>4.1798999999999999</v>
-      </c>
-      <c r="AG9" s="28">
-        <v>7.5494999999999995E-17</v>
-      </c>
-      <c r="AH9" s="1">
-        <v>0.5252</v>
-      </c>
-      <c r="AI9" s="1">
-        <v>0.88739999999999997</v>
       </c>
       <c r="AJ9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AK9" s="1" t="s">
-        <v>1</v>
+      <c r="AK9" s="1">
+        <v>6.7699999999999996E-2</v>
       </c>
       <c r="AL9" s="28">
-        <v>1.6954000000000001E-8</v>
+        <v>0</v>
       </c>
       <c r="AM9" s="1">
-        <v>0.56930000000000003</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="AN9" s="1">
-        <v>1.0162</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="AO9" s="28">
-        <v>6.2172000000000005E-17</v>
+        <v>0.93920000000000003</v>
       </c>
       <c r="AP9" s="1">
-        <v>0.94279999999999997</v>
+        <v>0.47610000000000002</v>
       </c>
       <c r="AQ9" s="1">
-        <v>1.1197999999999999</v>
-      </c>
-      <c r="AR9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AS9" s="1" t="s">
-        <v>1</v>
+        <v>1.0206999999999999</v>
+      </c>
+      <c r="AR9" s="1">
+        <v>0.72850000000000004</v>
+      </c>
+      <c r="AS9" s="1">
+        <v>1.1082000000000001</v>
       </c>
       <c r="AT9" s="1">
+        <v>1.0686</v>
+      </c>
+      <c r="AU9" s="1">
+        <v>1.083</v>
+      </c>
+      <c r="AV9" s="1">
+        <v>1.2529999999999999</v>
+      </c>
+      <c r="AW9" s="1">
+        <v>1.4253</v>
+      </c>
+      <c r="AX9" s="28">
+        <v>1.0018</v>
+      </c>
+      <c r="AY9" s="1">
         <v>0</v>
-      </c>
-      <c r="AU9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AV9" s="1">
-        <v>1.0342</v>
-      </c>
-      <c r="AW9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX9" s="28">
-        <v>1.6679999999999999E-4</v>
-      </c>
-      <c r="AY9" s="1">
-        <v>1.7331000000000001</v>
       </c>
     </row>
     <row r="10" spans="2:51" x14ac:dyDescent="0.3">
@@ -25795,145 +25815,145 @@
         <v>10</v>
       </c>
       <c r="E10" s="1">
-        <v>6.5934999999999997</v>
+        <v>2.0821999999999998</v>
       </c>
       <c r="F10" s="1">
-        <v>3.9708999999999999</v>
+        <v>3.6541999999999999</v>
       </c>
       <c r="G10" s="1">
-        <v>1.7565</v>
+        <v>1.5570999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>2.1267</v>
+        <v>3.0002</v>
       </c>
       <c r="I10" s="1">
-        <v>1.8552999999999999</v>
+        <v>2.3376000000000001</v>
       </c>
       <c r="J10" s="1">
-        <v>1.9495</v>
+        <v>1.8293999999999999</v>
       </c>
       <c r="K10" s="1">
-        <v>0.94169999999999998</v>
+        <v>1.0874999999999999</v>
       </c>
       <c r="L10" s="1">
-        <v>0.85440000000000005</v>
+        <v>2.5209999999999999</v>
       </c>
       <c r="M10" s="1">
-        <v>1.4011</v>
+        <v>1.425</v>
       </c>
       <c r="N10" s="1">
-        <v>1.8972</v>
+        <v>0.82830000000000004</v>
       </c>
       <c r="O10" s="1">
-        <v>1.9249000000000001</v>
+        <v>1.6578999999999999</v>
       </c>
       <c r="P10" s="1">
-        <v>0.34010000000000001</v>
+        <v>0.75160000000000005</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.57469999999999999</v>
-      </c>
-      <c r="R10" s="1" t="s">
+        <v>0.87170000000000003</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0.64129999999999998</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0.65880000000000005</v>
+      </c>
+      <c r="T10" s="28">
+        <v>0.40739999999999998</v>
+      </c>
+      <c r="U10" s="1">
+        <v>1.1298999999999999</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0.7339</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0.80289999999999995</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0.40849999999999997</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0.44490000000000002</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0.73909999999999998</v>
+      </c>
+      <c r="AB10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="S10" s="1">
-        <v>0.48849999999999999</v>
-      </c>
-      <c r="T10" s="28">
-        <v>4.9569999999999997E-14</v>
-      </c>
-      <c r="U10" s="1">
-        <v>0.88549999999999995</v>
-      </c>
-      <c r="V10" s="1">
-        <v>1.1872</v>
-      </c>
-      <c r="W10" s="1">
-        <v>1.9753000000000001</v>
-      </c>
-      <c r="X10" s="1">
-        <v>1.1806000000000001</v>
-      </c>
-      <c r="Y10" s="1">
-        <v>0.66149999999999998</v>
-      </c>
-      <c r="Z10" s="1">
-        <v>2.3E-3</v>
-      </c>
-      <c r="AA10" s="1">
-        <v>0.73970000000000002</v>
-      </c>
-      <c r="AB10" s="1">
-        <v>0.74370000000000003</v>
-      </c>
-      <c r="AC10" s="1">
-        <v>0.70089999999999997</v>
-      </c>
-      <c r="AD10" s="1">
-        <v>2.9554</v>
+      <c r="AC10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="AE10" s="1">
-        <v>1.5248999999999999</v>
+        <v>2.6507000000000001</v>
       </c>
       <c r="AF10" s="1">
-        <v>0.68279999999999996</v>
+        <v>3.7600000000000001E-2</v>
       </c>
       <c r="AG10" s="1">
-        <v>0.39810000000000001</v>
+        <v>3.0590999999999999</v>
       </c>
       <c r="AH10" s="1">
-        <v>1.9433</v>
-      </c>
-      <c r="AI10" s="1" t="s">
+        <v>1.5609</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>0.85940000000000005</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>1.2902</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>1.0537000000000001</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>1.6720999999999999</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>1.7461</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>1.8858999999999999</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>2.8163</v>
+      </c>
+      <c r="AQ10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AJ10" s="1">
-        <v>0.95089999999999997</v>
-      </c>
-      <c r="AK10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AL10" s="1">
-        <v>1.7458</v>
-      </c>
-      <c r="AM10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN10" s="1">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="AO10" s="1">
-        <v>1.2222999999999999</v>
-      </c>
-      <c r="AP10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AQ10" s="1">
-        <v>1.4177</v>
-      </c>
       <c r="AR10" s="1">
-        <v>1.2301</v>
+        <v>0</v>
       </c>
       <c r="AS10" s="1">
-        <v>0.93810000000000004</v>
+        <v>2.375</v>
       </c>
       <c r="AT10" s="1">
-        <v>0.90229999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU10" s="28">
-        <v>4.6494E-12</v>
-      </c>
-      <c r="AV10" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AV10" s="1">
+        <v>4.7919999999999998</v>
       </c>
       <c r="AW10" s="1">
-        <v>2.3016000000000001</v>
+        <v>0.69130000000000003</v>
       </c>
       <c r="AX10" s="1">
-        <v>1.1776</v>
+        <v>1.7847999999999999</v>
       </c>
       <c r="AY10" s="1">
-        <v>0.63449999999999995</v>
+        <v>1.0371999999999999</v>
       </c>
     </row>
     <row r="11" spans="2:51" x14ac:dyDescent="0.3">
@@ -25950,142 +25970,142 @@
         <v>10</v>
       </c>
       <c r="F11" s="28">
-        <v>5.7084000000000001</v>
+        <v>6.0301999999999998</v>
       </c>
       <c r="G11" s="1">
-        <v>3.5228000000000002</v>
+        <v>4.2361000000000004</v>
       </c>
       <c r="H11" s="1">
-        <v>3.4794</v>
+        <v>2.9224999999999999</v>
       </c>
       <c r="I11" s="1">
-        <v>0.53779999999999994</v>
+        <v>2.0474000000000001</v>
       </c>
       <c r="J11" s="1">
-        <v>2.8347000000000002</v>
+        <v>2.1238000000000001</v>
       </c>
       <c r="K11" s="1">
-        <v>2.6903000000000001</v>
+        <v>2.0649000000000002</v>
       </c>
       <c r="L11" s="1">
-        <v>4.7827999999999999</v>
+        <v>5.0827</v>
       </c>
       <c r="M11" s="1">
-        <v>2.387</v>
+        <v>1.3683000000000001</v>
       </c>
       <c r="N11" s="1">
-        <v>1.1605000000000001</v>
+        <v>1.4823999999999999</v>
       </c>
       <c r="O11" s="1">
-        <v>1.9159999999999999</v>
+        <v>0.58199999999999996</v>
       </c>
       <c r="P11" s="1">
-        <v>1.4534</v>
+        <v>3.3035000000000001</v>
       </c>
       <c r="Q11" s="1">
-        <v>2.6374</v>
+        <v>0.86880000000000002</v>
       </c>
       <c r="R11" s="1">
-        <v>1.0477000000000001</v>
+        <v>0.67390000000000005</v>
       </c>
       <c r="S11" s="1">
-        <v>0.75649999999999995</v>
+        <v>0.94740000000000002</v>
       </c>
       <c r="T11" s="1">
-        <v>0.86670000000000003</v>
+        <v>1.5065999999999999</v>
       </c>
       <c r="U11" s="1">
-        <v>1.5668</v>
+        <v>0.72250000000000003</v>
       </c>
       <c r="V11" s="28">
-        <v>3.2862999999999998E-16</v>
+        <v>0.7359</v>
       </c>
       <c r="W11" s="1">
-        <v>2.6602999999999999</v>
+        <v>2.0626000000000002</v>
       </c>
       <c r="X11" s="1">
-        <v>1.7577</v>
+        <v>0.16089999999999999</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.55930000000000002</v>
+        <v>0.56869999999999998</v>
       </c>
       <c r="Z11" s="1">
-        <v>0.98450000000000004</v>
+        <v>0.46360000000000001</v>
       </c>
       <c r="AA11" s="1">
-        <v>0.62560000000000004</v>
+        <v>1.8786</v>
       </c>
       <c r="AB11" s="1">
-        <v>1.1798999999999999</v>
+        <v>1.2332000000000001</v>
       </c>
       <c r="AC11" s="1">
-        <v>0.89459999999999995</v>
+        <v>1.1167</v>
       </c>
       <c r="AD11" s="1">
-        <v>0.82179999999999997</v>
+        <v>0.58579999999999999</v>
       </c>
       <c r="AE11" s="1">
-        <v>0.8911</v>
-      </c>
-      <c r="AF11" s="1" t="s">
+        <v>0.88239999999999996</v>
+      </c>
+      <c r="AF11" s="1">
+        <v>0.65910000000000002</v>
+      </c>
+      <c r="AG11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AG11" s="1">
-        <v>0.78390000000000004</v>
-      </c>
-      <c r="AH11" s="1">
-        <v>0.97309999999999997</v>
+      <c r="AH11" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="AI11" s="1">
-        <v>0.50029999999999997</v>
+        <v>0</v>
       </c>
       <c r="AJ11" s="1">
-        <v>1.0402</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="1">
-        <v>1.0073000000000001</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="AL11" s="1">
-        <v>4.8658999999999999</v>
+        <v>1.1727000000000001</v>
       </c>
       <c r="AM11" s="28">
-        <v>7.2440000000000002E-13</v>
+        <v>1.7061999999999999</v>
       </c>
       <c r="AN11" s="1">
-        <v>4.0883000000000003</v>
+        <v>3.3875000000000002</v>
       </c>
       <c r="AO11" s="1">
-        <v>5.91E-2</v>
+        <v>1.0588</v>
       </c>
       <c r="AP11" s="1">
-        <v>1.1760999999999999</v>
+        <v>1.4830000000000001</v>
       </c>
       <c r="AQ11" s="1">
-        <v>3.1154999999999999</v>
+        <v>1.3163</v>
       </c>
       <c r="AR11" s="1">
-        <v>3.1511999999999998</v>
+        <v>2.3450000000000002</v>
       </c>
       <c r="AS11" s="1">
-        <v>6.2747000000000002</v>
+        <v>2.2336</v>
       </c>
       <c r="AT11" s="28">
-        <v>4.9342000000000001E-14</v>
+        <v>2.5207000000000002</v>
       </c>
       <c r="AU11" s="1">
-        <v>5.1928000000000001</v>
+        <v>6.4222000000000001</v>
       </c>
       <c r="AV11" s="1">
-        <v>0.55900000000000005</v>
+        <v>6.7850000000000001</v>
       </c>
       <c r="AW11" s="1">
-        <v>2.0621</v>
+        <v>7.7743000000000002</v>
       </c>
       <c r="AX11" s="1">
-        <v>1.0154000000000001</v>
+        <v>7.2700000000000001E-2</v>
       </c>
       <c r="AY11" s="28">
-        <v>9.8405999999999995E-14</v>
+        <v>1.2968</v>
       </c>
     </row>
     <row r="12" spans="2:51" x14ac:dyDescent="0.3">
@@ -26105,139 +26125,139 @@
         <v>10</v>
       </c>
       <c r="G12" s="28">
-        <v>2.2482000000000002</v>
+        <v>14.641999999999999</v>
       </c>
       <c r="H12" s="28">
-        <v>3.8944000000000001</v>
+        <v>3.1795</v>
       </c>
       <c r="I12" s="1">
-        <v>5.2839</v>
+        <v>2.0049000000000001</v>
       </c>
       <c r="J12" s="1">
-        <v>2.1116999999999999</v>
+        <v>2.0059999999999998</v>
       </c>
       <c r="K12" s="1">
-        <v>3.6751</v>
+        <v>3.6341000000000001</v>
       </c>
       <c r="L12" s="1">
-        <v>2.8553999999999999</v>
+        <v>1.3158000000000001</v>
       </c>
       <c r="M12" s="1">
-        <v>2.7161</v>
+        <v>2.0931000000000002</v>
       </c>
       <c r="N12" s="1">
-        <v>1.5026999999999999</v>
+        <v>4.8594999999999997</v>
       </c>
       <c r="O12" s="1">
-        <v>2.8572000000000002</v>
+        <v>2.0099</v>
       </c>
       <c r="P12" s="1">
-        <v>4.8402000000000003</v>
+        <v>1.3549</v>
       </c>
       <c r="Q12" s="1">
-        <v>6.2297000000000002</v>
+        <v>1.6738999999999999</v>
       </c>
       <c r="R12" s="1">
-        <v>4.9635999999999996</v>
+        <v>2.3797999999999999</v>
       </c>
       <c r="S12" s="28">
-        <v>9.9256999999999996E-14</v>
+        <v>2.1640999999999999</v>
       </c>
       <c r="T12" s="1">
-        <v>0.6482</v>
+        <v>4.8112000000000004</v>
       </c>
       <c r="U12" s="1">
-        <v>1.5059</v>
+        <v>1.6035999999999999</v>
       </c>
       <c r="V12" s="1">
-        <v>5.9149000000000003</v>
+        <v>0.69350000000000001</v>
       </c>
       <c r="W12" s="1">
-        <v>3.4169999999999998</v>
+        <v>0.97160000000000002</v>
       </c>
       <c r="X12" s="1">
-        <v>2.2343000000000002</v>
+        <v>3.4666999999999999</v>
       </c>
       <c r="Y12" s="1">
-        <v>0.69650000000000001</v>
-      </c>
-      <c r="Z12" s="1">
-        <v>1.3874</v>
+        <v>7.1177000000000001</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="AA12" s="28">
-        <v>1.8679999999999999E-4</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="1">
-        <v>0.94389999999999996</v>
-      </c>
-      <c r="AC12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>0.36520000000000002</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0.99060000000000004</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>0.98260000000000003</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>1.8512999999999999</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>0.62409999999999999</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>1.6848000000000001</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>2.6337999999999999</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>6.7417999999999996</v>
+      </c>
+      <c r="AL12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AD12" s="1">
-        <v>1.9322999999999999</v>
-      </c>
-      <c r="AE12" s="1">
-        <v>1.3861000000000001</v>
-      </c>
-      <c r="AF12" s="1">
-        <v>1.7461</v>
-      </c>
-      <c r="AG12" s="1">
-        <v>1.5733999999999999</v>
-      </c>
-      <c r="AH12" s="1">
-        <v>0.69299999999999995</v>
-      </c>
-      <c r="AI12" s="1">
-        <v>8.4276999999999997</v>
-      </c>
-      <c r="AJ12" s="1">
-        <v>2E-3</v>
-      </c>
-      <c r="AK12" s="1">
-        <v>1.9380999999999999</v>
-      </c>
-      <c r="AL12" s="1">
-        <v>2.1078999999999999</v>
-      </c>
-      <c r="AM12" s="1">
-        <v>2.1017999999999999</v>
-      </c>
-      <c r="AN12" s="1" t="s">
+      <c r="AM12" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="AN12" s="1">
+        <v>1.9638</v>
+      </c>
       <c r="AO12" s="1">
-        <v>13.4237</v>
+        <v>0</v>
       </c>
       <c r="AP12" s="1">
-        <v>2.5270999999999999</v>
+        <v>1.4569000000000001</v>
       </c>
       <c r="AQ12" s="1">
-        <v>1.2738</v>
-      </c>
-      <c r="AR12" s="1" t="s">
-        <v>1</v>
+        <v>1.0064</v>
+      </c>
+      <c r="AR12" s="1">
+        <v>1.9952000000000001</v>
       </c>
       <c r="AS12" s="28">
-        <v>1.0658E-16</v>
+        <v>4.5495000000000001</v>
       </c>
       <c r="AT12" s="1">
-        <v>2.3751000000000002</v>
+        <v>13.2186</v>
       </c>
       <c r="AU12" s="1">
-        <v>10.742900000000001</v>
+        <v>0.68740000000000001</v>
       </c>
       <c r="AV12" s="1">
-        <v>1.3691</v>
+        <v>2.5583999999999998</v>
       </c>
       <c r="AW12" s="28">
-        <v>1.5084E-5</v>
+        <v>0.58699999999999997</v>
       </c>
       <c r="AX12" s="1">
-        <v>4.9781000000000004</v>
+        <v>1.9438</v>
       </c>
       <c r="AY12" s="1">
-        <v>4.2257999999999996</v>
+        <v>0.66100000000000003</v>
       </c>
     </row>
     <row r="13" spans="2:51" x14ac:dyDescent="0.3">
@@ -26263,133 +26283,133 @@
         <v>10</v>
       </c>
       <c r="I13" s="1">
-        <v>14.4291</v>
+        <v>6.4832999999999998</v>
       </c>
       <c r="J13" s="1">
-        <v>6.1852</v>
+        <v>7.3826000000000001</v>
       </c>
       <c r="K13" s="1">
-        <v>10.341200000000001</v>
+        <v>18.001799999999999</v>
       </c>
       <c r="L13" s="1">
-        <v>4.7329999999999997</v>
+        <v>6.39</v>
       </c>
       <c r="M13" s="1">
-        <v>2.1503999999999999</v>
+        <v>8.0501000000000005</v>
       </c>
       <c r="N13" s="1">
-        <v>2.9497</v>
+        <v>12.8711</v>
       </c>
       <c r="O13" s="1">
-        <v>4.4478</v>
+        <v>4.2380000000000004</v>
       </c>
       <c r="P13" s="1">
-        <v>2.8793000000000002</v>
+        <v>5.3880999999999997</v>
       </c>
       <c r="Q13" s="1">
-        <v>9.6168999999999993</v>
+        <v>7.3973000000000004</v>
       </c>
       <c r="R13" s="1">
-        <v>3.8395000000000001</v>
+        <v>3.1080999999999999</v>
       </c>
       <c r="S13" s="1">
-        <v>1.7901</v>
+        <v>4.0316000000000001</v>
       </c>
       <c r="T13" s="1">
-        <v>3.8222</v>
+        <v>3.5933000000000002</v>
       </c>
       <c r="U13" s="1">
-        <v>24.678899999999999</v>
+        <v>8.8750999999999998</v>
       </c>
       <c r="V13" s="1">
-        <v>2.7585999999999999</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="W13" s="1">
-        <v>13.604699999999999</v>
+        <v>2.0225</v>
       </c>
       <c r="X13" s="1">
-        <v>2.6004</v>
+        <v>4.0815000000000001</v>
       </c>
       <c r="Y13" s="1">
-        <v>2.48</v>
+        <v>1.6828000000000001</v>
       </c>
       <c r="Z13" s="1">
-        <v>0.22359999999999999</v>
+        <v>4.3449999999999998</v>
       </c>
       <c r="AA13" s="1">
-        <v>2.1991999999999998</v>
+        <v>17.245200000000001</v>
       </c>
       <c r="AB13" s="1">
-        <v>0.39579999999999999</v>
-      </c>
-      <c r="AC13" s="1">
-        <v>6.2619999999999996</v>
+        <v>3.7557</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="AD13" s="1">
-        <v>13.936999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="1">
-        <v>0.90180000000000005</v>
+        <v>2.2806000000000002</v>
       </c>
       <c r="AF13" s="1">
-        <v>0.95750000000000002</v>
-      </c>
-      <c r="AG13" s="1" t="s">
+        <v>1.8948</v>
+      </c>
+      <c r="AG13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="28">
+        <v>4.1863000000000001</v>
+      </c>
+      <c r="AJ13" s="28">
+        <v>1.9915</v>
+      </c>
+      <c r="AK13" s="1">
+        <v>5.4467999999999996</v>
+      </c>
+      <c r="AL13" s="1">
+        <v>1.0134000000000001</v>
+      </c>
+      <c r="AM13" s="1">
+        <v>4.1571999999999996</v>
+      </c>
+      <c r="AN13" s="1">
+        <v>11.259399999999999</v>
+      </c>
+      <c r="AO13" s="1">
+        <v>5.0186000000000002</v>
+      </c>
+      <c r="AP13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AH13" s="1">
-        <v>0.51080000000000003</v>
-      </c>
-      <c r="AI13" s="28">
-        <v>6.6130999999999996E-10</v>
-      </c>
-      <c r="AJ13" s="28">
-        <v>3.8858E-16</v>
-      </c>
-      <c r="AK13" s="1">
-        <v>15.8522</v>
-      </c>
-      <c r="AL13" s="1">
-        <v>5.8545999999999996</v>
-      </c>
-      <c r="AM13" s="1">
-        <v>2.9828000000000001</v>
-      </c>
-      <c r="AN13" s="1">
-        <v>38.828699999999998</v>
-      </c>
-      <c r="AO13" s="1">
-        <v>1.0666</v>
-      </c>
-      <c r="AP13" s="1">
-        <v>0.66869999999999996</v>
-      </c>
-      <c r="AQ13" s="1">
-        <v>1.1839</v>
+      <c r="AQ13" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="AR13" s="1">
-        <v>1.2215</v>
+        <v>0</v>
       </c>
       <c r="AS13" s="1">
-        <v>13.1357</v>
+        <v>1E-4</v>
       </c>
       <c r="AT13" s="1">
-        <v>34.671199999999999</v>
+        <v>0</v>
       </c>
       <c r="AU13" s="1">
-        <v>6.2782</v>
+        <v>1.3156000000000001</v>
       </c>
       <c r="AV13" s="28">
-        <v>9.9183000000000003E-14</v>
+        <v>0.78990000000000005</v>
       </c>
       <c r="AW13" s="28">
-        <v>6.3061000000000001E-16</v>
+        <v>7.5115999999999996</v>
       </c>
       <c r="AX13" s="1">
-        <v>21.1496</v>
+        <v>11.757099999999999</v>
       </c>
       <c r="AY13" s="1">
-        <v>1.4510000000000001</v>
+        <v>20.764900000000001</v>
       </c>
     </row>
     <row r="14" spans="2:51" x14ac:dyDescent="0.3">
@@ -26424,124 +26444,124 @@
         <v>10</v>
       </c>
       <c r="L14" s="1">
-        <v>14.7263</v>
+        <v>23.657800000000002</v>
       </c>
       <c r="M14" s="1">
-        <v>0.48359999999999997</v>
-      </c>
-      <c r="N14" s="1">
-        <v>11.6005</v>
+        <v>20.401900000000001</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="O14" s="1">
-        <v>15.3027</v>
+        <v>9.6194000000000006</v>
       </c>
       <c r="P14" s="1">
-        <v>43.913400000000003</v>
+        <v>15.598800000000001</v>
       </c>
       <c r="Q14" s="1">
-        <v>14.9612</v>
+        <v>16.6907</v>
       </c>
       <c r="R14" s="1">
-        <v>4.6788999999999996</v>
+        <v>4.5891999999999999</v>
       </c>
       <c r="S14" s="1">
-        <v>6.2796000000000003</v>
+        <v>2.0707</v>
       </c>
       <c r="T14" s="1">
-        <v>9.6432000000000002</v>
+        <v>31.975899999999999</v>
       </c>
       <c r="U14" s="1">
-        <v>51.548400000000001</v>
+        <v>8.6188000000000002</v>
       </c>
       <c r="V14" s="28">
-        <v>1.1408E-5</v>
+        <v>24.4299</v>
       </c>
       <c r="W14" s="1">
-        <v>21.5229</v>
+        <v>1.7025999999999999</v>
       </c>
       <c r="X14" s="1">
-        <v>2.9426999999999999</v>
+        <v>3.3144999999999998</v>
       </c>
       <c r="Y14" s="1">
-        <v>27.292400000000001</v>
+        <v>10.4503</v>
       </c>
       <c r="Z14" s="1">
-        <v>20.045000000000002</v>
+        <v>1.2309000000000001</v>
       </c>
       <c r="AA14" s="1">
-        <v>5.4419000000000004</v>
+        <v>17.7729</v>
       </c>
       <c r="AB14" s="1">
-        <v>33.802100000000003</v>
+        <v>17.6557</v>
       </c>
       <c r="AC14" s="1">
-        <v>47.579700000000003</v>
+        <v>8.3867999999999991</v>
       </c>
       <c r="AD14" s="1">
-        <v>29.305399999999999</v>
-      </c>
-      <c r="AE14" s="1">
-        <v>1.3345</v>
+        <v>62.529000000000003</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="AF14" s="1">
-        <v>21.610499999999998</v>
+        <v>0</v>
       </c>
       <c r="AG14" s="1">
-        <v>2.5678000000000001</v>
+        <v>2.5667</v>
       </c>
       <c r="AH14" s="1">
-        <v>2.3793000000000002</v>
+        <v>1.9107000000000001</v>
       </c>
       <c r="AI14" s="1">
-        <v>16.147300000000001</v>
+        <v>5.7564000000000002</v>
       </c>
       <c r="AJ14" s="1">
-        <v>1.2095</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="AK14" s="1">
-        <v>74.941500000000005</v>
+        <v>1.6851</v>
       </c>
       <c r="AL14" s="1">
-        <v>0</v>
+        <v>11.7988</v>
       </c>
       <c r="AM14" s="28">
-        <v>3.0071999999999998E-4</v>
+        <v>1.9838</v>
       </c>
       <c r="AN14" s="1">
-        <v>1.3160000000000001</v>
+        <v>1.7907999999999999</v>
       </c>
       <c r="AO14" s="28">
-        <v>7.3287999999999999E-4</v>
+        <v>0.44550000000000001</v>
       </c>
       <c r="AP14" s="1">
-        <v>5.0194000000000001</v>
+        <v>26.293199999999999</v>
       </c>
       <c r="AQ14" s="1">
-        <v>38.413699999999999</v>
+        <v>27.499400000000001</v>
       </c>
       <c r="AR14" s="1">
-        <v>100.9654</v>
+        <v>8.3760999999999992</v>
       </c>
       <c r="AS14" s="1">
-        <v>1.3474999999999999</v>
+        <v>22.137</v>
       </c>
       <c r="AT14" s="28">
-        <v>1.3867E-15</v>
-      </c>
-      <c r="AU14" s="1">
-        <v>7.4104000000000001</v>
+        <v>11.621600000000001</v>
+      </c>
+      <c r="AU14" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="AV14" s="1">
         <v>0</v>
       </c>
       <c r="AW14" s="1">
-        <v>2.5329999999999999</v>
+        <v>0.99619999999999997</v>
       </c>
       <c r="AX14" s="1">
-        <v>1.4908999999999999</v>
+        <v>1.036</v>
       </c>
       <c r="AY14" s="1">
-        <v>11.254099999999999</v>
+        <v>0.26019999999999999</v>
       </c>
     </row>
     <row r="15" spans="2:51" x14ac:dyDescent="0.3">
@@ -26594,106 +26614,106 @@
         <v>10</v>
       </c>
       <c r="R15" s="1">
-        <v>134.4787</v>
+        <v>13.236000000000001</v>
       </c>
       <c r="S15" s="1">
-        <v>2.8925000000000001</v>
+        <v>13.3667</v>
       </c>
       <c r="T15" s="1">
-        <v>160.3175</v>
+        <v>46.550800000000002</v>
       </c>
       <c r="U15" s="1">
-        <v>10.509499999999999</v>
+        <v>3.4742000000000002</v>
       </c>
       <c r="V15" s="1">
-        <v>89.633899999999997</v>
+        <v>66.898399999999995</v>
       </c>
       <c r="W15" s="1">
-        <v>150.1146</v>
+        <v>109.2889</v>
       </c>
       <c r="X15" s="1">
-        <v>6.7298</v>
+        <v>2.3506999999999998</v>
       </c>
       <c r="Y15" s="1">
-        <v>5.0404</v>
+        <v>6.7076000000000002</v>
       </c>
       <c r="Z15" s="1">
-        <v>67.253900000000002</v>
+        <v>6.9287000000000001</v>
       </c>
       <c r="AA15" s="28">
-        <v>1.4794999999999999E-8</v>
+        <v>5.3962000000000003</v>
       </c>
       <c r="AB15" s="1">
-        <v>221.55369999999999</v>
+        <v>32.713099999999997</v>
       </c>
       <c r="AC15" s="1">
-        <v>2.8452999999999999</v>
+        <v>74.917299999999997</v>
       </c>
       <c r="AD15" s="1">
-        <v>2.7501000000000002</v>
-      </c>
-      <c r="AE15" s="1" t="s">
+        <v>32.198500000000003</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>2.2000000000000001E-3</v>
+      </c>
+      <c r="AF15" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="AF15" s="1">
-        <v>8.4471000000000007</v>
-      </c>
       <c r="AG15" s="1">
-        <v>1.1531</v>
+        <v>0</v>
       </c>
       <c r="AH15" s="1">
-        <v>3.3759000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="1">
-        <v>1.8809</v>
+        <v>3.1682000000000001</v>
       </c>
       <c r="AJ15" s="1">
-        <v>3.0916000000000001</v>
+        <v>1.9974000000000001</v>
       </c>
       <c r="AK15" s="1">
-        <v>2.0199999999999999E-2</v>
+        <v>10.5509</v>
       </c>
       <c r="AL15" s="1">
-        <v>77.834699999999998</v>
+        <v>1.7723</v>
       </c>
       <c r="AM15" s="1">
-        <v>2.5325000000000002</v>
+        <v>1.3877999999999999</v>
       </c>
       <c r="AN15" s="1">
-        <v>29.884899999999998</v>
+        <v>9.1791</v>
       </c>
       <c r="AO15" s="1">
-        <v>1.8037000000000001</v>
+        <v>145.8621</v>
       </c>
       <c r="AP15" s="1">
-        <v>0.58989999999999998</v>
+        <v>4.5934999999999997</v>
       </c>
       <c r="AQ15" s="1">
-        <v>11.464700000000001</v>
+        <v>4.5594000000000001</v>
       </c>
       <c r="AR15" s="1">
-        <v>6.9961000000000002</v>
+        <v>1.6528</v>
       </c>
       <c r="AS15" s="1">
-        <v>0.56259999999999999</v>
+        <v>89.885999999999996</v>
       </c>
       <c r="AT15" s="1">
-        <v>13.069000000000001</v>
+        <v>102.8505</v>
       </c>
       <c r="AU15" s="1">
-        <v>5.1165000000000003</v>
+        <v>14.915800000000001</v>
       </c>
       <c r="AV15" s="1">
-        <v>12.5739</v>
+        <v>37.524900000000002</v>
       </c>
       <c r="AW15" s="28">
-        <v>1.4433E-16</v>
+        <v>35.255200000000002</v>
       </c>
       <c r="AX15" s="28">
-        <v>1.6875000000000001E-16</v>
+        <v>132.15309999999999</v>
       </c>
       <c r="AY15" s="1">
-        <v>491.94220000000001</v>
+        <v>1.8163</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
@@ -26701,12 +26721,12 @@
         <v>661</v>
       </c>
       <c r="C19" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>
@@ -26724,4 +26744,6466 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61F4B402-73D1-4ACC-83A0-F86D50733431}">
+  <dimension ref="B1:AY15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="51" width="5.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="P2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="R2" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="S2" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="T2" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="U2" s="1">
+        <v>2</v>
+      </c>
+      <c r="V2" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="W2" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X2" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>4</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B3" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.12330000000000001</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.1255</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.12720000000000001</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.12859999999999999</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.12970000000000001</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.12809999999999999</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.1241</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.1182</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0.1113</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0.10390000000000001</v>
+      </c>
+      <c r="M3" s="1">
+        <v>9.6500000000000002E-2</v>
+      </c>
+      <c r="N3" s="1">
+        <v>8.9399999999999993E-2</v>
+      </c>
+      <c r="O3" s="1">
+        <v>8.2900000000000001E-2</v>
+      </c>
+      <c r="P3" s="1">
+        <v>7.7399999999999997E-2</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>7.2900000000000006E-2</v>
+      </c>
+      <c r="R3" s="1">
+        <v>6.9699999999999998E-2</v>
+      </c>
+      <c r="S3" s="1">
+        <v>6.7699999999999996E-2</v>
+      </c>
+      <c r="T3" s="1">
+        <v>6.7799999999999999E-2</v>
+      </c>
+      <c r="U3" s="1">
+        <v>7.0499999999999993E-2</v>
+      </c>
+      <c r="V3" s="1">
+        <v>7.4899999999999994E-2</v>
+      </c>
+      <c r="W3" s="1">
+        <v>8.0600000000000005E-2</v>
+      </c>
+      <c r="X3" s="1">
+        <v>8.7599999999999997E-2</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>9.5799999999999996E-2</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>0.1051</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>0.1158</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>0.12790000000000001</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>0.14219999999999999</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>0.1593</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>0.17749999999999999</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>0.19620000000000001</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>0.21460000000000001</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>0.2472</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>0.25929999999999997</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>0.26729999999999998</v>
+      </c>
+      <c r="AL3" s="1">
+        <v>0.27039999999999997</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>0.26829999999999998</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>0.2606</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>0.24779999999999999</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>0.23080000000000001</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>0.21060000000000001</v>
+      </c>
+      <c r="AR3" s="1">
+        <v>0.1888</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>0.1673</v>
+      </c>
+      <c r="AT3" s="1">
+        <v>0.1479</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>0.13469999999999999</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>0.12920000000000001</v>
+      </c>
+      <c r="AW3" s="1">
+        <v>0.12939999999999999</v>
+      </c>
+      <c r="AX3" s="1">
+        <v>0.13569999999999999</v>
+      </c>
+      <c r="AY3" s="1">
+        <v>0.15049999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.1759</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.193</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.20530000000000001</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.21229999999999999</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.21429999999999999</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.21190000000000001</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.2059</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.1973</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0.18679999999999999</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0.17519999999999999</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.16309999999999999</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0.15110000000000001</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0.1396</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0.12889999999999999</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0.11940000000000001</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0.11119999999999999</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0.1045</v>
+      </c>
+      <c r="T4" s="1">
+        <v>9.9599999999999994E-2</v>
+      </c>
+      <c r="U4" s="1">
+        <v>9.6500000000000002E-2</v>
+      </c>
+      <c r="V4" s="1">
+        <v>9.5500000000000002E-2</v>
+      </c>
+      <c r="W4" s="1">
+        <v>9.6699999999999994E-2</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0.1003</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>0.10639999999999999</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0.11509999999999999</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>0.12640000000000001</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>0.14030000000000001</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>0.15659999999999999</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>0.1749</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>0.1948</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>0.21540000000000001</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>0.2359</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>0.25519999999999998</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>0.28510000000000002</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>0.29339999999999999</v>
+      </c>
+      <c r="AL4" s="1">
+        <v>0.29570000000000002</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>0.29149999999999998</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>0.28079999999999999</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>0.26379999999999998</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>0.24149999999999999</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>0.2157</v>
+      </c>
+      <c r="AR4" s="1">
+        <v>0.1885</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>0.17610000000000001</v>
+      </c>
+      <c r="AT4" s="1">
+        <v>0.1754</v>
+      </c>
+      <c r="AU4" s="1">
+        <v>0.183</v>
+      </c>
+      <c r="AV4" s="1">
+        <v>0.19670000000000001</v>
+      </c>
+      <c r="AW4" s="1">
+        <v>0.2155</v>
+      </c>
+      <c r="AX4" s="1">
+        <v>0.23960000000000001</v>
+      </c>
+      <c r="AY4" s="1">
+        <v>0.27260000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.20449999999999999</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.24660000000000001</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.26519999999999999</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.26579999999999998</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.26169999999999999</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.25380000000000003</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0.24310000000000001</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0.23039999999999999</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0.21659999999999999</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0.2024</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0.1883</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0.1749</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0.16239999999999999</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0.1512</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0.1416</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0.1338</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0.128</v>
+      </c>
+      <c r="V5" s="1">
+        <v>0.1244</v>
+      </c>
+      <c r="W5" s="1">
+        <v>0.1232</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0.12470000000000001</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>0.12889999999999999</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>0.14610000000000001</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>0.15920000000000001</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>0.17510000000000001</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>0.19350000000000001</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0.214</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>0.2359</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>0.25850000000000001</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>0.28070000000000001</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>0.3014</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>0.31950000000000001</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>0.33389999999999997</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>0.34370000000000001</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>0.3483</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>0.3473</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>0.34110000000000001</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>0.33019999999999999</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>0.31609999999999999</v>
+      </c>
+      <c r="AR5" s="28">
+        <v>0.3004</v>
+      </c>
+      <c r="AS5" s="1">
+        <v>0.28539999999999999</v>
+      </c>
+      <c r="AT5" s="1">
+        <v>0.27410000000000001</v>
+      </c>
+      <c r="AU5" s="1">
+        <v>0.26989999999999997</v>
+      </c>
+      <c r="AV5" s="1">
+        <v>0.2767</v>
+      </c>
+      <c r="AW5" s="1">
+        <v>0.29980000000000001</v>
+      </c>
+      <c r="AX5" s="1">
+        <v>0.34560000000000002</v>
+      </c>
+      <c r="AY5" s="1">
+        <v>0.42249999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.2031</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.2339</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.25929999999999997</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.27839999999999998</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.29070000000000001</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.29659999999999997</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.29680000000000001</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0.28339999999999999</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.2586</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0.24410000000000001</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0.2293</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0.21460000000000001</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0.20080000000000001</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0.188</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0.17680000000000001</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0.1673</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0.15970000000000001</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0.15440000000000001</v>
+      </c>
+      <c r="W6" s="28">
+        <v>0.1515</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0.15110000000000001</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0.15340000000000001</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0.1585</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0.16639999999999999</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0.17710000000000001</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0.1905</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>0.20630000000000001</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0.22409999999999999</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>0.24340000000000001</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>0.2636</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>0.2838</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>0.30320000000000003</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>0.32090000000000002</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>0.33589999999999998</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>0.34760000000000002</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>0.35539999999999999</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>0.3589</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>0.35809999999999997</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>0.35360000000000003</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>0.33689999999999998</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>0.32790000000000002</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>0.3216</v>
+      </c>
+      <c r="AU6" s="28">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>0.3301</v>
+      </c>
+      <c r="AW6" s="1">
+        <v>0.35389999999999999</v>
+      </c>
+      <c r="AX6" s="1">
+        <v>0.39939999999999998</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>0.4753</v>
+      </c>
+    </row>
+    <row r="7" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.18360000000000001</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.21779999999999999</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.24890000000000001</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.27410000000000001</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.29310000000000003</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.30530000000000002</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.31109999999999999</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.31130000000000002</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.30669999999999997</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0.2984</v>
+      </c>
+      <c r="M7" s="28">
+        <v>0.28720000000000001</v>
+      </c>
+      <c r="N7" s="28">
+        <v>0.27429999999999999</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0.26029999999999998</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0.24610000000000001</v>
+      </c>
+      <c r="Q7" s="28">
+        <v>0.23230000000000001</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0.21929999999999999</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0.20760000000000001</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0.1976</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0.18940000000000001</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0.18329999999999999</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0.17949999999999999</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0.17810000000000001</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0.1792</v>
+      </c>
+      <c r="Z7" s="28">
+        <v>0.1827</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0.1888</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>0.19719999999999999</v>
+      </c>
+      <c r="AC7" s="28">
+        <v>0.20780000000000001</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>0.22040000000000001</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0.2346</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>0.26590000000000003</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>0.28179999999999999</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>0.29699999999999999</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>0.31069999999999998</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>0.32229999999999998</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>0.33119999999999999</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>0.33689999999999998</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>0.33739999999999998</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>0.33250000000000002</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>0.3246</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>0.31469999999999998</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>0.30420000000000003</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>0.28970000000000001</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>0.29139999999999999</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>0.30480000000000002</v>
+      </c>
+      <c r="AX7" s="1">
+        <v>0.3357</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>0.3926</v>
+      </c>
+    </row>
+    <row r="8" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.71230000000000004</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.27050000000000002</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.2581</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.26989999999999997</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.29010000000000002</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.30449999999999999</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.30830000000000002</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.30630000000000002</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.30180000000000001</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0.29770000000000002</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0.29020000000000001</v>
+      </c>
+      <c r="N8" s="28">
+        <v>0.28029999999999999</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0.26869999999999999</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0.25640000000000002</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0.2321</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0.22120000000000001</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0.21179999999999999</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="V8" s="1">
+        <v>0.19819999999999999</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0.19450000000000001</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0.19309999999999999</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0.19389999999999999</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0.19689999999999999</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0.2021</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>0.20930000000000001</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>0.21840000000000001</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0.24079999999999999</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>0.2535</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>0.2666</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>0.27960000000000002</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>0.30330000000000001</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>0.31309999999999999</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>0.32069999999999999</v>
+      </c>
+      <c r="AM8" s="1">
+        <v>0.32590000000000002</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>0.32819999999999999</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>0.32740000000000002</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>0.32369999999999999</v>
+      </c>
+      <c r="AQ8" s="1">
+        <v>0.31709999999999999</v>
+      </c>
+      <c r="AR8" s="1">
+        <v>0.30830000000000002</v>
+      </c>
+      <c r="AS8" s="1">
+        <v>0.2984</v>
+      </c>
+      <c r="AT8" s="1">
+        <v>0.28860000000000002</v>
+      </c>
+      <c r="AU8" s="1">
+        <v>0.28120000000000001</v>
+      </c>
+      <c r="AV8" s="1">
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="AW8" s="1">
+        <v>0.28560000000000002</v>
+      </c>
+      <c r="AX8" s="1">
+        <v>0.30659999999999998</v>
+      </c>
+      <c r="AY8" s="1">
+        <v>0.34939999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1.5009999999999999</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.64990000000000003</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.42870000000000003</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.33129999999999998</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.30719999999999997</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.28789999999999999</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.28120000000000001</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0.27139999999999997</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0.26129999999999998</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0.25640000000000002</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0.24940000000000001</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0.2404</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0.23039999999999999</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0.2198</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0.20949999999999999</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0.19989999999999999</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0.19139999999999999</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0.18440000000000001</v>
+      </c>
+      <c r="V9" s="1">
+        <v>0.1792</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0.17469999999999999</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>0.1757</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0.1787</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0.18310000000000001</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0.18920000000000001</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>0.1971</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0.20619999999999999</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0.21629999999999999</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>0.2271</v>
+      </c>
+      <c r="AG9" s="28">
+        <v>0.23830000000000001</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0.24940000000000001</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>0.26040000000000002</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>0.27089999999999997</v>
+      </c>
+      <c r="AK9" s="1">
+        <v>0.28050000000000003</v>
+      </c>
+      <c r="AL9" s="28">
+        <v>0.28910000000000002</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>0.29630000000000001</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>0.30180000000000001</v>
+      </c>
+      <c r="AO9" s="28">
+        <v>0.30530000000000002</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>0.30659999999999998</v>
+      </c>
+      <c r="AQ9" s="1">
+        <v>0.30570000000000003</v>
+      </c>
+      <c r="AR9" s="1">
+        <v>0.3029</v>
+      </c>
+      <c r="AS9" s="1">
+        <v>0.29870000000000002</v>
+      </c>
+      <c r="AT9" s="1">
+        <v>0.29409999999999997</v>
+      </c>
+      <c r="AU9" s="1">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="AV9" s="1">
+        <v>0.29170000000000001</v>
+      </c>
+      <c r="AW9" s="1">
+        <v>0.29959999999999998</v>
+      </c>
+      <c r="AX9" s="28">
+        <v>0.31969999999999998</v>
+      </c>
+      <c r="AY9" s="1">
+        <v>0.35980000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1.1900999999999999</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.51329999999999998</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.31690000000000002</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.252</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.23050000000000001</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.21460000000000001</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.2079</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0.20610000000000001</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0.20319999999999999</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0.1973</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0.18940000000000001</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0.1802</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0.17030000000000001</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0.1605</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0.152</v>
+      </c>
+      <c r="T10" s="28">
+        <v>0.1555</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0.1608</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0.16470000000000001</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0.1668</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0.1671</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0.1636</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0.16059999999999999</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0.1573</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>0.15479999999999999</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>0.1547</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>0.15809999999999999</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>0.16539999999999999</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>0.1825</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>0.19109999999999999</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>0.19939999999999999</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>0.21129999999999999</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>0.2278</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>0.2465</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>0.3024</v>
+      </c>
+      <c r="AQ10" s="1">
+        <v>0.31709999999999999</v>
+      </c>
+      <c r="AR10" s="1">
+        <v>0.32769999999999999</v>
+      </c>
+      <c r="AS10" s="1">
+        <v>0.3332</v>
+      </c>
+      <c r="AT10" s="1">
+        <v>0.33379999999999999</v>
+      </c>
+      <c r="AU10" s="28">
+        <v>0.3306</v>
+      </c>
+      <c r="AV10" s="1">
+        <v>0.32719999999999999</v>
+      </c>
+      <c r="AW10" s="1">
+        <v>0.32919999999999999</v>
+      </c>
+      <c r="AX10" s="1">
+        <v>0.3453</v>
+      </c>
+      <c r="AY10" s="1">
+        <v>0.3861</v>
+      </c>
+    </row>
+    <row r="11" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="28">
+        <v>0.53849999999999998</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.2414</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.1618</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.1618</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.17050000000000001</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0.17519999999999999</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0.17560000000000001</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0.17230000000000001</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0.1661</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0.15759999999999999</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0.158</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0.1686</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0.18529999999999999</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0.19869999999999999</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0.20849999999999999</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0.21440000000000001</v>
+      </c>
+      <c r="V11" s="28">
+        <v>0.21679999999999999</v>
+      </c>
+      <c r="W11" s="1">
+        <v>0.2157</v>
+      </c>
+      <c r="X11" s="1">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>0.2031</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0.19239999999999999</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>0.1789</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>0.1628</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>0.1454</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>0.13070000000000001</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>0.1246</v>
+      </c>
+      <c r="AF11" s="1">
+        <v>0.13339999999999999</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>0.15939999999999999</v>
+      </c>
+      <c r="AH11" s="1">
+        <v>0.19070000000000001</v>
+      </c>
+      <c r="AI11" s="1">
+        <v>0.224</v>
+      </c>
+      <c r="AJ11" s="1">
+        <v>0.25729999999999997</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>0.29010000000000002</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>0.32069999999999999</v>
+      </c>
+      <c r="AM11" s="28">
+        <v>0.34889999999999999</v>
+      </c>
+      <c r="AN11" s="1">
+        <v>0.3735</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>0.40949999999999998</v>
+      </c>
+      <c r="AQ11" s="1">
+        <v>0.41889999999999999</v>
+      </c>
+      <c r="AR11" s="1">
+        <v>0.42170000000000002</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>0.4173</v>
+      </c>
+      <c r="AT11" s="28">
+        <v>0.40589999999999998</v>
+      </c>
+      <c r="AU11" s="1">
+        <v>0.38929999999999998</v>
+      </c>
+      <c r="AV11" s="1">
+        <v>0.37109999999999999</v>
+      </c>
+      <c r="AW11" s="1">
+        <v>0.36009999999999998</v>
+      </c>
+      <c r="AX11" s="1">
+        <v>0.37030000000000002</v>
+      </c>
+      <c r="AY11" s="28">
+        <v>0.41820000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="28">
+        <v>0.35489999999999999</v>
+      </c>
+      <c r="H12" s="28">
+        <v>0.20150000000000001</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.1754</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.19059999999999999</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.20030000000000001</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0.2031</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0.20180000000000001</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0.19939999999999999</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0.2001</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0.21060000000000001</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0.2235</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0.23719999999999999</v>
+      </c>
+      <c r="S12" s="28">
+        <v>0.25409999999999999</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0.26790000000000003</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0.2767</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0.28070000000000001</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0.28010000000000002</v>
+      </c>
+      <c r="X12" s="1">
+        <v>0.2752</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>0.2661</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0.25359999999999999</v>
+      </c>
+      <c r="AA12" s="28">
+        <v>0.23769999999999999</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>0.21929999999999999</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>0.2014</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0.1918</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>0.21440000000000001</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>0.25480000000000003</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>0.30309999999999998</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>0.35339999999999999</v>
+      </c>
+      <c r="AI12" s="1">
+        <v>0.40129999999999999</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>0.443</v>
+      </c>
+      <c r="AK12" s="1">
+        <v>0.47489999999999999</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>0.49409999999999998</v>
+      </c>
+      <c r="AM12" s="1">
+        <v>0.49919999999999998</v>
+      </c>
+      <c r="AN12" s="1">
+        <v>0.49020000000000002</v>
+      </c>
+      <c r="AO12" s="1">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="AP12" s="1">
+        <v>0.43609999999999999</v>
+      </c>
+      <c r="AQ12" s="1">
+        <v>0.39860000000000001</v>
+      </c>
+      <c r="AR12" s="1">
+        <v>0.35780000000000001</v>
+      </c>
+      <c r="AS12" s="28">
+        <v>0.31419999999999998</v>
+      </c>
+      <c r="AT12" s="1">
+        <v>0.26550000000000001</v>
+      </c>
+      <c r="AU12" s="1">
+        <v>0.2082</v>
+      </c>
+      <c r="AV12" s="1">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AW12" s="28">
+        <v>9.8500000000000004E-2</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>0.2228</v>
+      </c>
+      <c r="AY12" s="1">
+        <v>0.39379999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.26350000000000001</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0.32379999999999998</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0.33029999999999998</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0.33660000000000001</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0.3417</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0.34689999999999999</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>0.35270000000000001</v>
+      </c>
+      <c r="R13" s="1">
+        <v>0.36030000000000001</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0.36830000000000002</v>
+      </c>
+      <c r="T13" s="1">
+        <v>0.37080000000000002</v>
+      </c>
+      <c r="U13" s="1">
+        <v>0.36809999999999998</v>
+      </c>
+      <c r="V13" s="1">
+        <v>0.36130000000000001</v>
+      </c>
+      <c r="W13" s="1">
+        <v>0.35120000000000001</v>
+      </c>
+      <c r="X13" s="1">
+        <v>0.33839999999999998</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>0.3231</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>0.30470000000000003</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>0.2823</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>0.2316</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>0.2094</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>0.24679999999999999</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>0.31669999999999998</v>
+      </c>
+      <c r="AG13" s="1">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>0.48909999999999998</v>
+      </c>
+      <c r="AI13" s="28">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="AJ13" s="28">
+        <v>0.67279999999999995</v>
+      </c>
+      <c r="AK13" s="1">
+        <v>0.75390000000000001</v>
+      </c>
+      <c r="AL13" s="1">
+        <v>0.82279999999999998</v>
+      </c>
+      <c r="AM13" s="1">
+        <v>0.87729999999999997</v>
+      </c>
+      <c r="AN13" s="1">
+        <v>0.9163</v>
+      </c>
+      <c r="AO13" s="1">
+        <v>0.94059999999999999</v>
+      </c>
+      <c r="AP13" s="1">
+        <v>0.95220000000000005</v>
+      </c>
+      <c r="AQ13" s="1">
+        <v>0.95530000000000004</v>
+      </c>
+      <c r="AR13" s="1">
+        <v>0.95579999999999998</v>
+      </c>
+      <c r="AS13" s="1">
+        <v>0.96130000000000004</v>
+      </c>
+      <c r="AT13" s="1">
+        <v>0.98129999999999995</v>
+      </c>
+      <c r="AU13" s="1">
+        <v>1.0258</v>
+      </c>
+      <c r="AV13" s="28">
+        <v>1.1054999999999999</v>
+      </c>
+      <c r="AW13" s="28">
+        <v>1.2307999999999999</v>
+      </c>
+      <c r="AX13" s="1">
+        <v>1.41</v>
+      </c>
+      <c r="AY13" s="1">
+        <v>1.6465000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0.66159999999999997</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0.6502</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0.58640000000000003</v>
+      </c>
+      <c r="P14" s="1">
+        <v>0.63780000000000003</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>0.72350000000000003</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0.80289999999999995</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0.86109999999999998</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0.89239999999999997</v>
+      </c>
+      <c r="U14" s="1">
+        <v>0.90029999999999999</v>
+      </c>
+      <c r="V14" s="28">
+        <v>0.88490000000000002</v>
+      </c>
+      <c r="W14" s="1">
+        <v>0.8508</v>
+      </c>
+      <c r="X14" s="1">
+        <v>0.80489999999999995</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>0.75429999999999997</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>0.70420000000000005</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>0.65559999999999996</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>0.59450000000000003</v>
+      </c>
+      <c r="AC14" s="1">
+        <v>0.52449999999999997</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>0.45329999999999998</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>0.3846</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>0.32479999999999998</v>
+      </c>
+      <c r="AG14" s="1">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="AH14" s="1">
+        <v>0.2661</v>
+      </c>
+      <c r="AI14" s="1">
+        <v>0.29210000000000003</v>
+      </c>
+      <c r="AJ14" s="1">
+        <v>0.35339999999999999</v>
+      </c>
+      <c r="AK14" s="1">
+        <v>0.41970000000000002</v>
+      </c>
+      <c r="AL14" s="1">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="AM14" s="28">
+        <v>0.54259999999999997</v>
+      </c>
+      <c r="AN14" s="1">
+        <v>0.59179999999999999</v>
+      </c>
+      <c r="AO14" s="28">
+        <v>0.62980000000000003</v>
+      </c>
+      <c r="AP14" s="1">
+        <v>0.65949999999999998</v>
+      </c>
+      <c r="AQ14" s="1">
+        <v>0.68689999999999996</v>
+      </c>
+      <c r="AR14" s="1">
+        <v>0.72140000000000004</v>
+      </c>
+      <c r="AS14" s="1">
+        <v>0.77610000000000001</v>
+      </c>
+      <c r="AT14" s="28">
+        <v>0.86819999999999997</v>
+      </c>
+      <c r="AU14" s="1">
+        <v>1.0198</v>
+      </c>
+      <c r="AV14" s="1">
+        <v>1.2606999999999999</v>
+      </c>
+      <c r="AW14" s="1">
+        <v>1.633</v>
+      </c>
+      <c r="AX14" s="1">
+        <v>2.1953999999999998</v>
+      </c>
+      <c r="AY14" s="1">
+        <v>3.0202</v>
+      </c>
+    </row>
+    <row r="15" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="1">
+        <v>4.3574000000000002</v>
+      </c>
+      <c r="S15" s="1">
+        <v>4.0557999999999996</v>
+      </c>
+      <c r="T15" s="1">
+        <v>3.5714999999999999</v>
+      </c>
+      <c r="U15" s="1">
+        <v>3.0200999999999998</v>
+      </c>
+      <c r="V15" s="1">
+        <v>2.4861</v>
+      </c>
+      <c r="W15" s="1">
+        <v>2.0204</v>
+      </c>
+      <c r="X15" s="1">
+        <v>1.6412</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>1.3429</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="AA15" s="28">
+        <v>0.91869999999999996</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>0.76359999999999995</v>
+      </c>
+      <c r="AC15" s="1">
+        <v>0.64139999999999997</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>0.54039999999999999</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>0.4627</v>
+      </c>
+      <c r="AF15" s="1">
+        <v>0.41539999999999999</v>
+      </c>
+      <c r="AG15" s="1">
+        <v>0.40560000000000002</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>0.47070000000000001</v>
+      </c>
+      <c r="AJ15" s="1">
+        <v>0.51780000000000004</v>
+      </c>
+      <c r="AK15" s="1">
+        <v>0.56279999999999997</v>
+      </c>
+      <c r="AL15" s="1">
+        <v>0.60150000000000003</v>
+      </c>
+      <c r="AM15" s="1">
+        <v>0.63149999999999995</v>
+      </c>
+      <c r="AN15" s="1">
+        <v>0.6522</v>
+      </c>
+      <c r="AO15" s="1">
+        <v>0.66339999999999999</v>
+      </c>
+      <c r="AP15" s="1">
+        <v>0.66569999999999996</v>
+      </c>
+      <c r="AQ15" s="1">
+        <v>0.66010000000000002</v>
+      </c>
+      <c r="AR15" s="1">
+        <v>0.64649999999999996</v>
+      </c>
+      <c r="AS15" s="1">
+        <v>0.62439999999999996</v>
+      </c>
+      <c r="AT15" s="1">
+        <v>0.59340000000000004</v>
+      </c>
+      <c r="AU15" s="1">
+        <v>0.55410000000000004</v>
+      </c>
+      <c r="AV15" s="1">
+        <v>0.51919999999999999</v>
+      </c>
+      <c r="AW15" s="28">
+        <v>0.56810000000000005</v>
+      </c>
+      <c r="AX15" s="28">
+        <v>0.78590000000000004</v>
+      </c>
+      <c r="AY15" s="1">
+        <v>1.2672000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C3:AY15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="10"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41562958-9881-4FDB-8D2B-196A9DF91CAF}">
+  <dimension ref="B1:AY15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="51" width="9.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="P2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="R2" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="S2" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="T2" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="U2" s="1">
+        <v>2</v>
+      </c>
+      <c r="V2" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="W2" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X2" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>4</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B3" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.247</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.23430000000000001</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.218</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.19170000000000001</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.12529999999999999</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.11459999999999999</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.1094</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0.1113</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0.1137</v>
+      </c>
+      <c r="M3" s="1">
+        <v>9.9299999999999999E-2</v>
+      </c>
+      <c r="N3" s="1">
+        <v>9.2299999999999993E-2</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.26569999999999999</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.1125</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.31819999999999998</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.24709999999999999</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.2024</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.21310000000000001</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.19409999999999999</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.18590000000000001</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0.16009999999999999</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0.17169999999999999</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.13589999999999999</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0.13639999999999999</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0.1419</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0.13519999999999999</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0.1229</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0.11219999999999999</v>
+      </c>
+      <c r="S4" s="1">
+        <v>9.8799999999999999E-2</v>
+      </c>
+      <c r="T4" s="1">
+        <v>8.6099999999999996E-2</v>
+      </c>
+      <c r="U4" s="1">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="V4" s="1">
+        <v>8.1299999999999997E-2</v>
+      </c>
+      <c r="W4" s="1">
+        <v>6.0299999999999999E-2</v>
+      </c>
+      <c r="X4" s="1">
+        <v>6.2700000000000006E-2</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.31419999999999998</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.23330000000000001</v>
+      </c>
+      <c r="E5" s="28">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.28549999999999998</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.28220000000000001</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.22009999999999999</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.189</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.2162</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0.24149999999999999</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0.2296</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0.1923</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0.1973</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0.17810000000000001</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0.16270000000000001</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0.16139999999999999</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0.1472</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0.12559999999999999</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0.1457</v>
+      </c>
+      <c r="V5" s="1">
+        <v>0.1008</v>
+      </c>
+      <c r="W5" s="1">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0.11559999999999999</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>0.18290000000000001</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>9.3700000000000006E-2</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>9.2899999999999996E-2</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>0.1371</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>0.27810000000000001</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>0.1053</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0.22520000000000001</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>0.3624</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>0.1749</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>0.34789999999999999</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>0.47020000000000001</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>0.14169999999999999</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>0.29330000000000001</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>0.3972</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>0.2082</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>0.34089999999999998</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR5" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="28">
+        <v>0.2429</v>
+      </c>
+      <c r="D6" s="28">
+        <v>0.23980000000000001</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.29110000000000003</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.29770000000000002</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.2525</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.29680000000000001</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.2477</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.22070000000000001</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0.2414</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0.25259999999999999</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.20319999999999999</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0.2155</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0.23780000000000001</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0.21560000000000001</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0.19980000000000001</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0.17610000000000001</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0.1653</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0.25140000000000001</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0.14460000000000001</v>
+      </c>
+      <c r="W6" s="28">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0.26790000000000003</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0.27060000000000001</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0.1651</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0.26869999999999999</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0.47460000000000002</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0.15060000000000001</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>0.2737</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0.44579999999999997</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>0.2291</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>0.37659999999999999</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>0.4214</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>0.24329999999999999</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>0.35110000000000002</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>0.47820000000000001</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>0.33119999999999999</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>0.33460000000000001</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>0.41460000000000002</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>0.3664</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>0.41120000000000001</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>0.29959999999999998</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>0.33489999999999998</v>
+      </c>
+      <c r="AU6" s="28">
+        <v>0.2432</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>0.2651</v>
+      </c>
+      <c r="AW6" s="1">
+        <v>0.1991</v>
+      </c>
+      <c r="AX6" s="1">
+        <v>0.21310000000000001</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>0.33310000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C7" s="28">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="D7" s="28">
+        <v>0.32079999999999997</v>
+      </c>
+      <c r="E7" s="28">
+        <v>0.22420000000000001</v>
+      </c>
+      <c r="F7" s="28">
+        <v>0.20649999999999999</v>
+      </c>
+      <c r="G7" s="28">
+        <v>0.23119999999999999</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.30180000000000001</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.3049</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.29659999999999997</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0.26369999999999999</v>
+      </c>
+      <c r="M7" s="28">
+        <v>0.2702</v>
+      </c>
+      <c r="N7" s="28">
+        <v>0.23350000000000001</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0.25790000000000002</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0.26819999999999999</v>
+      </c>
+      <c r="Q7" s="28">
+        <v>0.25259999999999999</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0.26579999999999998</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0.1973</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0.19070000000000001</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0.21010000000000001</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0.1736</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0.1699</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="Z7" s="28">
+        <v>0.1678</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0.17879999999999999</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>0.26119999999999999</v>
+      </c>
+      <c r="AC7" s="28">
+        <v>0.15609999999999999</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>0.1671</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0.26779999999999998</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>0.1694</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>0.2576</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>0.29409999999999997</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>0.16550000000000001</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>0.24879999999999999</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>0.34889999999999999</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>0.18429999999999999</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>0.25069999999999998</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>0.34570000000000001</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>0.1986</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>0.21429999999999999</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>0.29260000000000003</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>0.2102</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>0.2104</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>0.25090000000000001</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>0.22570000000000001</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>0.20250000000000001</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>0.19639999999999999</v>
+      </c>
+      <c r="AX7" s="1">
+        <v>0.25380000000000003</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>0.21240000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="C8" s="28">
+        <v>0.505</v>
+      </c>
+      <c r="D8" s="28">
+        <v>0.53159999999999996</v>
+      </c>
+      <c r="E8" s="28">
+        <v>1.0649</v>
+      </c>
+      <c r="F8" s="28">
+        <v>0.34150000000000003</v>
+      </c>
+      <c r="G8" s="28">
+        <v>0.1749</v>
+      </c>
+      <c r="H8" s="28">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.30840000000000001</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.31209999999999999</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.3009</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0.308</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0.2823</v>
+      </c>
+      <c r="N8" s="28">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0.24149999999999999</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0.27089999999999997</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0.2278</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0.23980000000000001</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0.21609999999999999</v>
+      </c>
+      <c r="V8" s="1">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0.80059999999999998</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0.2266</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0.16850000000000001</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0.16619999999999999</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0.18190000000000001</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>0.21260000000000001</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>0.60029999999999994</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>0.29160000000000003</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0.42920000000000003</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>0.39389999999999997</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>0.53110000000000002</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>1.1634</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>0.25869999999999999</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>0.31940000000000002</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>0.47670000000000001</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>0.93569999999999998</v>
+      </c>
+      <c r="AM8" s="1">
+        <v>0.33510000000000001</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>0.25509999999999999</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>0.35580000000000001</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>0.2326</v>
+      </c>
+      <c r="AQ8" s="1">
+        <v>0.40379999999999999</v>
+      </c>
+      <c r="AR8" s="1">
+        <v>0.41820000000000002</v>
+      </c>
+      <c r="AS8" s="1">
+        <v>0.45950000000000002</v>
+      </c>
+      <c r="AT8" s="1">
+        <v>0.45469999999999999</v>
+      </c>
+      <c r="AU8" s="1">
+        <v>0.2321</v>
+      </c>
+      <c r="AV8" s="1">
+        <v>0.23139999999999999</v>
+      </c>
+      <c r="AW8" s="1">
+        <v>0.42120000000000002</v>
+      </c>
+      <c r="AX8" s="1">
+        <v>0.3417</v>
+      </c>
+      <c r="AY8" s="1">
+        <v>0.31369999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="28">
+        <v>0.31030000000000002</v>
+      </c>
+      <c r="E9" s="28">
+        <v>0.58340000000000003</v>
+      </c>
+      <c r="F9" s="28">
+        <v>0.49509999999999998</v>
+      </c>
+      <c r="G9" s="28">
+        <v>0.2301</v>
+      </c>
+      <c r="H9" s="28">
+        <v>0.25659999999999999</v>
+      </c>
+      <c r="I9" s="28">
+        <v>0.25009999999999999</v>
+      </c>
+      <c r="J9" s="28">
+        <v>0.29089999999999999</v>
+      </c>
+      <c r="K9" s="28">
+        <v>0.29870000000000002</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0.32369999999999999</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0.31340000000000001</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0.31640000000000001</v>
+      </c>
+      <c r="P9" s="1">
+        <v>0.32190000000000002</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0.32050000000000001</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0.26690000000000003</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0.30380000000000001</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0.31140000000000001</v>
+      </c>
+      <c r="V9" s="1">
+        <v>0.28760000000000002</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0.34770000000000001</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0.1827</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>0.28120000000000001</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0.1512</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0.67600000000000005</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0.27860000000000001</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>0.31859999999999999</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0.19550000000000001</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0.27339999999999998</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>0.2424</v>
+      </c>
+      <c r="AG9" s="28">
+        <v>0.4415</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0.3009</v>
+      </c>
+      <c r="AI9" s="28">
+        <v>1.2139</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>0.32579999999999998</v>
+      </c>
+      <c r="AK9" s="1">
+        <v>0.29780000000000001</v>
+      </c>
+      <c r="AL9" s="28">
+        <v>0.22040000000000001</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>0.24030000000000001</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>0.3357</v>
+      </c>
+      <c r="AO9" s="28">
+        <v>0.37740000000000001</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>0.24610000000000001</v>
+      </c>
+      <c r="AQ9" s="1">
+        <v>0.41370000000000001</v>
+      </c>
+      <c r="AR9" s="1">
+        <v>0.2853</v>
+      </c>
+      <c r="AS9" s="1">
+        <v>0.4254</v>
+      </c>
+      <c r="AT9" s="1">
+        <v>0.30059999999999998</v>
+      </c>
+      <c r="AU9" s="1">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="AV9" s="1">
+        <v>1.3902000000000001</v>
+      </c>
+      <c r="AW9" s="1">
+        <v>0.52270000000000005</v>
+      </c>
+      <c r="AX9" s="28">
+        <v>4.9379999999999997E+49</v>
+      </c>
+      <c r="AY9" s="1">
+        <v>0.26869999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="28">
+        <v>0.32319999999999999</v>
+      </c>
+      <c r="F10" s="28">
+        <v>2.0701000000000001</v>
+      </c>
+      <c r="G10" s="28">
+        <v>0.2011</v>
+      </c>
+      <c r="H10" s="28">
+        <v>0.25569999999999998</v>
+      </c>
+      <c r="I10" s="28">
+        <v>0.27950000000000003</v>
+      </c>
+      <c r="J10" s="28">
+        <v>0.30309999999999998</v>
+      </c>
+      <c r="K10" s="28">
+        <v>0.45369999999999999</v>
+      </c>
+      <c r="L10" s="28">
+        <v>0.3679</v>
+      </c>
+      <c r="M10" s="28">
+        <v>0.32850000000000001</v>
+      </c>
+      <c r="N10" s="28">
+        <v>0.31590000000000001</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0.30570000000000003</v>
+      </c>
+      <c r="P10" s="1">
+        <v>0.25950000000000001</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0.34510000000000002</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0.1608</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="T10" s="28">
+        <v>0.26960000000000001</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0.19539999999999999</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0.2984</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0.13089999999999999</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0.22969999999999999</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0.1236</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0.23780000000000001</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0.40679999999999999</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>0.27010000000000001</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>0.21609999999999999</v>
+      </c>
+      <c r="AF10" s="1">
+        <v>0.21640000000000001</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>0.26319999999999999</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>0.2535</v>
+      </c>
+      <c r="AI10" s="1">
+        <v>0.19819999999999999</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>0.2011</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>0.3533</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>0.26169999999999999</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>0.30370000000000003</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>0.32750000000000001</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>0.47460000000000002</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>0.49519999999999997</v>
+      </c>
+      <c r="AQ10" s="1">
+        <v>0.31640000000000001</v>
+      </c>
+      <c r="AR10" s="1">
+        <v>0.5323</v>
+      </c>
+      <c r="AS10" s="1">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AT10" s="1">
+        <v>0.56950000000000001</v>
+      </c>
+      <c r="AU10" s="28">
+        <v>0.32619999999999999</v>
+      </c>
+      <c r="AV10" s="1">
+        <v>0.63460000000000005</v>
+      </c>
+      <c r="AW10" s="1">
+        <v>0.71879999999999999</v>
+      </c>
+      <c r="AX10" s="1">
+        <v>0.76470000000000005</v>
+      </c>
+      <c r="AY10" s="1">
+        <v>0.78349999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="28">
+        <v>0.24110000000000001</v>
+      </c>
+      <c r="G11" s="28">
+        <v>2.8894000000000002</v>
+      </c>
+      <c r="H11" s="28">
+        <v>0.49249999999999999</v>
+      </c>
+      <c r="I11" s="28">
+        <v>0.29680000000000001</v>
+      </c>
+      <c r="J11" s="28">
+        <v>0.40379999999999999</v>
+      </c>
+      <c r="K11" s="28">
+        <v>0.57830000000000004</v>
+      </c>
+      <c r="L11" s="28">
+        <v>0.60070000000000001</v>
+      </c>
+      <c r="M11" s="28">
+        <v>0.3528</v>
+      </c>
+      <c r="N11" s="28">
+        <v>0.37830000000000003</v>
+      </c>
+      <c r="O11" s="28">
+        <v>0.41920000000000002</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0.15790000000000001</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0.15909999999999999</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0.25740000000000002</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0.17710000000000001</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0.2001</v>
+      </c>
+      <c r="V11" s="28">
+        <v>0.1973</v>
+      </c>
+      <c r="W11" s="1">
+        <v>0.21640000000000001</v>
+      </c>
+      <c r="X11" s="1">
+        <v>0.1976</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>0.14430000000000001</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0.27160000000000001</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>0.33040000000000003</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>0.69720000000000004</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>0.16980000000000001</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>0.32440000000000002</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>0.31769999999999998</v>
+      </c>
+      <c r="AF11" s="1">
+        <v>0.4259</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>0.443</v>
+      </c>
+      <c r="AH11" s="1">
+        <v>0.3448</v>
+      </c>
+      <c r="AI11" s="1">
+        <v>0.3659</v>
+      </c>
+      <c r="AJ11" s="1">
+        <v>0.4647</v>
+      </c>
+      <c r="AK11" s="1">
+        <v>0.5585</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>0.496</v>
+      </c>
+      <c r="AM11" s="28">
+        <v>0.58720000000000006</v>
+      </c>
+      <c r="AN11" s="1">
+        <v>0.68240000000000001</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>0.64680000000000004</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>0.36049999999999999</v>
+      </c>
+      <c r="AQ11" s="1">
+        <v>0.69840000000000002</v>
+      </c>
+      <c r="AR11" s="1">
+        <v>0.79469999999999996</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>0.68369999999999997</v>
+      </c>
+      <c r="AT11" s="28">
+        <v>0.871</v>
+      </c>
+      <c r="AU11" s="1">
+        <v>0.82889999999999997</v>
+      </c>
+      <c r="AV11" s="1">
+        <v>0.96660000000000001</v>
+      </c>
+      <c r="AW11" s="1">
+        <v>0.87370000000000003</v>
+      </c>
+      <c r="AX11" s="1">
+        <v>1.1305000000000001</v>
+      </c>
+      <c r="AY11" s="28">
+        <v>1.1026</v>
+      </c>
+    </row>
+    <row r="12" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="28">
+        <v>0.30840000000000001</v>
+      </c>
+      <c r="H12" s="28">
+        <v>0.2104</v>
+      </c>
+      <c r="I12" s="28">
+        <v>0.87029999999999996</v>
+      </c>
+      <c r="J12" s="28">
+        <v>0.47460000000000002</v>
+      </c>
+      <c r="K12" s="28">
+        <v>0.48409999999999997</v>
+      </c>
+      <c r="L12" s="28">
+        <v>0.43290000000000001</v>
+      </c>
+      <c r="M12" s="28">
+        <v>1.0648</v>
+      </c>
+      <c r="N12" s="28">
+        <v>0.26910000000000001</v>
+      </c>
+      <c r="O12" s="28">
+        <v>0.37069999999999997</v>
+      </c>
+      <c r="P12" s="28">
+        <v>0.56510000000000005</v>
+      </c>
+      <c r="Q12" s="28">
+        <v>0.2422</v>
+      </c>
+      <c r="R12" s="28">
+        <v>0.42880000000000001</v>
+      </c>
+      <c r="S12" s="28">
+        <v>0.27989999999999998</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0.41489999999999999</v>
+      </c>
+      <c r="U12" s="1">
+        <v>0.39350000000000002</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0.26629999999999998</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0.2271</v>
+      </c>
+      <c r="X12" s="1">
+        <v>0.33119999999999999</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>0.3871</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="AA12" s="28">
+        <v>0.2893</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>0.45400000000000001</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>0.2084</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0.43440000000000001</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>1.0934999999999999</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>0.377</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>1.2218</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>0.75719999999999998</v>
+      </c>
+      <c r="AI12" s="28">
+        <v>0.6925</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>0.38769999999999999</v>
+      </c>
+      <c r="AK12" s="28">
+        <v>0.80449999999999999</v>
+      </c>
+      <c r="AL12" s="1">
+        <v>0.42859999999999998</v>
+      </c>
+      <c r="AM12" s="28">
+        <v>0.55179999999999996</v>
+      </c>
+      <c r="AN12" s="28">
+        <v>0.63629999999999998</v>
+      </c>
+      <c r="AO12" s="28">
+        <v>0.47199999999999998</v>
+      </c>
+      <c r="AP12" s="28">
+        <v>0.59930000000000005</v>
+      </c>
+      <c r="AQ12" s="28">
+        <v>0.3085</v>
+      </c>
+      <c r="AR12" s="28">
+        <v>0.61060000000000003</v>
+      </c>
+      <c r="AS12" s="28">
+        <v>0.45269999999999999</v>
+      </c>
+      <c r="AT12" s="28">
+        <v>0.72629999999999995</v>
+      </c>
+      <c r="AU12" s="28">
+        <v>0.93230000000000002</v>
+      </c>
+      <c r="AV12" s="28">
+        <v>0.92800000000000005</v>
+      </c>
+      <c r="AW12" s="28">
+        <v>1.1324000000000001</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>1.177</v>
+      </c>
+      <c r="AY12" s="1">
+        <v>0.87539999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="28">
+        <v>13.627599999999999</v>
+      </c>
+      <c r="J13" s="28">
+        <v>0.3821</v>
+      </c>
+      <c r="K13" s="28">
+        <v>3.7606999999999999</v>
+      </c>
+      <c r="L13" s="28">
+        <v>0.57820000000000005</v>
+      </c>
+      <c r="M13" s="28">
+        <v>1.8177000000000001</v>
+      </c>
+      <c r="N13" s="28">
+        <v>0.43759999999999999</v>
+      </c>
+      <c r="O13" s="28">
+        <v>0.37080000000000002</v>
+      </c>
+      <c r="P13" s="28">
+        <v>0.37009999999999998</v>
+      </c>
+      <c r="Q13" s="28">
+        <v>0.48659999999999998</v>
+      </c>
+      <c r="R13" s="28">
+        <v>0.4924</v>
+      </c>
+      <c r="S13" s="28">
+        <v>0.41570000000000001</v>
+      </c>
+      <c r="T13" s="28">
+        <v>0.53069999999999995</v>
+      </c>
+      <c r="U13" s="28">
+        <v>0.40529999999999999</v>
+      </c>
+      <c r="V13" s="28">
+        <v>0.48139999999999999</v>
+      </c>
+      <c r="W13" s="28">
+        <v>0.45490000000000003</v>
+      </c>
+      <c r="X13" s="1">
+        <v>0.4798</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>0.58289999999999997</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>0.83140000000000003</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>0.48820000000000002</v>
+      </c>
+      <c r="AC13" s="1">
+        <v>0.97550000000000003</v>
+      </c>
+      <c r="AD13" s="1">
+        <v>0.54969999999999997</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>0.75019999999999998</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>0.44209999999999999</v>
+      </c>
+      <c r="AG13" s="1">
+        <v>1.1365000000000001</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>0.81869999999999998</v>
+      </c>
+      <c r="AI13" s="28">
+        <v>0.71179999999999999</v>
+      </c>
+      <c r="AJ13" s="28">
+        <v>0.5353</v>
+      </c>
+      <c r="AK13" s="1">
+        <v>0.92269999999999996</v>
+      </c>
+      <c r="AL13" s="1">
+        <v>0.79730000000000001</v>
+      </c>
+      <c r="AM13" s="28">
+        <v>0.62749999999999995</v>
+      </c>
+      <c r="AN13" s="28">
+        <v>0.56130000000000002</v>
+      </c>
+      <c r="AO13" s="28">
+        <v>0.83120000000000005</v>
+      </c>
+      <c r="AP13" s="28">
+        <v>0.63980000000000004</v>
+      </c>
+      <c r="AQ13" s="28">
+        <v>0.38850000000000001</v>
+      </c>
+      <c r="AR13" s="28">
+        <v>0.93940000000000001</v>
+      </c>
+      <c r="AS13" s="28">
+        <v>1.2112000000000001</v>
+      </c>
+      <c r="AT13" s="28">
+        <v>1.0258</v>
+      </c>
+      <c r="AU13" s="28">
+        <v>0.91959999999999997</v>
+      </c>
+      <c r="AV13" s="28">
+        <v>0.68379999999999996</v>
+      </c>
+      <c r="AW13" s="28">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="AX13" s="28">
+        <v>0.8911</v>
+      </c>
+      <c r="AY13" s="28">
+        <v>0.93289999999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="28">
+        <v>0.49419999999999997</v>
+      </c>
+      <c r="M14" s="28">
+        <v>0.9728</v>
+      </c>
+      <c r="N14" s="28">
+        <v>0.68640000000000001</v>
+      </c>
+      <c r="O14" s="28">
+        <v>0.55120000000000002</v>
+      </c>
+      <c r="P14" s="28">
+        <v>0.81979999999999997</v>
+      </c>
+      <c r="Q14" s="28">
+        <v>0.70289999999999997</v>
+      </c>
+      <c r="R14" s="28">
+        <v>0.68440000000000001</v>
+      </c>
+      <c r="S14" s="28">
+        <v>0.91339999999999999</v>
+      </c>
+      <c r="T14" s="28">
+        <v>0.85909999999999997</v>
+      </c>
+      <c r="U14" s="28">
+        <v>1.2137</v>
+      </c>
+      <c r="V14" s="28">
+        <v>0.79779999999999995</v>
+      </c>
+      <c r="W14" s="28">
+        <v>3.4697</v>
+      </c>
+      <c r="X14" s="28">
+        <v>1.0852999999999999</v>
+      </c>
+      <c r="Y14" s="28">
+        <v>0.93630000000000002</v>
+      </c>
+      <c r="Z14" s="28">
+        <v>1.7565999999999999</v>
+      </c>
+      <c r="AA14" s="28">
+        <v>1.651</v>
+      </c>
+      <c r="AB14" s="28">
+        <v>0.41289999999999999</v>
+      </c>
+      <c r="AC14" s="28">
+        <v>1.405</v>
+      </c>
+      <c r="AD14" s="28">
+        <v>2.7951999999999999</v>
+      </c>
+      <c r="AE14" s="28">
+        <v>2.9483000000000001</v>
+      </c>
+      <c r="AF14" s="28">
+        <v>1.3117000000000001</v>
+      </c>
+      <c r="AG14" s="28">
+        <v>0.52410000000000001</v>
+      </c>
+      <c r="AH14" s="1">
+        <v>1.5995999999999999</v>
+      </c>
+      <c r="AI14" s="28">
+        <v>0.97589999999999999</v>
+      </c>
+      <c r="AJ14" s="28">
+        <v>0.52759999999999996</v>
+      </c>
+      <c r="AK14" s="28">
+        <v>0.9899</v>
+      </c>
+      <c r="AL14" s="1">
+        <v>3.2783000000000002</v>
+      </c>
+      <c r="AM14" s="28">
+        <v>2.2292000000000001</v>
+      </c>
+      <c r="AN14" s="28">
+        <v>1.905</v>
+      </c>
+      <c r="AO14" s="28">
+        <v>2.4291999999999998</v>
+      </c>
+      <c r="AP14" s="28">
+        <v>1.8466</v>
+      </c>
+      <c r="AQ14" s="28">
+        <v>1.9795</v>
+      </c>
+      <c r="AR14" s="28">
+        <v>1.9478</v>
+      </c>
+      <c r="AS14" s="28">
+        <v>1.2199</v>
+      </c>
+      <c r="AT14" s="28">
+        <v>1.5215000000000001</v>
+      </c>
+      <c r="AU14" s="28">
+        <v>2.1793999999999998</v>
+      </c>
+      <c r="AV14" s="28">
+        <v>2.9323999999999999</v>
+      </c>
+      <c r="AW14" s="28">
+        <v>2.9104999999999999</v>
+      </c>
+      <c r="AX14" s="28">
+        <v>1.9217</v>
+      </c>
+      <c r="AY14" s="28">
+        <v>0.35089999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="28">
+        <v>41.144100000000002</v>
+      </c>
+      <c r="S15" s="28">
+        <v>1.2357</v>
+      </c>
+      <c r="T15" s="28">
+        <v>1.1204000000000001</v>
+      </c>
+      <c r="U15" s="28">
+        <v>1.2765</v>
+      </c>
+      <c r="V15" s="28">
+        <v>100.4384</v>
+      </c>
+      <c r="W15" s="28">
+        <v>1.9205000000000001</v>
+      </c>
+      <c r="X15" s="28">
+        <v>2.2953000000000001</v>
+      </c>
+      <c r="Y15" s="28">
+        <v>2.456</v>
+      </c>
+      <c r="Z15" s="28">
+        <v>2.5085999999999999</v>
+      </c>
+      <c r="AA15" s="28">
+        <v>15.668799999999999</v>
+      </c>
+      <c r="AB15" s="28">
+        <v>5.1798000000000002</v>
+      </c>
+      <c r="AC15" s="28">
+        <v>3.5949</v>
+      </c>
+      <c r="AD15" s="28">
+        <v>1.4345000000000001</v>
+      </c>
+      <c r="AE15" s="28">
+        <v>0.42580000000000001</v>
+      </c>
+      <c r="AF15" s="28">
+        <v>1.6500999999999999</v>
+      </c>
+      <c r="AG15" s="28">
+        <v>1.3920999999999999</v>
+      </c>
+      <c r="AH15" s="28">
+        <v>2.165</v>
+      </c>
+      <c r="AI15" s="28">
+        <v>0.68310000000000004</v>
+      </c>
+      <c r="AJ15" s="28">
+        <v>1.6545000000000001</v>
+      </c>
+      <c r="AK15" s="28">
+        <v>1.0805</v>
+      </c>
+      <c r="AL15" s="28">
+        <v>1.8096000000000001</v>
+      </c>
+      <c r="AM15" s="28">
+        <v>0.87719999999999998</v>
+      </c>
+      <c r="AN15" s="28">
+        <v>1.8569</v>
+      </c>
+      <c r="AO15" s="28">
+        <v>3.0882999999999998</v>
+      </c>
+      <c r="AP15" s="28">
+        <v>1.7862</v>
+      </c>
+      <c r="AQ15" s="28">
+        <v>2.8898000000000001</v>
+      </c>
+      <c r="AR15" s="28">
+        <v>4.2367999999999997</v>
+      </c>
+      <c r="AS15" s="28">
+        <v>5.2419000000000002</v>
+      </c>
+      <c r="AT15" s="28">
+        <v>4.3381999999999996</v>
+      </c>
+      <c r="AU15" s="28">
+        <v>0.65900000000000003</v>
+      </c>
+      <c r="AV15" s="28">
+        <v>1.1178999999999999</v>
+      </c>
+      <c r="AW15" s="28">
+        <v>2.3780000000000001</v>
+      </c>
+      <c r="AX15" s="28">
+        <v>1.2301</v>
+      </c>
+      <c r="AY15" s="28">
+        <v>1.9853000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C3:AY15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="200"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9795A190-BFBD-49A6-B2BC-4EB11AD4D948}">
+  <dimension ref="B1:AY15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="51" width="6.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:51" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="P2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="R2" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="S2" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="T2" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="U2" s="1">
+        <v>2</v>
+      </c>
+      <c r="V2" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="W2" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X2" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>2.7</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>2.9</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>3</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>3.1</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="AI2" s="1">
+        <v>3.4</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>3.8</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>4</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="AR2" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="AU2" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="AX2" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AY2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B3" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.31669999999999998</v>
+      </c>
+      <c r="D3" s="28">
+        <v>0.32550000000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.31180000000000002</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.2797</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.1865</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.1545</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0.12770000000000001</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0.14069999999999999</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0.1113</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0.1105</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0.1012</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0.1062</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.20860000000000001</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.29759999999999998</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.29909999999999998</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.26269999999999999</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.21820000000000001</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.2384</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.23469999999999999</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0.1933</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0.18959999999999999</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0.1958</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0.1802</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0.1716</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0.1527</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0.1221</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0.1338</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0.1193</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0.1022</v>
+      </c>
+      <c r="T4" s="1">
+        <v>8.8700000000000001E-2</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0.1074</v>
+      </c>
+      <c r="V4" s="1">
+        <v>9.3100000000000002E-2</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0.13039999999999999</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0.2092</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>0.14649999999999999</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0.66110000000000002</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>0.69710000000000005</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1.2715000000000001</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.30059999999999998</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.2959</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.25590000000000002</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0.18940000000000001</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0.1777</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0.21110000000000001</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0.2082</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0.1968</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0.1721</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0.1734</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0.1512</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0.59750000000000003</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0.66969999999999996</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0.35010000000000002</v>
+      </c>
+      <c r="V5" s="1">
+        <v>0.65610000000000002</v>
+      </c>
+      <c r="W5" s="1">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0.90239999999999998</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>1.0049999999999999</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>0.2276</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>0.78480000000000005</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>1.4414</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>0.11840000000000001</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>0.10829999999999999</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>0.1197</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>0.23830000000000001</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>0.20949999999999999</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>0.1376</v>
+      </c>
+      <c r="AJ5" s="28">
+        <v>0.1908</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>0.19650000000000001</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>0.21460000000000001</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>0.26469999999999999</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>0.27429999999999999</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>0.31590000000000001</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>0.58389999999999997</v>
+      </c>
+      <c r="AR5" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="28">
+        <v>0.29770000000000002</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.30470000000000003</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.24210000000000001</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0.22550000000000001</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0.20669999999999999</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0.27229999999999999</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0.21709999999999999</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0.31780000000000003</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0.59670000000000001</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0.88949999999999996</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0.83350000000000002</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0.9113</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0.8246</v>
+      </c>
+      <c r="W6" s="28">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0.86060000000000003</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>1.0504</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0.188</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0.13120000000000001</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0.1079</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0.18529999999999999</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>0.51539999999999997</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0.30309999999999998</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>0.2747</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>0.34329999999999999</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>0.36830000000000002</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>0.15390000000000001</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>0.2044</v>
+      </c>
+      <c r="AL6" s="1">
+        <v>0.27550000000000002</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>0.23810000000000001</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>0.43940000000000001</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>0.44009999999999999</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>1.4469000000000001</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>0.2203</v>
+      </c>
+      <c r="AR6" s="1">
+        <v>0.17419999999999999</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>0.23130000000000001</v>
+      </c>
+      <c r="AT6" s="1">
+        <v>0.22320000000000001</v>
+      </c>
+      <c r="AU6" s="28">
+        <v>0.26390000000000002</v>
+      </c>
+      <c r="AV6" s="1">
+        <v>0.3962</v>
+      </c>
+      <c r="AW6" s="1">
+        <v>0.36009999999999998</v>
+      </c>
+      <c r="AX6" s="1">
+        <v>0.22739999999999999</v>
+      </c>
+      <c r="AY6" s="1">
+        <v>0.63549999999999995</v>
+      </c>
+    </row>
+    <row r="7" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C7" s="28">
+        <v>0.38769999999999999</v>
+      </c>
+      <c r="D7" s="28">
+        <v>0.32550000000000001</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="28">
+        <v>0.32050000000000001</v>
+      </c>
+      <c r="G7" s="28">
+        <v>0.18529999999999999</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.13850000000000001</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.18160000000000001</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.30580000000000002</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0.3024</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="28">
+        <v>0.92769999999999997</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0.3478</v>
+      </c>
+      <c r="Q7" s="28">
+        <v>0.25869999999999999</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X7" s="28">
+        <v>0.82250000000000001</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>0.31690000000000002</v>
+      </c>
+      <c r="AC7" s="28">
+        <v>0.1598</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>0.14560000000000001</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0.41039999999999999</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>0.15459999999999999</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>0.1915</v>
+      </c>
+      <c r="AH7" s="1">
+        <v>0.16339999999999999</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>0.18429999999999999</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>0.18740000000000001</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>0.2041</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>0.25319999999999998</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>0.25009999999999999</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>0.28910000000000002</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>0.23219999999999999</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="AR7" s="1">
+        <v>0.20910000000000001</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>0.221</v>
+      </c>
+      <c r="AT7" s="1">
+        <v>0.2142</v>
+      </c>
+      <c r="AU7" s="1">
+        <v>0.24360000000000001</v>
+      </c>
+      <c r="AV7" s="1">
+        <v>0.31909999999999999</v>
+      </c>
+      <c r="AW7" s="1">
+        <v>0.2218</v>
+      </c>
+      <c r="AX7" s="1">
+        <v>0.28039999999999998</v>
+      </c>
+      <c r="AY7" s="1">
+        <v>0.21060000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="C8" s="28">
+        <v>0.3851</v>
+      </c>
+      <c r="D8" s="28">
+        <v>3.8068</v>
+      </c>
+      <c r="E8" s="28">
+        <v>0.32029999999999997</v>
+      </c>
+      <c r="F8" s="28">
+        <v>0.36370000000000002</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="28">
+        <v>0.29370000000000002</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.31630000000000003</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0.30549999999999999</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.30919999999999997</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0.29260000000000003</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0.21909999999999999</v>
+      </c>
+      <c r="N8" s="28">
+        <v>1.1304000000000001</v>
+      </c>
+      <c r="O8" s="28">
+        <v>2.1558000000000001E+193</v>
+      </c>
+      <c r="P8" s="28">
+        <v>2.2723999999999999E+53</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0.23810000000000001</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0.2306</v>
+      </c>
+      <c r="V8" s="1">
+        <v>0.18990000000000001</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0.68979999999999997</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0.20330000000000001</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0.39119999999999999</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>0.1852</v>
+      </c>
+      <c r="AG8" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="28">
+        <v>5.4966E+138</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>0.40789999999999998</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>1.0907</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>0.63880000000000003</v>
+      </c>
+      <c r="AL8" s="1">
+        <v>0.3765</v>
+      </c>
+      <c r="AM8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="28">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>0.33939999999999998</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>0.36099999999999999</v>
+      </c>
+      <c r="AQ8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR8" s="28">
+        <v>1.1339E+16</v>
+      </c>
+      <c r="AS8" s="1">
+        <v>0.62380000000000002</v>
+      </c>
+      <c r="AT8" s="1">
+        <v>0.53190000000000004</v>
+      </c>
+      <c r="AU8" s="1">
+        <v>0.377</v>
+      </c>
+      <c r="AV8" s="1">
+        <v>0.38129999999999997</v>
+      </c>
+      <c r="AW8" s="1">
+        <v>0.4844</v>
+      </c>
+      <c r="AX8" s="1">
+        <v>0.44479999999999997</v>
+      </c>
+      <c r="AY8" s="1">
+        <v>0.59279999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="28">
+        <v>0.33739999999999998</v>
+      </c>
+      <c r="E9" s="28">
+        <v>0.2661</v>
+      </c>
+      <c r="F9" s="28">
+        <v>1.1209</v>
+      </c>
+      <c r="G9" s="28">
+        <v>0.2029</v>
+      </c>
+      <c r="H9" s="28">
+        <v>0.31140000000000001</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="28">
+        <v>0.30330000000000001</v>
+      </c>
+      <c r="K9" s="28">
+        <v>0.2218</v>
+      </c>
+      <c r="L9" s="1">
+        <v>2.2965</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0.31559999999999999</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0.315</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0.21510000000000001</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0.26910000000000001</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0.34379999999999999</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0.3332</v>
+      </c>
+      <c r="U9" s="1">
+        <v>1.0928</v>
+      </c>
+      <c r="V9" s="28">
+        <v>1.2883E+122</v>
+      </c>
+      <c r="W9" s="1">
+        <v>0.311</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="28">
+        <v>5.1162E+44</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0.2944</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0.27789999999999998</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0.51619999999999999</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>1.3091999999999999</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>0.44219999999999998</v>
+      </c>
+      <c r="AG9" s="28">
+        <v>0.48270000000000002</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="AI9" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM9" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>0.52010000000000001</v>
+      </c>
+      <c r="AO9" s="28">
+        <v>0.46039999999999998</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>0.50509999999999999</v>
+      </c>
+      <c r="AQ9" s="1">
+        <v>0.60009999999999997</v>
+      </c>
+      <c r="AR9" s="1">
+        <v>0.27289999999999998</v>
+      </c>
+      <c r="AS9" s="1">
+        <v>0.62290000000000001</v>
+      </c>
+      <c r="AT9" s="1">
+        <v>0.42180000000000001</v>
+      </c>
+      <c r="AU9" s="1">
+        <v>0.65080000000000005</v>
+      </c>
+      <c r="AV9" s="1">
+        <v>0.6452</v>
+      </c>
+      <c r="AW9" s="1">
+        <v>0.55840000000000001</v>
+      </c>
+      <c r="AX9" s="28">
+        <v>0.61450000000000005</v>
+      </c>
+      <c r="AY9" s="28" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="28">
+        <v>0.54630000000000001</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="28">
+        <v>0.90849999999999997</v>
+      </c>
+      <c r="I10" s="28">
+        <v>0.37340000000000001</v>
+      </c>
+      <c r="J10" s="28">
+        <v>0.18260000000000001</v>
+      </c>
+      <c r="K10" s="28">
+        <v>0.2354</v>
+      </c>
+      <c r="L10" s="28">
+        <v>0.2389</v>
+      </c>
+      <c r="M10" s="28">
+        <v>0.1457</v>
+      </c>
+      <c r="N10" s="28">
+        <v>0.33660000000000001</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0.34620000000000001</v>
+      </c>
+      <c r="P10" s="1">
+        <v>2.3542999999999998</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0.13969999999999999</v>
+      </c>
+      <c r="R10" s="1">
+        <v>1.0515000000000001</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0.8669</v>
+      </c>
+      <c r="T10" s="28">
+        <v>0.15</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0.41639999999999999</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0.26729999999999998</v>
+      </c>
+      <c r="X10" s="28">
+        <v>0.1239</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0.17949999999999999</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0.45269999999999999</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0.246</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>0.3367</v>
+      </c>
+      <c r="AF10" s="28">
+        <v>7.9279999999999997E+118</v>
+      </c>
+      <c r="AG10" s="1">
+        <v>0.73209999999999997</v>
+      </c>
+      <c r="AH10" s="1">
+        <v>0.32919999999999999</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="1">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="AL10" s="1">
+        <v>0.41060000000000002</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>0.62409999999999999</v>
+      </c>
+      <c r="AN10" s="1">
+        <v>0.63939999999999997</v>
+      </c>
+      <c r="AO10" s="1">
+        <v>0.66120000000000001</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="AQ10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="1">
+        <v>7.8324999999999996</v>
+      </c>
+      <c r="AS10" s="1">
+        <v>0.55089999999999995</v>
+      </c>
+      <c r="AT10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU10" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV10" s="1">
+        <v>0.44419999999999998</v>
+      </c>
+      <c r="AW10" s="1">
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="AX10" s="1">
+        <v>0.90680000000000005</v>
+      </c>
+      <c r="AY10" s="28">
+        <v>0.72629999999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="28">
+        <v>157860000</v>
+      </c>
+      <c r="G11" s="28">
+        <v>0.22570000000000001</v>
+      </c>
+      <c r="H11" s="28">
+        <v>0.49249999999999999</v>
+      </c>
+      <c r="I11" s="28">
+        <v>0.48259999999999997</v>
+      </c>
+      <c r="J11" s="28">
+        <v>0.2545</v>
+      </c>
+      <c r="K11" s="28">
+        <v>0.23619999999999999</v>
+      </c>
+      <c r="L11" s="28">
+        <v>2.5735000000000001</v>
+      </c>
+      <c r="M11" s="28">
+        <v>0.19539999999999999</v>
+      </c>
+      <c r="N11" s="28">
+        <v>0.1794</v>
+      </c>
+      <c r="O11" s="28">
+        <v>0.33110000000000001</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>2.5213000000000001</v>
+      </c>
+      <c r="R11" s="1">
+        <v>20.243600000000001</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0.37590000000000001</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0.26190000000000002</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0.18010000000000001</v>
+      </c>
+      <c r="V11" s="28">
+        <v>1.6922999999999999</v>
+      </c>
+      <c r="W11" s="1">
+        <v>0.49659999999999999</v>
+      </c>
+      <c r="X11" s="1">
+        <v>0.3261</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>0.50239999999999996</v>
+      </c>
+      <c r="Z11" s="28">
+        <v>0.20319999999999999</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>0.31869999999999998</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>0.24579999999999999</v>
+      </c>
+      <c r="AC11" s="1">
+        <v>1.0382</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>0.33779999999999999</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>0.26340000000000002</v>
+      </c>
+      <c r="AF11" s="1">
+        <v>0.55469999999999997</v>
+      </c>
+      <c r="AG11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL11" s="1">
+        <v>0.6159</v>
+      </c>
+      <c r="AM11" s="28">
+        <v>0.70009999999999994</v>
+      </c>
+      <c r="AN11" s="1">
+        <v>0.80420000000000003</v>
+      </c>
+      <c r="AO11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>0.29859999999999998</v>
+      </c>
+      <c r="AQ11" s="1">
+        <v>0.87329999999999997</v>
+      </c>
+      <c r="AR11" s="1">
+        <v>0.89639999999999997</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>0.79910000000000003</v>
+      </c>
+      <c r="AT11" s="28">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="AU11" s="1">
+        <v>1.0609</v>
+      </c>
+      <c r="AV11" s="1">
+        <v>1.0114000000000001</v>
+      </c>
+      <c r="AW11" s="1">
+        <v>0.9355</v>
+      </c>
+      <c r="AX11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY11" s="28">
+        <v>1.3186</v>
+      </c>
+    </row>
+    <row r="12" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="28">
+        <v>0.1754</v>
+      </c>
+      <c r="H12" s="28">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="I12" s="28">
+        <v>0.18859999999999999</v>
+      </c>
+      <c r="J12" s="28">
+        <v>1.0025999999999999</v>
+      </c>
+      <c r="K12" s="28">
+        <v>0.30359999999999998</v>
+      </c>
+      <c r="L12" s="28">
+        <v>1.5008999999999999</v>
+      </c>
+      <c r="M12" s="28">
+        <v>0.1973</v>
+      </c>
+      <c r="N12" s="28">
+        <v>2.1695000000000002</v>
+      </c>
+      <c r="O12" s="28">
+        <v>0.44340000000000002</v>
+      </c>
+      <c r="P12" s="28">
+        <v>0.39229999999999998</v>
+      </c>
+      <c r="Q12" s="28">
+        <v>0.50580000000000003</v>
+      </c>
+      <c r="R12" s="28">
+        <v>0.69969999999999999</v>
+      </c>
+      <c r="S12" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="T12" s="1">
+        <v>1.0103</v>
+      </c>
+      <c r="U12" s="1">
+        <v>3.0975999999999999</v>
+      </c>
+      <c r="V12" s="1">
+        <v>0.2732</v>
+      </c>
+      <c r="W12" s="1">
+        <v>0.2215</v>
+      </c>
+      <c r="X12" s="1">
+        <v>0.62119999999999997</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>1.0694999999999999</v>
+      </c>
+      <c r="Z12" s="28">
+        <v>3.9796000000000001E+142</v>
+      </c>
+      <c r="AA12" s="28">
+        <v>0.39379999999999998</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>2.8372000000000002</v>
+      </c>
+      <c r="AC12" s="1">
+        <v>0.64419999999999999</v>
+      </c>
+      <c r="AD12" s="1">
+        <v>0.97709999999999997</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>3.3950999999999998</v>
+      </c>
+      <c r="AF12" s="1">
+        <v>0.65739999999999998</v>
+      </c>
+      <c r="AG12" s="1">
+        <v>0.31290000000000001</v>
+      </c>
+      <c r="AH12" s="1">
+        <v>0.23330000000000001</v>
+      </c>
+      <c r="AI12" s="28">
+        <v>0.72950000000000004</v>
+      </c>
+      <c r="AJ12" s="1">
+        <v>0.89690000000000003</v>
+      </c>
+      <c r="AK12" s="28">
+        <v>1.4026000000000001</v>
+      </c>
+      <c r="AL12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM12" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN12" s="28">
+        <v>1.6679E+35</v>
+      </c>
+      <c r="AO12" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP12" s="28">
+        <v>0.2475</v>
+      </c>
+      <c r="AQ12" s="28">
+        <v>1.2087000000000001</v>
+      </c>
+      <c r="AR12" s="28">
+        <v>0.75019999999999998</v>
+      </c>
+      <c r="AS12" s="28">
+        <v>0.93689999999999996</v>
+      </c>
+      <c r="AT12" s="28">
+        <v>1.5008999999999999</v>
+      </c>
+      <c r="AU12" s="28">
+        <v>4.2244999999999999E+130</v>
+      </c>
+      <c r="AV12" s="28">
+        <v>0.96819999999999995</v>
+      </c>
+      <c r="AW12" s="28">
+        <v>1.0764</v>
+      </c>
+      <c r="AX12" s="1">
+        <v>0.78720000000000001</v>
+      </c>
+      <c r="AY12" s="1">
+        <v>1.327</v>
+      </c>
+    </row>
+    <row r="13" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B13" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="28">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="J13" s="28">
+        <v>5.3078000000000003</v>
+      </c>
+      <c r="K13" s="28">
+        <v>2.7877999999999998</v>
+      </c>
+      <c r="L13" s="28">
+        <v>0.75170000000000003</v>
+      </c>
+      <c r="M13" s="28">
+        <v>0.70230000000000004</v>
+      </c>
+      <c r="N13" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="O13" s="28">
+        <v>0.35970000000000002</v>
+      </c>
+      <c r="P13" s="28">
+        <v>0.44280000000000003</v>
+      </c>
+      <c r="Q13" s="28">
+        <v>1.4796</v>
+      </c>
+      <c r="R13" s="28">
+        <v>0.48609999999999998</v>
+      </c>
+      <c r="S13" s="28">
+        <v>0.35449999999999998</v>
+      </c>
+      <c r="T13" s="28">
+        <v>0.52249999999999996</v>
+      </c>
+      <c r="U13" s="28">
+        <v>1.0941000000000001</v>
+      </c>
+      <c r="V13" s="28">
+        <v>1.1261000000000001</v>
+      </c>
+      <c r="W13" s="28">
+        <v>1.0622</v>
+      </c>
+      <c r="X13" s="1">
+        <v>0.97240000000000004</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>0.84130000000000005</v>
+      </c>
+      <c r="Z13" s="28">
+        <v>1.0689</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>2.2545999999999999</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>1.0762</v>
+      </c>
+      <c r="AC13" s="28">
+        <v>6.4069999999999998E+99</v>
+      </c>
+      <c r="AD13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>1.2293000000000001</v>
+      </c>
+      <c r="AF13" s="1">
+        <v>1.0359</v>
+      </c>
+      <c r="AG13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="1">
+        <v>4.8190999999999997</v>
+      </c>
+      <c r="AI13" s="28">
+        <v>1.5825</v>
+      </c>
+      <c r="AJ13" s="28">
+        <v>0.70620000000000005</v>
+      </c>
+      <c r="AK13" s="1">
+        <v>0.88660000000000005</v>
+      </c>
+      <c r="AL13" s="1">
+        <v>0.89410000000000001</v>
+      </c>
+      <c r="AM13" s="28">
+        <v>1.0528999999999999</v>
+      </c>
+      <c r="AN13" s="28">
+        <v>2.0619000000000001</v>
+      </c>
+      <c r="AO13" s="28">
+        <v>1.1359999999999999</v>
+      </c>
+      <c r="AP13" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ13" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR13" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT13" s="28">
+        <v>0.40250000000000002</v>
+      </c>
+      <c r="AU13" s="28">
+        <v>3.1251000000000002</v>
+      </c>
+      <c r="AV13" s="28">
+        <v>1.32</v>
+      </c>
+      <c r="AW13" s="28">
+        <v>2.2252000000000001</v>
+      </c>
+      <c r="AX13" s="28">
+        <v>1.3008</v>
+      </c>
+      <c r="AY13" s="28">
+        <v>2.2789999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B14" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="28">
+        <v>1.0946</v>
+      </c>
+      <c r="M14" s="28">
+        <v>1.5347999999999999</v>
+      </c>
+      <c r="N14" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="O14" s="28">
+        <v>0.54120000000000001</v>
+      </c>
+      <c r="P14" s="28">
+        <v>0.21840000000000001</v>
+      </c>
+      <c r="Q14" s="28">
+        <v>1.0235000000000001</v>
+      </c>
+      <c r="R14" s="28">
+        <v>3.1724000000000001</v>
+      </c>
+      <c r="S14" s="28">
+        <v>13.688800000000001</v>
+      </c>
+      <c r="T14" s="28">
+        <v>1.5456000000000001</v>
+      </c>
+      <c r="U14" s="28">
+        <v>0.56279999999999997</v>
+      </c>
+      <c r="V14" s="28">
+        <v>1.0620000000000001</v>
+      </c>
+      <c r="W14" s="28">
+        <v>1.236</v>
+      </c>
+      <c r="X14" s="28">
+        <v>1.4297</v>
+      </c>
+      <c r="Y14" s="28">
+        <v>0.84909999999999997</v>
+      </c>
+      <c r="Z14" s="28">
+        <v>1.9100999999999999</v>
+      </c>
+      <c r="AA14" s="28">
+        <v>1.3222</v>
+      </c>
+      <c r="AB14" s="28">
+        <v>1.6451</v>
+      </c>
+      <c r="AC14" s="28">
+        <v>1.0263</v>
+      </c>
+      <c r="AD14" s="28">
+        <v>0.48970000000000002</v>
+      </c>
+      <c r="AE14" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="28">
+        <v>1.8612</v>
+      </c>
+      <c r="AH14" s="1">
+        <v>3.2532000000000001</v>
+      </c>
+      <c r="AI14" s="28">
+        <v>2.9603000000000002</v>
+      </c>
+      <c r="AJ14" s="28">
+        <v>1.99</v>
+      </c>
+      <c r="AK14" s="28">
+        <v>1.9750000000000001</v>
+      </c>
+      <c r="AL14" s="28">
+        <v>1.9252</v>
+      </c>
+      <c r="AM14" s="28">
+        <v>2.1928000000000001</v>
+      </c>
+      <c r="AN14" s="28">
+        <v>3.9388000000000001</v>
+      </c>
+      <c r="AO14" s="28">
+        <v>6.2644999999999997E+107</v>
+      </c>
+      <c r="AP14" s="28">
+        <v>2.2501000000000002</v>
+      </c>
+      <c r="AQ14" s="28">
+        <v>2.1608000000000001</v>
+      </c>
+      <c r="AR14" s="28">
+        <v>1.8461000000000001</v>
+      </c>
+      <c r="AS14" s="28">
+        <v>2.0411000000000001</v>
+      </c>
+      <c r="AT14" s="28">
+        <v>1.881</v>
+      </c>
+      <c r="AU14" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV14" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW14" s="28">
+        <v>1.0967E+124</v>
+      </c>
+      <c r="AX14" s="28">
+        <v>2.2099000000000001E+123</v>
+      </c>
+      <c r="AY14" s="28">
+        <v>9.7100000000000009</v>
+      </c>
+    </row>
+    <row r="15" spans="2:51" x14ac:dyDescent="0.3">
+      <c r="B15" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="28">
+        <v>2.3651</v>
+      </c>
+      <c r="S15" s="28">
+        <v>1.2584</v>
+      </c>
+      <c r="T15" s="28">
+        <v>0.96630000000000005</v>
+      </c>
+      <c r="U15" s="28">
+        <v>261.04829999999998</v>
+      </c>
+      <c r="V15" s="28">
+        <v>1.5444</v>
+      </c>
+      <c r="W15" s="28">
+        <v>2.2850999999999999</v>
+      </c>
+      <c r="X15" s="28">
+        <v>1.8593</v>
+      </c>
+      <c r="Y15" s="28">
+        <v>1.4443999999999999</v>
+      </c>
+      <c r="Z15" s="28">
+        <v>1.7008000000000001</v>
+      </c>
+      <c r="AA15" s="28">
+        <v>1.4611000000000001</v>
+      </c>
+      <c r="AB15" s="28">
+        <v>2.3993000000000002</v>
+      </c>
+      <c r="AC15" s="28">
+        <v>1.5720000000000001</v>
+      </c>
+      <c r="AD15" s="28">
+        <v>7.5404</v>
+      </c>
+      <c r="AE15" s="28">
+        <v>2.0152999999999999</v>
+      </c>
+      <c r="AF15" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH15" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI15" s="28">
+        <v>0.58420000000000005</v>
+      </c>
+      <c r="AJ15" s="28">
+        <v>0.57979999999999998</v>
+      </c>
+      <c r="AK15" s="28">
+        <v>4.2016999999999998</v>
+      </c>
+      <c r="AL15" s="28">
+        <v>337.02640000000002</v>
+      </c>
+      <c r="AM15" s="28">
+        <v>4.3887</v>
+      </c>
+      <c r="AN15" s="28">
+        <v>6.2431000000000001</v>
+      </c>
+      <c r="AO15" s="28">
+        <v>4.7836999999999996</v>
+      </c>
+      <c r="AP15" s="28">
+        <v>2.1509999999999998</v>
+      </c>
+      <c r="AQ15" s="28">
+        <v>2.2425000000000002</v>
+      </c>
+      <c r="AR15" s="28">
+        <v>1.3763000000000001</v>
+      </c>
+      <c r="AS15" s="28">
+        <v>5.0964</v>
+      </c>
+      <c r="AT15" s="28">
+        <v>3.7332999999999998</v>
+      </c>
+      <c r="AU15" s="28">
+        <v>4.6148999999999996</v>
+      </c>
+      <c r="AV15" s="28">
+        <v>3.3820999999999999</v>
+      </c>
+      <c r="AW15" s="28">
+        <v>3.5024999999999999</v>
+      </c>
+      <c r="AX15" s="28">
+        <v>3.6312000000000002</v>
+      </c>
+      <c r="AY15" s="28">
+        <v>2.3393999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C3:AY15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="num" val="200"/>
+        <cfvo type="max"/>
+        <color rgb="FF92D050"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>